--- a/activity/M01A02/M01A02.xlsx
+++ b/activity/M01A02/M01A02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD508B7-4F1B-4D63-A92B-F7A5380DFF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E3A540-9D6A-4FF0-BF10-CFE8BB7812E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="66">
   <si>
     <t>J4660</t>
   </si>
@@ -159,12 +159,6 @@
     <t>Código</t>
   </si>
   <si>
-    <t>Calificación: 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Cuenca lateral 2 Fa independiente (Área original HMS = 15.195 km²)</t>
   </si>
   <si>
@@ -181,9 +175,6 @@
   </si>
   <si>
     <t>Hietogramas en repositorio</t>
-  </si>
-  <si>
-    <t>https://pruebacorreoescuelaingeduco.sharepoint.com/sites/HCMC/SitePages/HCMC0002.aspx</t>
   </si>
   <si>
     <t>Observaciones &gt;&gt;</t>
@@ -264,83 +255,37 @@
     <t>Autocalificación alumno</t>
   </si>
   <si>
-    <t>Falta</t>
+    <t>Grupo 6</t>
   </si>
   <si>
-    <t>Ok.</t>
+    <t>Grupo 7</t>
   </si>
   <si>
-    <t>Ok</t>
+    <t>Grupo 8</t>
   </si>
   <si>
-    <t>Nombre no corresponde al solicitado, sin fecha para control de versión</t>
+    <t>Grupo 9</t>
   </si>
   <si>
-    <t>No presentado</t>
+    <t>Grupo 10</t>
   </si>
   <si>
-    <t>No presentado, solo mostraron 1 gráfica con el ejemplo realizado en clase.</t>
+    <t>Grupo 11</t>
   </si>
   <si>
-    <t>No presentado, solo existe la versión del 20240818. En una nueva versión del libro de parámetros se deben registrar los caudales que utilizarán en el diseño.</t>
+    <t>Grupo 12</t>
   </si>
   <si>
-    <t>No presentado, solo existe la versión del 20240817. En una nueva versión del libro de parámetros se deben registrar los caudales que utilizarán en el diseño.</t>
+    <t>Grupo 13</t>
   </si>
   <si>
-    <t>Integrada en descarga lateral J4660</t>
+    <t>M01A02</t>
   </si>
   <si>
-    <t>No requerido</t>
+    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A02/Readme.md</t>
   </si>
   <si>
-    <t>Falto incluir las latitudes y longitudes en grados decimales.</t>
-  </si>
-  <si>
-    <t>Integrado en informe principal.</t>
-  </si>
-  <si>
-    <t>No presentado, solo existen las versiones anteriores. En una nueva versión del libro de parámetros se deben registrar los caudales que utilizarán en el diseño.</t>
-  </si>
-  <si>
-    <t>En QResumen falto incluir 3 curvas en las graficas generales. Sin registro de caudales a utilizar en los diseños en libro de parámetros.</t>
-  </si>
-  <si>
-    <t>Celdas en rojo corresponden a valores errados o incompletos. Todos los análisis de resultados de caudal se debían presentar en una única hoja. Hoja QResumen no integrada. Sin registro de caudales a utilizar en los diseños en libro de parámetros. Falto obtener los caudales para el factor de atenuación combinado en las cuencas laterales. El avance de radios de curvatura se presenta en la carpeta HCMC0003.</t>
-  </si>
-  <si>
-    <t>En los archivos de hietogramas no aparecen las columnas para 0.67 y 0.96.</t>
-  </si>
-  <si>
-    <t>Capturas de pantalla no muestran las cuencas disueltas utilizadas para el análisis de estadística zonal.</t>
-  </si>
-  <si>
-    <t>Incorporado parcialmente al informe principal pero sin las gráficas obtenidas directamente en HEC-HMS.</t>
-  </si>
-  <si>
-    <t>Comprimido corresponden al ejercicio de clase y no a su eje de proyecto</t>
-  </si>
-  <si>
-    <t>Datos entregados corresponden al ejercicio de clase y no a su eje de proyecto</t>
-  </si>
-  <si>
-    <t>Informe entregado corresponden al ejercicio de clase y no a su eje de proyecto</t>
-  </si>
-  <si>
-    <t>Informe y datos entregados corresponden al ejercicio de clase y no a su eje de proyecto.</t>
-  </si>
-  <si>
-    <t>Incluidos en comprimido de modelo HEC-HMS.</t>
-  </si>
-  <si>
-    <t>Falto incluir las coordenadas de múltiples localizaciones. La gráfica no requiere de líneas, solo la localización de puntos.</t>
-  </si>
-  <si>
-    <t>Celdas en rojo corresponden a valores errados o incompletos. Sin análisis de caudales medios y sin detalle de cálculos realizados por cuenca e hidrogramas mostrados en HEC-HMS, informe técnico incompleto. Hoja QResumen incompleta, faltan puntos de estudio y la incorporación de los valores leídos en las gráficas integradas. El avance de radios de curvatura se debe presentar en HCMC0003. Caudal TR 50 en R19120 con lectura errada. Falto la hoja de puntos de estudio con coordenadas de localización y criterios para valores de factores de atenuación. Los caudales en W19520 no son requeridos si en J4682 no se descontó esta área.</t>
-  </si>
-  <si>
-    <t>En QResumen falto incluir 3 curvas en las graficas generales. Sin registro de caudales a utilizar en los diseños en libro de parámetros.
-De acuerdo a lo indicado en la entrega HCMC0001, el valle del canal lo van a diseñar para 200 años de periodo de retorno y en las hojas de hidrogramas presentada, no se ha estimado el hidrograma y caudal pico en los nodos del cauce principal. No presentaron el informe complementario con los hidrogramas mostrados en HEC-HMS y las diferentes tablas donde se realizaron las lecturas de valores.</t>
+    <t>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</t>
   </si>
 </sst>
 </file>
@@ -352,7 +297,7 @@
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,11 +489,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -557,6 +497,18 @@
     <font>
       <sz val="8"/>
       <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -754,7 +706,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="32">
     <border>
       <left/>
       <right/>
@@ -924,36 +876,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
@@ -972,19 +898,6 @@
       </top>
       <bottom style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-4.9989318521683403E-2"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1113,6 +1026,93 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1122,21 +1122,21 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="25" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1155,7 +1155,7 @@
     <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -1167,7 +1167,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1207,9 +1207,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -1218,10 +1215,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1236,15 +1229,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1252,13 +1238,6 @@
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1268,47 +1247,15 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1325,58 +1272,75 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1387,21 +1351,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1415,47 +1364,29 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1545,7 +1476,7 @@
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
-              <c:v>Calificación: 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</c:v>
+              <c:v>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</c:v>
             </c:pt>
           </c:strCache>
         </c:strRef>
@@ -1594,7 +1525,7 @@
           <c:x val="0.13451837270341208"/>
           <c:y val="0.14726960784313725"/>
           <c:w val="0.83492607174103239"/>
-          <c:h val="0.48625065359477126"/>
+          <c:h val="0.5239936559784939"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -1657,19 +1588,19 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>4.5</c:v>
+                  <c:v>2.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>4.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.95</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.5999999999999996</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2517,8 +2448,8 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>57065</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>27176</xdr:rowOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>14883</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
@@ -2852,302 +2783,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF50BAE-D7A1-4B9B-8511-69070389923C}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="B2:F20"/>
+  <dimension ref="B1:F20"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" style="19" customWidth="1"/>
-    <col min="3" max="4" width="11.46484375" style="19" customWidth="1"/>
-    <col min="5" max="5" width="12.796875" style="19" customWidth="1"/>
-    <col min="6" max="6" width="11.46484375" style="19" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="19" customWidth="1"/>
-    <col min="8" max="16384" width="11.33203125" style="19"/>
+    <col min="1" max="1" width="2.6640625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" style="17" customWidth="1"/>
+    <col min="3" max="4" width="11.46484375" style="17" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="17" customWidth="1"/>
+    <col min="6" max="6" width="11.46484375" style="17" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="17" customWidth="1"/>
+    <col min="8" max="16384" width="11.33203125" style="17"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="F1" s="35" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="55" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
+      <c r="B2" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
     </row>
     <row r="4" spans="2:6" ht="32.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="D4" s="45" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="46" t="s">
-        <v>49</v>
+      <c r="C4" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B5" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="C5" s="51">
+      <c r="B5" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="33">
         <v>5</v>
       </c>
       <c r="D5" s="10">
         <f>Detalle!J22*C5/5</f>
-        <v>4</v>
-      </c>
-      <c r="E5" s="53">
+        <v>0</v>
+      </c>
+      <c r="E5" s="33">
         <v>5</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f>AVERAGE(D5:E5)</f>
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B6" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="51">
+      <c r="B6" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="33">
         <v>5</v>
       </c>
       <c r="D6" s="10">
         <f>Detalle!V22*C6/5</f>
-        <v>4.5</v>
-      </c>
-      <c r="E6" s="53"/>
-      <c r="F6" s="14">
+        <v>0</v>
+      </c>
+      <c r="E6" s="33"/>
+      <c r="F6" s="13">
         <f t="shared" ref="F6:F17" si="0">AVERAGE(D6:E6)</f>
-        <v>4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B7" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" s="51">
+      <c r="B7" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="33">
         <v>5</v>
       </c>
       <c r="D7" s="10">
         <f>Detalle!AH22*C7/5</f>
-        <v>4.95</v>
-      </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="14">
+        <v>0</v>
+      </c>
+      <c r="E7" s="33"/>
+      <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>4.95</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B8" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="51">
+      <c r="B8" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="33">
         <v>5</v>
       </c>
       <c r="D8" s="10">
         <f>Detalle!AT22*C8/5</f>
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="E8" s="53"/>
-      <c r="F8" s="14">
+        <v>0</v>
+      </c>
+      <c r="E8" s="33"/>
+      <c r="F8" s="13">
         <f t="shared" si="0"/>
-        <v>4.5999999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B9" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="51">
+      <c r="B9" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="33">
         <v>5</v>
       </c>
       <c r="D9" s="10">
         <f>Detalle!BF22*C9/5</f>
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="53"/>
-      <c r="F9" s="14">
+        <v>0</v>
+      </c>
+      <c r="E9" s="33"/>
+      <c r="F9" s="13">
         <f t="shared" si="0"/>
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B10" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="51">
+      <c r="B10" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="33">
         <v>5</v>
       </c>
       <c r="D10" s="10">
         <f>Detalle!BR22*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="14">
+      <c r="E10" s="33"/>
+      <c r="F10" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B11" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="51">
+      <c r="B11" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="33">
         <v>5</v>
       </c>
       <c r="D11" s="10">
         <f>Detalle!CD22*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="53"/>
-      <c r="F11" s="14">
+      <c r="E11" s="33"/>
+      <c r="F11" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B12" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="51">
+      <c r="B12" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="33">
         <v>5</v>
       </c>
       <c r="D12" s="10">
         <f>Detalle!CP22*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="53"/>
-      <c r="F12" s="14">
+      <c r="E12" s="33"/>
+      <c r="F12" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B13" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="51">
+      <c r="B13" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="33">
         <v>5</v>
       </c>
       <c r="D13" s="10">
         <f>Detalle!DB22*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="14">
+      <c r="E13" s="33"/>
+      <c r="F13" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B14" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="51">
+      <c r="B14" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="33">
         <v>5</v>
       </c>
       <c r="D14" s="10">
         <f>Detalle!DN22*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="53"/>
-      <c r="F14" s="14">
+      <c r="E14" s="33"/>
+      <c r="F14" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B15" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="51">
+      <c r="B15" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" s="33">
         <v>5</v>
       </c>
       <c r="D15" s="10">
         <f>Detalle!DZ22*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="53"/>
-      <c r="F15" s="14">
+      <c r="E15" s="33"/>
+      <c r="F15" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="51">
+      <c r="B16" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="33">
         <v>5</v>
       </c>
       <c r="D16" s="10">
         <f>Detalle!EL22*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="53"/>
-      <c r="F16" s="14">
+      <c r="E16" s="33"/>
+      <c r="F16" s="13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="52">
+      <c r="B17" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="34">
         <v>5</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="28">
         <f>Detalle!EX22*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="54"/>
-      <c r="F17" s="14">
+      <c r="E17" s="34"/>
+      <c r="F17" s="36">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B18" s="57" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
+      <c r="B18" s="47" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
+      <c r="B19" s="32"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="32"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="47"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
+      <c r="B20" s="32"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:F3"/>
-    <mergeCell ref="B18:F19"/>
+    <mergeCell ref="B18:F18"/>
   </mergeCells>
+  <phoneticPr fontId="29" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B18" r:id="rId1" xr:uid="{0ED9F5D1-07FA-4304-A913-580B839EC9D2}"/>
   </hyperlinks>
@@ -3224,8 +3161,9 @@
   <sheetData>
     <row r="1" spans="1:165" x14ac:dyDescent="0.45">
       <c r="A1" s="3"/>
-      <c r="B1" s="7" t="s">
-        <v>23</v>
+      <c r="B1" s="7" t="str">
+        <f>Calificacion!B2</f>
+        <v>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -3367,241 +3305,241 @@
     </row>
     <row r="2" spans="1:165" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="76" t="s">
+      <c r="C2" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="78" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="78"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="78"/>
-      <c r="I2" s="79"/>
-      <c r="J2" s="64" t="str">
+      <c r="D2" s="63" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="64"/>
+      <c r="J2" s="53" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="K2" s="65"/>
-      <c r="L2" s="66"/>
-      <c r="M2" s="66"/>
-      <c r="N2" s="66"/>
-      <c r="O2" s="66"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="66"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="68"/>
-      <c r="V2" s="64" t="str">
+      <c r="K2" s="54"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="53" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="W2" s="65"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="66"/>
-      <c r="Z2" s="66"/>
-      <c r="AA2" s="66"/>
-      <c r="AB2" s="66"/>
-      <c r="AC2" s="66"/>
-      <c r="AD2" s="66"/>
-      <c r="AE2" s="67"/>
-      <c r="AF2" s="67"/>
-      <c r="AG2" s="68"/>
-      <c r="AH2" s="64" t="str">
+      <c r="W2" s="54"/>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+      <c r="AA2" s="55"/>
+      <c r="AB2" s="55"/>
+      <c r="AC2" s="55"/>
+      <c r="AD2" s="55"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="53" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="AI2" s="65"/>
-      <c r="AJ2" s="66"/>
-      <c r="AK2" s="66"/>
-      <c r="AL2" s="66"/>
-      <c r="AM2" s="66"/>
-      <c r="AN2" s="66"/>
-      <c r="AO2" s="66"/>
-      <c r="AP2" s="66"/>
-      <c r="AQ2" s="67"/>
-      <c r="AR2" s="67"/>
-      <c r="AS2" s="68"/>
-      <c r="AT2" s="64" t="str">
+      <c r="AI2" s="54"/>
+      <c r="AJ2" s="55"/>
+      <c r="AK2" s="55"/>
+      <c r="AL2" s="55"/>
+      <c r="AM2" s="55"/>
+      <c r="AN2" s="55"/>
+      <c r="AO2" s="55"/>
+      <c r="AP2" s="55"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="57"/>
+      <c r="AT2" s="53" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="AU2" s="65"/>
-      <c r="AV2" s="66"/>
-      <c r="AW2" s="66"/>
-      <c r="AX2" s="66"/>
-      <c r="AY2" s="66"/>
-      <c r="AZ2" s="66"/>
-      <c r="BA2" s="66"/>
-      <c r="BB2" s="66"/>
-      <c r="BC2" s="67"/>
-      <c r="BD2" s="67"/>
-      <c r="BE2" s="68"/>
-      <c r="BF2" s="64" t="str">
+      <c r="AU2" s="54"/>
+      <c r="AV2" s="55"/>
+      <c r="AW2" s="55"/>
+      <c r="AX2" s="55"/>
+      <c r="AY2" s="55"/>
+      <c r="AZ2" s="55"/>
+      <c r="BA2" s="55"/>
+      <c r="BB2" s="55"/>
+      <c r="BC2" s="56"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="57"/>
+      <c r="BF2" s="53" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="BG2" s="66"/>
-      <c r="BH2" s="66"/>
-      <c r="BI2" s="66"/>
-      <c r="BJ2" s="66"/>
-      <c r="BK2" s="66"/>
-      <c r="BL2" s="66"/>
-      <c r="BM2" s="66"/>
-      <c r="BN2" s="66"/>
-      <c r="BO2" s="67"/>
-      <c r="BP2" s="67"/>
-      <c r="BQ2" s="68"/>
-      <c r="BR2" s="64" t="str">
+      <c r="BG2" s="55"/>
+      <c r="BH2" s="55"/>
+      <c r="BI2" s="55"/>
+      <c r="BJ2" s="55"/>
+      <c r="BK2" s="55"/>
+      <c r="BL2" s="55"/>
+      <c r="BM2" s="55"/>
+      <c r="BN2" s="55"/>
+      <c r="BO2" s="56"/>
+      <c r="BP2" s="56"/>
+      <c r="BQ2" s="57"/>
+      <c r="BR2" s="53" t="str">
         <f>Calificacion!$B10</f>
-        <v>N/A</v>
-      </c>
-      <c r="BS2" s="65"/>
-      <c r="BT2" s="66"/>
-      <c r="BU2" s="66"/>
-      <c r="BV2" s="66"/>
-      <c r="BW2" s="66"/>
-      <c r="BX2" s="66"/>
-      <c r="BY2" s="66"/>
-      <c r="BZ2" s="66"/>
-      <c r="CA2" s="67"/>
-      <c r="CB2" s="67"/>
-      <c r="CC2" s="68"/>
-      <c r="CD2" s="64" t="str">
+        <v>Grupo 6</v>
+      </c>
+      <c r="BS2" s="54"/>
+      <c r="BT2" s="55"/>
+      <c r="BU2" s="55"/>
+      <c r="BV2" s="55"/>
+      <c r="BW2" s="55"/>
+      <c r="BX2" s="55"/>
+      <c r="BY2" s="55"/>
+      <c r="BZ2" s="55"/>
+      <c r="CA2" s="56"/>
+      <c r="CB2" s="56"/>
+      <c r="CC2" s="57"/>
+      <c r="CD2" s="53" t="str">
         <f>Calificacion!$B11</f>
-        <v>N/A</v>
-      </c>
-      <c r="CE2" s="65"/>
-      <c r="CF2" s="66"/>
-      <c r="CG2" s="66"/>
-      <c r="CH2" s="66"/>
-      <c r="CI2" s="66"/>
-      <c r="CJ2" s="66"/>
-      <c r="CK2" s="66"/>
-      <c r="CL2" s="66"/>
-      <c r="CM2" s="67"/>
-      <c r="CN2" s="67"/>
-      <c r="CO2" s="68"/>
-      <c r="CP2" s="64" t="str">
+        <v>Grupo 7</v>
+      </c>
+      <c r="CE2" s="54"/>
+      <c r="CF2" s="55"/>
+      <c r="CG2" s="55"/>
+      <c r="CH2" s="55"/>
+      <c r="CI2" s="55"/>
+      <c r="CJ2" s="55"/>
+      <c r="CK2" s="55"/>
+      <c r="CL2" s="55"/>
+      <c r="CM2" s="56"/>
+      <c r="CN2" s="56"/>
+      <c r="CO2" s="57"/>
+      <c r="CP2" s="53" t="str">
         <f>Calificacion!$B12</f>
-        <v>N/A</v>
-      </c>
-      <c r="CQ2" s="65"/>
-      <c r="CR2" s="66"/>
-      <c r="CS2" s="66"/>
-      <c r="CT2" s="66"/>
-      <c r="CU2" s="66"/>
-      <c r="CV2" s="66"/>
-      <c r="CW2" s="66"/>
-      <c r="CX2" s="66"/>
-      <c r="CY2" s="67"/>
-      <c r="CZ2" s="67"/>
-      <c r="DA2" s="68"/>
-      <c r="DB2" s="64" t="str">
+        <v>Grupo 8</v>
+      </c>
+      <c r="CQ2" s="54"/>
+      <c r="CR2" s="55"/>
+      <c r="CS2" s="55"/>
+      <c r="CT2" s="55"/>
+      <c r="CU2" s="55"/>
+      <c r="CV2" s="55"/>
+      <c r="CW2" s="55"/>
+      <c r="CX2" s="55"/>
+      <c r="CY2" s="56"/>
+      <c r="CZ2" s="56"/>
+      <c r="DA2" s="57"/>
+      <c r="DB2" s="53" t="str">
         <f>Calificacion!$B13</f>
-        <v>N/A</v>
-      </c>
-      <c r="DC2" s="65"/>
-      <c r="DD2" s="66"/>
-      <c r="DE2" s="66"/>
-      <c r="DF2" s="66"/>
-      <c r="DG2" s="66"/>
-      <c r="DH2" s="66"/>
-      <c r="DI2" s="66"/>
-      <c r="DJ2" s="66"/>
-      <c r="DK2" s="67"/>
-      <c r="DL2" s="67"/>
-      <c r="DM2" s="68"/>
-      <c r="DN2" s="64" t="str">
+        <v>Grupo 9</v>
+      </c>
+      <c r="DC2" s="54"/>
+      <c r="DD2" s="55"/>
+      <c r="DE2" s="55"/>
+      <c r="DF2" s="55"/>
+      <c r="DG2" s="55"/>
+      <c r="DH2" s="55"/>
+      <c r="DI2" s="55"/>
+      <c r="DJ2" s="55"/>
+      <c r="DK2" s="56"/>
+      <c r="DL2" s="56"/>
+      <c r="DM2" s="57"/>
+      <c r="DN2" s="53" t="str">
         <f>Calificacion!$B14</f>
-        <v>N/A</v>
-      </c>
-      <c r="DO2" s="65"/>
-      <c r="DP2" s="66"/>
-      <c r="DQ2" s="66"/>
-      <c r="DR2" s="66"/>
-      <c r="DS2" s="66"/>
-      <c r="DT2" s="66"/>
-      <c r="DU2" s="66"/>
-      <c r="DV2" s="66"/>
-      <c r="DW2" s="67"/>
-      <c r="DX2" s="67"/>
-      <c r="DY2" s="68"/>
-      <c r="DZ2" s="64" t="str">
+        <v>Grupo 10</v>
+      </c>
+      <c r="DO2" s="54"/>
+      <c r="DP2" s="55"/>
+      <c r="DQ2" s="55"/>
+      <c r="DR2" s="55"/>
+      <c r="DS2" s="55"/>
+      <c r="DT2" s="55"/>
+      <c r="DU2" s="55"/>
+      <c r="DV2" s="55"/>
+      <c r="DW2" s="56"/>
+      <c r="DX2" s="56"/>
+      <c r="DY2" s="57"/>
+      <c r="DZ2" s="53" t="str">
         <f>Calificacion!$B15</f>
-        <v>N/A</v>
-      </c>
-      <c r="EA2" s="66"/>
-      <c r="EB2" s="66"/>
-      <c r="EC2" s="66"/>
-      <c r="ED2" s="66"/>
-      <c r="EE2" s="66"/>
-      <c r="EF2" s="66"/>
-      <c r="EG2" s="66"/>
-      <c r="EH2" s="66"/>
-      <c r="EI2" s="67"/>
-      <c r="EJ2" s="67"/>
-      <c r="EK2" s="68"/>
-      <c r="EL2" s="64" t="str">
+        <v>Grupo 11</v>
+      </c>
+      <c r="EA2" s="55"/>
+      <c r="EB2" s="55"/>
+      <c r="EC2" s="55"/>
+      <c r="ED2" s="55"/>
+      <c r="EE2" s="55"/>
+      <c r="EF2" s="55"/>
+      <c r="EG2" s="55"/>
+      <c r="EH2" s="55"/>
+      <c r="EI2" s="56"/>
+      <c r="EJ2" s="56"/>
+      <c r="EK2" s="57"/>
+      <c r="EL2" s="53" t="str">
         <f>Calificacion!$B16</f>
-        <v>N/A</v>
-      </c>
-      <c r="EM2" s="66"/>
-      <c r="EN2" s="66"/>
-      <c r="EO2" s="66"/>
-      <c r="EP2" s="66"/>
-      <c r="EQ2" s="66"/>
-      <c r="ER2" s="66"/>
-      <c r="ES2" s="66"/>
-      <c r="ET2" s="66"/>
-      <c r="EU2" s="67"/>
-      <c r="EV2" s="67"/>
-      <c r="EW2" s="68"/>
-      <c r="EX2" s="64" t="str">
+        <v>Grupo 12</v>
+      </c>
+      <c r="EM2" s="55"/>
+      <c r="EN2" s="55"/>
+      <c r="EO2" s="55"/>
+      <c r="EP2" s="55"/>
+      <c r="EQ2" s="55"/>
+      <c r="ER2" s="55"/>
+      <c r="ES2" s="55"/>
+      <c r="ET2" s="55"/>
+      <c r="EU2" s="56"/>
+      <c r="EV2" s="56"/>
+      <c r="EW2" s="57"/>
+      <c r="EX2" s="53" t="str">
         <f>Calificacion!$B17</f>
-        <v>N/A</v>
-      </c>
-      <c r="EY2" s="66"/>
-      <c r="EZ2" s="66"/>
-      <c r="FA2" s="66"/>
-      <c r="FB2" s="66"/>
-      <c r="FC2" s="66"/>
-      <c r="FD2" s="66"/>
-      <c r="FE2" s="66"/>
-      <c r="FF2" s="66"/>
-      <c r="FG2" s="67"/>
-      <c r="FH2" s="67"/>
-      <c r="FI2" s="68"/>
+        <v>Grupo 13</v>
+      </c>
+      <c r="EY2" s="55"/>
+      <c r="EZ2" s="55"/>
+      <c r="FA2" s="55"/>
+      <c r="FB2" s="55"/>
+      <c r="FC2" s="55"/>
+      <c r="FD2" s="55"/>
+      <c r="FE2" s="55"/>
+      <c r="FF2" s="55"/>
+      <c r="FG2" s="56"/>
+      <c r="FH2" s="56"/>
+      <c r="FI2" s="57"/>
     </row>
     <row r="3" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="75"/>
-      <c r="C3" s="77"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I3" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="J3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="38" t="s">
+      <c r="K3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="L3" s="8" t="s">
@@ -3626,18 +3564,18 @@
         <v>13</v>
       </c>
       <c r="S3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="U3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="V3" s="16" t="s">
+      <c r="V3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="W3" s="38" t="s">
+      <c r="W3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="X3" s="8" t="s">
@@ -3662,18 +3600,18 @@
         <v>13</v>
       </c>
       <c r="AE3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AF3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AG3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="AH3" s="16" t="s">
+      <c r="AH3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AI3" s="38" t="s">
+      <c r="AI3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="AJ3" s="8" t="s">
@@ -3698,18 +3636,18 @@
         <v>13</v>
       </c>
       <c r="AQ3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="AR3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AS3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="AT3" s="16" t="s">
+      <c r="AT3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AU3" s="38" t="s">
+      <c r="AU3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="AV3" s="8" t="s">
@@ -3734,15 +3672,15 @@
         <v>13</v>
       </c>
       <c r="BC3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="BD3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BE3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="BF3" s="16" t="s">
+      <c r="BF3" s="15" t="s">
         <v>5</v>
       </c>
       <c r="BG3" s="8" t="s">
@@ -3770,18 +3708,18 @@
         <v>13</v>
       </c>
       <c r="BO3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="BP3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="BQ3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="BR3" s="16" t="s">
+      <c r="BR3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="BS3" s="38" t="s">
+      <c r="BS3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="BT3" s="8" t="s">
@@ -3806,18 +3744,18 @@
         <v>13</v>
       </c>
       <c r="CA3" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="CB3" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="CC3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="CD3" s="16" t="s">
+      <c r="CD3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CE3" s="38" t="s">
+      <c r="CE3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="CF3" s="8" t="s">
@@ -3841,19 +3779,19 @@
       <c r="CL3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="CM3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="CN3" s="15" t="s">
-        <v>47</v>
+      <c r="CM3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="CN3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="CO3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="CP3" s="16" t="s">
+      <c r="CP3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="CQ3" s="38" t="s">
+      <c r="CQ3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="CR3" s="8" t="s">
@@ -3877,19 +3815,19 @@
       <c r="CX3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="CY3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="CZ3" s="15" t="s">
-        <v>47</v>
+      <c r="CY3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="CZ3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="DA3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DB3" s="16" t="s">
+      <c r="DB3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="DC3" s="38" t="s">
+      <c r="DC3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="DD3" s="8" t="s">
@@ -3913,19 +3851,19 @@
       <c r="DJ3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="DK3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="DL3" s="15" t="s">
-        <v>47</v>
+      <c r="DK3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="DL3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="DM3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DN3" s="16" t="s">
+      <c r="DN3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="DO3" s="38" t="s">
+      <c r="DO3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="DP3" s="8" t="s">
@@ -3949,19 +3887,19 @@
       <c r="DV3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="DW3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="DX3" s="15" t="s">
-        <v>47</v>
+      <c r="DW3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="DX3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="DY3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="DZ3" s="16" t="s">
+      <c r="DZ3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="EA3" s="38" t="s">
+      <c r="EA3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="EB3" s="8" t="s">
@@ -3985,19 +3923,19 @@
       <c r="EH3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="EI3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="EJ3" s="15" t="s">
-        <v>47</v>
+      <c r="EI3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="EJ3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="EK3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="EL3" s="16" t="s">
+      <c r="EL3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="EM3" s="38" t="s">
+      <c r="EM3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="EN3" s="8" t="s">
@@ -4021,19 +3959,19 @@
       <c r="ET3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="EU3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="EV3" s="15" t="s">
-        <v>47</v>
+      <c r="EU3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="EV3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="EW3" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="EX3" s="16" t="s">
+      <c r="EX3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="EY3" s="38" t="s">
+      <c r="EY3" s="27" t="s">
         <v>7</v>
       </c>
       <c r="EZ3" s="8" t="s">
@@ -4057,24 +3995,24 @@
       <c r="FF3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="FG3" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="FH3" s="15" t="s">
-        <v>47</v>
+      <c r="FG3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="FH3" s="14" t="s">
+        <v>44</v>
       </c>
       <c r="FI3" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:165" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:165" x14ac:dyDescent="0.45">
       <c r="B4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="21">
         <v>185.2118016</v>
       </c>
       <c r="E4" s="10">
@@ -4091,193 +4029,85 @@
       <c r="H4" s="9">
         <v>1232.8382879999999</v>
       </c>
-      <c r="I4" s="23">
+      <c r="I4" s="20">
         <f>(((G4-H4)/1000)*(D4*(1000*1000)))/(365*24*60*60)</f>
         <v>1.6061554631551613</v>
       </c>
-      <c r="J4" s="17">
-        <v>9</v>
-      </c>
-      <c r="K4" s="39">
-        <v>185.21</v>
-      </c>
-      <c r="L4" s="10">
-        <v>0.67</v>
-      </c>
-      <c r="M4" s="10">
-        <v>119.2</v>
-      </c>
-      <c r="N4" s="10">
-        <v>187.7</v>
-      </c>
-      <c r="O4" s="10">
-        <v>250.4</v>
-      </c>
-      <c r="P4" s="10">
-        <v>335.6</v>
-      </c>
-      <c r="Q4" s="10">
-        <v>402.6</v>
-      </c>
-      <c r="R4" s="10">
-        <v>472</v>
-      </c>
-      <c r="S4" s="10">
-        <v>1506.318</v>
-      </c>
-      <c r="T4" s="10">
-        <v>1232.8382879999999</v>
-      </c>
-      <c r="U4" s="14">
-        <v>1.606138300974125</v>
-      </c>
-      <c r="V4" s="17">
-        <v>9</v>
-      </c>
-      <c r="W4" s="50">
-        <v>185.21</v>
-      </c>
-      <c r="X4" s="48">
-        <v>0.67</v>
-      </c>
-      <c r="Y4" s="49">
-        <v>118.8</v>
-      </c>
-      <c r="Z4" s="49">
-        <v>187.6</v>
-      </c>
-      <c r="AA4" s="49">
-        <v>250.2</v>
-      </c>
-      <c r="AB4" s="49">
-        <v>335.5</v>
-      </c>
-      <c r="AC4" s="49">
-        <v>402.4</v>
-      </c>
-      <c r="AD4" s="49">
-        <v>472.2</v>
-      </c>
-      <c r="AE4" s="10">
-        <v>1506.318262</v>
-      </c>
-      <c r="AF4" s="10">
-        <v>1232.8382879999999</v>
-      </c>
-      <c r="AG4" s="14">
-        <v>1.6061398396924156</v>
-      </c>
-      <c r="AH4" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI4" s="39">
-        <v>185.21</v>
-      </c>
-      <c r="AJ4" s="10">
-        <v>0.67</v>
-      </c>
-      <c r="AK4" s="10">
-        <v>119.21</v>
-      </c>
-      <c r="AL4" s="10">
-        <v>187.67</v>
-      </c>
-      <c r="AM4" s="10">
-        <v>250.42</v>
-      </c>
-      <c r="AN4" s="10">
-        <v>335.59</v>
-      </c>
-      <c r="AO4" s="10">
-        <v>402.58</v>
-      </c>
-      <c r="AP4" s="10">
-        <v>472.01</v>
-      </c>
-      <c r="AQ4" s="10">
-        <v>1506.318262</v>
-      </c>
-      <c r="AR4" s="10">
-        <v>1232.8382879999999</v>
-      </c>
-      <c r="AS4" s="14">
-        <v>1.6061398396924156</v>
-      </c>
-      <c r="AT4" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU4" s="39">
-        <v>185.21</v>
-      </c>
-      <c r="AV4" s="39">
-        <v>0.67</v>
-      </c>
-      <c r="AW4" s="39">
-        <v>120.42</v>
-      </c>
-      <c r="AX4" s="39">
-        <v>189.41</v>
-      </c>
-      <c r="AY4" s="39">
-        <v>252.63</v>
-      </c>
-      <c r="AZ4" s="39">
-        <v>338.34</v>
-      </c>
-      <c r="BA4" s="39">
-        <v>405.74</v>
-      </c>
-      <c r="BB4" s="39">
-        <v>475.57</v>
-      </c>
-      <c r="BC4" s="39">
-        <v>1506.32</v>
-      </c>
-      <c r="BD4" s="39">
-        <v>1232.8399999999999</v>
-      </c>
-      <c r="BE4" s="14">
-        <v>1.61</v>
-      </c>
-      <c r="BF4" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG4" s="10">
-        <v>225.3574016</v>
-      </c>
-      <c r="BH4" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="BI4" s="10">
-        <v>130</v>
-      </c>
-      <c r="BJ4" s="10">
-        <v>205.9</v>
-      </c>
-      <c r="BK4" s="10">
-        <v>275.3</v>
-      </c>
-      <c r="BL4" s="10">
-        <v>369.9</v>
-      </c>
-      <c r="BM4" s="10">
-        <v>445</v>
-      </c>
-      <c r="BN4" s="10">
-        <v>522.1</v>
-      </c>
-      <c r="BO4" s="10">
-        <v>1508.479462</v>
-      </c>
-      <c r="BP4" s="10">
-        <v>1240.1193410000001</v>
-      </c>
-      <c r="BQ4" s="14">
-        <v>1.9177111733137235</v>
-      </c>
-      <c r="BR4" s="17"/>
-      <c r="BS4" s="39"/>
-      <c r="BT4" s="10"/>
+      <c r="J4" s="37">
+        <v>0</v>
+      </c>
+      <c r="K4" s="38"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="39"/>
+      <c r="V4" s="37">
+        <v>0</v>
+      </c>
+      <c r="W4" s="38"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="22"/>
+      <c r="AB4" s="22"/>
+      <c r="AC4" s="22"/>
+      <c r="AD4" s="22"/>
+      <c r="AE4" s="22"/>
+      <c r="AF4" s="22"/>
+      <c r="AG4" s="39"/>
+      <c r="AH4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="38"/>
+      <c r="AJ4" s="22"/>
+      <c r="AK4" s="22"/>
+      <c r="AL4" s="22"/>
+      <c r="AM4" s="22"/>
+      <c r="AN4" s="22"/>
+      <c r="AO4" s="22"/>
+      <c r="AP4" s="22"/>
+      <c r="AQ4" s="22"/>
+      <c r="AR4" s="22"/>
+      <c r="AS4" s="39"/>
+      <c r="AT4" s="37">
+        <v>0</v>
+      </c>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="22"/>
+      <c r="AW4" s="22"/>
+      <c r="AX4" s="22"/>
+      <c r="AY4" s="22"/>
+      <c r="AZ4" s="22"/>
+      <c r="BA4" s="22"/>
+      <c r="BB4" s="22"/>
+      <c r="BC4" s="22"/>
+      <c r="BD4" s="22"/>
+      <c r="BE4" s="39"/>
+      <c r="BF4" s="37">
+        <v>0</v>
+      </c>
+      <c r="BG4" s="38"/>
+      <c r="BH4" s="22"/>
+      <c r="BI4" s="22"/>
+      <c r="BJ4" s="22"/>
+      <c r="BK4" s="22"/>
+      <c r="BL4" s="22"/>
+      <c r="BM4" s="22"/>
+      <c r="BN4" s="22"/>
+      <c r="BO4" s="22"/>
+      <c r="BP4" s="22"/>
+      <c r="BQ4" s="39"/>
+      <c r="BR4" s="37">
+        <v>0</v>
+      </c>
+      <c r="BS4" s="38"/>
+      <c r="BT4" s="22"/>
       <c r="BU4" s="22"/>
       <c r="BV4" s="22"/>
       <c r="BW4" s="22"/>
@@ -4286,100 +4116,114 @@
       <c r="BZ4" s="22"/>
       <c r="CA4" s="22"/>
       <c r="CB4" s="22"/>
-      <c r="CC4" s="13"/>
-      <c r="CD4" s="17"/>
-      <c r="CE4" s="39"/>
-      <c r="CF4" s="10"/>
-      <c r="CG4" s="10"/>
-      <c r="CH4" s="10"/>
-      <c r="CI4" s="10"/>
-      <c r="CJ4" s="10"/>
-      <c r="CK4" s="10"/>
-      <c r="CL4" s="10"/>
-      <c r="CM4" s="23"/>
-      <c r="CN4" s="23"/>
-      <c r="CO4" s="14"/>
-      <c r="CP4" s="17"/>
-      <c r="CQ4" s="39"/>
-      <c r="CR4" s="10"/>
-      <c r="CS4" s="10"/>
-      <c r="CT4" s="10"/>
-      <c r="CU4" s="10"/>
-      <c r="CV4" s="10"/>
-      <c r="CW4" s="10"/>
-      <c r="CX4" s="10"/>
-      <c r="CY4" s="23"/>
-      <c r="CZ4" s="23"/>
-      <c r="DA4" s="14"/>
-      <c r="DB4" s="17"/>
-      <c r="DC4" s="39"/>
-      <c r="DD4" s="10"/>
-      <c r="DE4" s="10"/>
-      <c r="DF4" s="10"/>
-      <c r="DG4" s="10"/>
-      <c r="DH4" s="10"/>
-      <c r="DI4" s="10"/>
-      <c r="DJ4" s="10"/>
-      <c r="DK4" s="23"/>
-      <c r="DL4" s="23"/>
-      <c r="DM4" s="14"/>
-      <c r="DN4" s="17"/>
-      <c r="DO4" s="39"/>
-      <c r="DP4" s="10"/>
-      <c r="DQ4" s="10"/>
-      <c r="DR4" s="10"/>
-      <c r="DS4" s="10"/>
-      <c r="DT4" s="10"/>
-      <c r="DU4" s="10"/>
-      <c r="DV4" s="10"/>
-      <c r="DW4" s="23"/>
-      <c r="DX4" s="23"/>
-      <c r="DY4" s="14"/>
-      <c r="DZ4" s="17"/>
-      <c r="EA4" s="39"/>
-      <c r="EB4" s="10"/>
-      <c r="EC4" s="10"/>
-      <c r="ED4" s="10"/>
-      <c r="EE4" s="10"/>
-      <c r="EF4" s="10"/>
-      <c r="EG4" s="10"/>
-      <c r="EH4" s="10"/>
-      <c r="EI4" s="23"/>
-      <c r="EJ4" s="23"/>
-      <c r="EK4" s="14"/>
-      <c r="EL4" s="17"/>
-      <c r="EM4" s="39"/>
-      <c r="EN4" s="10"/>
-      <c r="EO4" s="10"/>
-      <c r="EP4" s="10"/>
-      <c r="EQ4" s="10"/>
-      <c r="ER4" s="10"/>
-      <c r="ES4" s="10"/>
-      <c r="ET4" s="10"/>
-      <c r="EU4" s="23"/>
-      <c r="EV4" s="23"/>
-      <c r="EW4" s="14"/>
-      <c r="EX4" s="17"/>
-      <c r="EY4" s="39"/>
-      <c r="EZ4" s="10"/>
-      <c r="FA4" s="10"/>
-      <c r="FB4" s="10"/>
-      <c r="FC4" s="10"/>
-      <c r="FD4" s="10"/>
-      <c r="FE4" s="10"/>
-      <c r="FF4" s="10"/>
-      <c r="FG4" s="23"/>
-      <c r="FH4" s="23"/>
-      <c r="FI4" s="14"/>
+      <c r="CC4" s="39"/>
+      <c r="CD4" s="37">
+        <v>0</v>
+      </c>
+      <c r="CE4" s="38"/>
+      <c r="CF4" s="22"/>
+      <c r="CG4" s="22"/>
+      <c r="CH4" s="22"/>
+      <c r="CI4" s="22"/>
+      <c r="CJ4" s="22"/>
+      <c r="CK4" s="22"/>
+      <c r="CL4" s="22"/>
+      <c r="CM4" s="22"/>
+      <c r="CN4" s="22"/>
+      <c r="CO4" s="39"/>
+      <c r="CP4" s="37">
+        <v>0</v>
+      </c>
+      <c r="CQ4" s="38"/>
+      <c r="CR4" s="22"/>
+      <c r="CS4" s="22"/>
+      <c r="CT4" s="22"/>
+      <c r="CU4" s="22"/>
+      <c r="CV4" s="22"/>
+      <c r="CW4" s="22"/>
+      <c r="CX4" s="22"/>
+      <c r="CY4" s="22"/>
+      <c r="CZ4" s="22"/>
+      <c r="DA4" s="39"/>
+      <c r="DB4" s="37">
+        <v>0</v>
+      </c>
+      <c r="DC4" s="38"/>
+      <c r="DD4" s="22"/>
+      <c r="DE4" s="22"/>
+      <c r="DF4" s="22"/>
+      <c r="DG4" s="22"/>
+      <c r="DH4" s="22"/>
+      <c r="DI4" s="22"/>
+      <c r="DJ4" s="22"/>
+      <c r="DK4" s="22"/>
+      <c r="DL4" s="22"/>
+      <c r="DM4" s="39"/>
+      <c r="DN4" s="37">
+        <v>0</v>
+      </c>
+      <c r="DO4" s="38"/>
+      <c r="DP4" s="22"/>
+      <c r="DQ4" s="22"/>
+      <c r="DR4" s="22"/>
+      <c r="DS4" s="22"/>
+      <c r="DT4" s="22"/>
+      <c r="DU4" s="22"/>
+      <c r="DV4" s="22"/>
+      <c r="DW4" s="22"/>
+      <c r="DX4" s="22"/>
+      <c r="DY4" s="39"/>
+      <c r="DZ4" s="37">
+        <v>0</v>
+      </c>
+      <c r="EA4" s="38"/>
+      <c r="EB4" s="22"/>
+      <c r="EC4" s="22"/>
+      <c r="ED4" s="22"/>
+      <c r="EE4" s="22"/>
+      <c r="EF4" s="22"/>
+      <c r="EG4" s="22"/>
+      <c r="EH4" s="22"/>
+      <c r="EI4" s="22"/>
+      <c r="EJ4" s="22"/>
+      <c r="EK4" s="39"/>
+      <c r="EL4" s="37">
+        <v>0</v>
+      </c>
+      <c r="EM4" s="38"/>
+      <c r="EN4" s="22"/>
+      <c r="EO4" s="22"/>
+      <c r="EP4" s="22"/>
+      <c r="EQ4" s="22"/>
+      <c r="ER4" s="22"/>
+      <c r="ES4" s="22"/>
+      <c r="ET4" s="22"/>
+      <c r="EU4" s="22"/>
+      <c r="EV4" s="22"/>
+      <c r="EW4" s="39"/>
+      <c r="EX4" s="37">
+        <v>0</v>
+      </c>
+      <c r="EY4" s="38"/>
+      <c r="EZ4" s="22"/>
+      <c r="FA4" s="22"/>
+      <c r="FB4" s="22"/>
+      <c r="FC4" s="22"/>
+      <c r="FD4" s="22"/>
+      <c r="FE4" s="22"/>
+      <c r="FF4" s="22"/>
+      <c r="FG4" s="22"/>
+      <c r="FH4" s="22"/>
+      <c r="FI4" s="39"/>
     </row>
     <row r="5" spans="1:165" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="21">
         <v>247.05620160000001</v>
       </c>
       <c r="E5" s="10">
@@ -4396,193 +4240,73 @@
       <c r="H5" s="9">
         <v>1243.4873700000001</v>
       </c>
-      <c r="I5" s="23">
+      <c r="I5" s="20">
         <f>(((G5-H5)/1000)*(D5*(1000*1000)))/(365*24*60*60)</f>
         <v>2.0708528536983977</v>
       </c>
-      <c r="J5" s="17">
-        <v>9</v>
-      </c>
-      <c r="K5" s="39">
-        <v>247.05620160000001</v>
-      </c>
-      <c r="L5" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="M5" s="10">
-        <v>127.7</v>
-      </c>
-      <c r="N5" s="10">
-        <v>202.4</v>
-      </c>
-      <c r="O5" s="10">
-        <v>271</v>
-      </c>
-      <c r="P5" s="10">
-        <v>364.5</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>438</v>
-      </c>
-      <c r="R5" s="10">
-        <v>514.20000000000005</v>
-      </c>
-      <c r="S5" s="10">
-        <v>1507.8256670000001</v>
-      </c>
-      <c r="T5" s="10">
-        <v>1243.4873700000001</v>
-      </c>
-      <c r="U5" s="14">
-        <v>2.0708528536983977</v>
-      </c>
-      <c r="V5" s="17">
-        <v>9</v>
-      </c>
-      <c r="W5" s="39">
-        <v>247.05620160000001</v>
-      </c>
-      <c r="X5" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="Y5" s="10">
-        <v>128.30000000000001</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>202.6</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>270.7</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>364.7</v>
-      </c>
-      <c r="AC5" s="10">
-        <v>438.3</v>
-      </c>
-      <c r="AD5" s="10">
-        <v>513.9</v>
-      </c>
-      <c r="AE5" s="10">
-        <v>1507.8256670000001</v>
-      </c>
-      <c r="AF5" s="10">
-        <v>1243.4873700000001</v>
-      </c>
-      <c r="AG5" s="14">
-        <v>2.0708528536983977</v>
-      </c>
-      <c r="AH5" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI5" s="39">
-        <v>247.06</v>
-      </c>
-      <c r="AJ5" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="AK5" s="10">
-        <v>127.67</v>
-      </c>
-      <c r="AL5" s="10">
-        <v>202.42</v>
-      </c>
-      <c r="AM5" s="10">
-        <v>271.04000000000002</v>
-      </c>
-      <c r="AN5" s="10">
-        <v>364.48</v>
-      </c>
-      <c r="AO5" s="10">
-        <v>437.97</v>
-      </c>
-      <c r="AP5" s="10">
-        <v>514.16</v>
-      </c>
-      <c r="AQ5" s="10">
-        <v>1507.8256668229701</v>
-      </c>
-      <c r="AR5" s="10">
-        <v>1243.4873700000001</v>
-      </c>
-      <c r="AS5" s="14">
-        <v>2.0708846909272891</v>
-      </c>
-      <c r="AT5" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU5" s="39">
-        <v>247.06</v>
-      </c>
-      <c r="AV5" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="AW5" s="10">
-        <v>128.96</v>
-      </c>
-      <c r="AX5" s="10">
-        <v>204.29</v>
-      </c>
-      <c r="AY5" s="10">
-        <v>273.41000000000003</v>
-      </c>
-      <c r="AZ5" s="10">
-        <v>367.45</v>
-      </c>
-      <c r="BA5" s="10">
-        <v>441.4</v>
-      </c>
-      <c r="BB5" s="10">
-        <v>518.04</v>
-      </c>
-      <c r="BC5" s="10">
-        <v>1507.83</v>
-      </c>
-      <c r="BD5" s="10">
-        <v>1243.49</v>
-      </c>
-      <c r="BE5" s="14">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="BF5" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG5" s="10">
-        <v>247.05620160000001</v>
-      </c>
-      <c r="BH5" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="BI5" s="10">
-        <v>128.30000000000001</v>
-      </c>
-      <c r="BJ5" s="10">
-        <v>202.6</v>
-      </c>
-      <c r="BK5" s="10">
-        <v>270.7</v>
-      </c>
-      <c r="BL5" s="10">
-        <v>364.7</v>
-      </c>
-      <c r="BM5" s="10">
-        <v>438.3</v>
-      </c>
-      <c r="BN5" s="10">
-        <v>513.9</v>
-      </c>
-      <c r="BO5" s="10">
-        <v>1507.8256670000001</v>
-      </c>
-      <c r="BP5" s="10">
-        <v>1243.4873698582501</v>
-      </c>
-      <c r="BQ5" s="14">
-        <v>2.0708528548088814</v>
-      </c>
-      <c r="BR5" s="17"/>
-      <c r="BS5" s="39"/>
-      <c r="BT5" s="10"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="38"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="39"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="38"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="22"/>
+      <c r="Z5" s="22"/>
+      <c r="AA5" s="22"/>
+      <c r="AB5" s="22"/>
+      <c r="AC5" s="22"/>
+      <c r="AD5" s="22"/>
+      <c r="AE5" s="22"/>
+      <c r="AF5" s="22"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="37"/>
+      <c r="AI5" s="38"/>
+      <c r="AJ5" s="22"/>
+      <c r="AK5" s="22"/>
+      <c r="AL5" s="22"/>
+      <c r="AM5" s="22"/>
+      <c r="AN5" s="22"/>
+      <c r="AO5" s="22"/>
+      <c r="AP5" s="22"/>
+      <c r="AQ5" s="22"/>
+      <c r="AR5" s="22"/>
+      <c r="AS5" s="39"/>
+      <c r="AT5" s="37"/>
+      <c r="AU5" s="38"/>
+      <c r="AV5" s="22"/>
+      <c r="AW5" s="22"/>
+      <c r="AX5" s="22"/>
+      <c r="AY5" s="22"/>
+      <c r="AZ5" s="22"/>
+      <c r="BA5" s="22"/>
+      <c r="BB5" s="22"/>
+      <c r="BC5" s="22"/>
+      <c r="BD5" s="22"/>
+      <c r="BE5" s="39"/>
+      <c r="BF5" s="37"/>
+      <c r="BG5" s="38"/>
+      <c r="BH5" s="22"/>
+      <c r="BI5" s="22"/>
+      <c r="BJ5" s="22"/>
+      <c r="BK5" s="22"/>
+      <c r="BL5" s="22"/>
+      <c r="BM5" s="22"/>
+      <c r="BN5" s="22"/>
+      <c r="BO5" s="22"/>
+      <c r="BP5" s="22"/>
+      <c r="BQ5" s="39"/>
+      <c r="BR5" s="37"/>
+      <c r="BS5" s="38"/>
+      <c r="BT5" s="22"/>
       <c r="BU5" s="22"/>
       <c r="BV5" s="22"/>
       <c r="BW5" s="22"/>
@@ -4591,100 +4315,100 @@
       <c r="BZ5" s="22"/>
       <c r="CA5" s="22"/>
       <c r="CB5" s="22"/>
-      <c r="CC5" s="13"/>
-      <c r="CD5" s="17"/>
-      <c r="CE5" s="39"/>
-      <c r="CF5" s="10"/>
-      <c r="CG5" s="10"/>
-      <c r="CH5" s="10"/>
-      <c r="CI5" s="10"/>
-      <c r="CJ5" s="10"/>
-      <c r="CK5" s="10"/>
-      <c r="CL5" s="10"/>
-      <c r="CM5" s="23"/>
-      <c r="CN5" s="23"/>
-      <c r="CO5" s="14"/>
-      <c r="CP5" s="17"/>
-      <c r="CQ5" s="39"/>
-      <c r="CR5" s="10"/>
-      <c r="CS5" s="10"/>
-      <c r="CT5" s="10"/>
-      <c r="CU5" s="10"/>
-      <c r="CV5" s="10"/>
-      <c r="CW5" s="10"/>
-      <c r="CX5" s="10"/>
-      <c r="CY5" s="23"/>
-      <c r="CZ5" s="23"/>
-      <c r="DA5" s="14"/>
-      <c r="DB5" s="17"/>
-      <c r="DC5" s="39"/>
-      <c r="DD5" s="10"/>
-      <c r="DE5" s="10"/>
-      <c r="DF5" s="10"/>
-      <c r="DG5" s="10"/>
-      <c r="DH5" s="10"/>
-      <c r="DI5" s="10"/>
-      <c r="DJ5" s="10"/>
-      <c r="DK5" s="23"/>
-      <c r="DL5" s="23"/>
-      <c r="DM5" s="14"/>
-      <c r="DN5" s="17"/>
-      <c r="DO5" s="39"/>
-      <c r="DP5" s="10"/>
-      <c r="DQ5" s="10"/>
-      <c r="DR5" s="10"/>
-      <c r="DS5" s="10"/>
-      <c r="DT5" s="10"/>
-      <c r="DU5" s="10"/>
-      <c r="DV5" s="10"/>
-      <c r="DW5" s="23"/>
-      <c r="DX5" s="23"/>
-      <c r="DY5" s="14"/>
-      <c r="DZ5" s="17"/>
-      <c r="EA5" s="39"/>
-      <c r="EB5" s="10"/>
-      <c r="EC5" s="10"/>
-      <c r="ED5" s="10"/>
-      <c r="EE5" s="10"/>
-      <c r="EF5" s="10"/>
-      <c r="EG5" s="10"/>
-      <c r="EH5" s="10"/>
-      <c r="EI5" s="23"/>
-      <c r="EJ5" s="23"/>
-      <c r="EK5" s="14"/>
-      <c r="EL5" s="17"/>
-      <c r="EM5" s="39"/>
-      <c r="EN5" s="10"/>
-      <c r="EO5" s="10"/>
-      <c r="EP5" s="10"/>
-      <c r="EQ5" s="10"/>
-      <c r="ER5" s="10"/>
-      <c r="ES5" s="10"/>
-      <c r="ET5" s="10"/>
-      <c r="EU5" s="23"/>
-      <c r="EV5" s="23"/>
-      <c r="EW5" s="14"/>
-      <c r="EX5" s="17"/>
-      <c r="EY5" s="39"/>
-      <c r="EZ5" s="10"/>
-      <c r="FA5" s="10"/>
-      <c r="FB5" s="10"/>
-      <c r="FC5" s="10"/>
-      <c r="FD5" s="10"/>
-      <c r="FE5" s="10"/>
-      <c r="FF5" s="10"/>
-      <c r="FG5" s="23"/>
-      <c r="FH5" s="23"/>
-      <c r="FI5" s="14"/>
+      <c r="CC5" s="39"/>
+      <c r="CD5" s="37"/>
+      <c r="CE5" s="38"/>
+      <c r="CF5" s="22"/>
+      <c r="CG5" s="22"/>
+      <c r="CH5" s="22"/>
+      <c r="CI5" s="22"/>
+      <c r="CJ5" s="22"/>
+      <c r="CK5" s="22"/>
+      <c r="CL5" s="22"/>
+      <c r="CM5" s="22"/>
+      <c r="CN5" s="22"/>
+      <c r="CO5" s="39"/>
+      <c r="CP5" s="37"/>
+      <c r="CQ5" s="38"/>
+      <c r="CR5" s="22"/>
+      <c r="CS5" s="22"/>
+      <c r="CT5" s="22"/>
+      <c r="CU5" s="22"/>
+      <c r="CV5" s="22"/>
+      <c r="CW5" s="22"/>
+      <c r="CX5" s="22"/>
+      <c r="CY5" s="22"/>
+      <c r="CZ5" s="22"/>
+      <c r="DA5" s="39"/>
+      <c r="DB5" s="37"/>
+      <c r="DC5" s="38"/>
+      <c r="DD5" s="22"/>
+      <c r="DE5" s="22"/>
+      <c r="DF5" s="22"/>
+      <c r="DG5" s="22"/>
+      <c r="DH5" s="22"/>
+      <c r="DI5" s="22"/>
+      <c r="DJ5" s="22"/>
+      <c r="DK5" s="22"/>
+      <c r="DL5" s="22"/>
+      <c r="DM5" s="39"/>
+      <c r="DN5" s="37"/>
+      <c r="DO5" s="38"/>
+      <c r="DP5" s="22"/>
+      <c r="DQ5" s="22"/>
+      <c r="DR5" s="22"/>
+      <c r="DS5" s="22"/>
+      <c r="DT5" s="22"/>
+      <c r="DU5" s="22"/>
+      <c r="DV5" s="22"/>
+      <c r="DW5" s="22"/>
+      <c r="DX5" s="22"/>
+      <c r="DY5" s="39"/>
+      <c r="DZ5" s="37"/>
+      <c r="EA5" s="38"/>
+      <c r="EB5" s="22"/>
+      <c r="EC5" s="22"/>
+      <c r="ED5" s="22"/>
+      <c r="EE5" s="22"/>
+      <c r="EF5" s="22"/>
+      <c r="EG5" s="22"/>
+      <c r="EH5" s="22"/>
+      <c r="EI5" s="22"/>
+      <c r="EJ5" s="22"/>
+      <c r="EK5" s="39"/>
+      <c r="EL5" s="37"/>
+      <c r="EM5" s="38"/>
+      <c r="EN5" s="22"/>
+      <c r="EO5" s="22"/>
+      <c r="EP5" s="22"/>
+      <c r="EQ5" s="22"/>
+      <c r="ER5" s="22"/>
+      <c r="ES5" s="22"/>
+      <c r="ET5" s="22"/>
+      <c r="EU5" s="22"/>
+      <c r="EV5" s="22"/>
+      <c r="EW5" s="39"/>
+      <c r="EX5" s="37"/>
+      <c r="EY5" s="38"/>
+      <c r="EZ5" s="22"/>
+      <c r="FA5" s="22"/>
+      <c r="FB5" s="22"/>
+      <c r="FC5" s="22"/>
+      <c r="FD5" s="22"/>
+      <c r="FE5" s="22"/>
+      <c r="FF5" s="22"/>
+      <c r="FG5" s="22"/>
+      <c r="FH5" s="22"/>
+      <c r="FI5" s="39"/>
     </row>
     <row r="6" spans="1:165" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="21">
         <v>225.3574016</v>
       </c>
       <c r="E6" s="10">
@@ -4701,216 +4425,96 @@
       <c r="H6" s="9">
         <v>1240.1193410000001</v>
       </c>
-      <c r="I6" s="23">
+      <c r="I6" s="20">
         <f t="shared" ref="I6:I11" si="2">(((G6-H6)/1000)*(D6*(1000*1000)))/(365*24*60*60)</f>
         <v>1.9177111733137235</v>
       </c>
-      <c r="J6" s="17">
-        <v>9</v>
-      </c>
-      <c r="K6" s="42">
-        <v>185.21</v>
-      </c>
-      <c r="L6" s="22">
-        <v>0.63</v>
-      </c>
-      <c r="M6" s="10">
-        <v>130</v>
-      </c>
-      <c r="N6" s="10">
-        <v>205.9</v>
-      </c>
-      <c r="O6" s="10">
-        <v>275.60000000000002</v>
-      </c>
-      <c r="P6" s="10">
-        <v>370.4</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>444.9</v>
-      </c>
-      <c r="R6" s="10">
-        <v>522.1</v>
-      </c>
-      <c r="S6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U6" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="V6" s="17">
-        <v>9</v>
-      </c>
-      <c r="W6" s="39">
-        <v>225.36</v>
-      </c>
-      <c r="X6" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="Y6" s="10">
-        <v>130</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>205.9</v>
-      </c>
-      <c r="AA6" s="10">
-        <v>275.3</v>
-      </c>
-      <c r="AB6" s="10">
-        <v>369.9</v>
-      </c>
-      <c r="AC6" s="10">
-        <v>445</v>
-      </c>
-      <c r="AD6" s="10">
-        <v>522.1</v>
-      </c>
-      <c r="AE6" s="10">
-        <v>1508.479462</v>
-      </c>
-      <c r="AF6" s="10">
-        <v>1240.1193410000001</v>
-      </c>
-      <c r="AG6" s="14">
-        <v>1.917733284771689</v>
-      </c>
-      <c r="AH6" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI6" s="39">
-        <v>225.36</v>
-      </c>
-      <c r="AJ6" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="AK6" s="10">
-        <v>130.02000000000001</v>
-      </c>
-      <c r="AL6" s="10">
-        <v>205.91</v>
-      </c>
-      <c r="AM6" s="10">
-        <v>275.60000000000002</v>
-      </c>
-      <c r="AN6" s="10">
-        <v>370.37</v>
-      </c>
-      <c r="AO6" s="10">
-        <v>444.87</v>
-      </c>
-      <c r="AP6" s="10">
-        <v>522.1</v>
-      </c>
-      <c r="AQ6" s="10">
-        <v>1508.479462</v>
-      </c>
-      <c r="AR6" s="10">
-        <v>1240.1193410000001</v>
-      </c>
-      <c r="AS6" s="14">
-        <v>1.917733284771689</v>
-      </c>
-      <c r="AT6" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU6" s="39">
-        <v>225.36</v>
-      </c>
-      <c r="AV6" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="AW6" s="10">
-        <v>131.34</v>
-      </c>
-      <c r="AX6" s="10">
-        <v>207.82</v>
-      </c>
-      <c r="AY6" s="10">
-        <v>278.01</v>
-      </c>
-      <c r="AZ6" s="10">
-        <v>373.39</v>
-      </c>
-      <c r="BA6" s="10">
-        <v>448.37</v>
-      </c>
-      <c r="BB6" s="10">
-        <v>526.04</v>
-      </c>
-      <c r="BC6" s="39">
-        <v>1508.48</v>
-      </c>
-      <c r="BD6" s="39">
-        <v>1240.1199999999999</v>
-      </c>
-      <c r="BE6" s="39">
-        <v>1.92</v>
-      </c>
-      <c r="BF6" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BM6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP6" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BQ6" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="BR6" s="17"/>
-      <c r="BS6" s="39"/>
-      <c r="BT6" s="10"/>
-      <c r="BU6" s="10"/>
-      <c r="BV6" s="10"/>
-      <c r="BW6" s="10"/>
-      <c r="BX6" s="10"/>
-      <c r="BY6" s="10"/>
-      <c r="BZ6" s="10"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="22"/>
+      <c r="P6" s="22"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="22"/>
+      <c r="S6" s="22"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="22"/>
+      <c r="Z6" s="22"/>
+      <c r="AA6" s="22"/>
+      <c r="AB6" s="22"/>
+      <c r="AC6" s="22"/>
+      <c r="AD6" s="22"/>
+      <c r="AE6" s="22"/>
+      <c r="AF6" s="22"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="37"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="22"/>
+      <c r="AK6" s="22"/>
+      <c r="AL6" s="22"/>
+      <c r="AM6" s="22"/>
+      <c r="AN6" s="22"/>
+      <c r="AO6" s="22"/>
+      <c r="AP6" s="22"/>
+      <c r="AQ6" s="22"/>
+      <c r="AR6" s="22"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="37"/>
+      <c r="AU6" s="38"/>
+      <c r="AV6" s="22"/>
+      <c r="AW6" s="22"/>
+      <c r="AX6" s="22"/>
+      <c r="AY6" s="22"/>
+      <c r="AZ6" s="22"/>
+      <c r="BA6" s="22"/>
+      <c r="BB6" s="22"/>
+      <c r="BC6" s="22"/>
+      <c r="BD6" s="22"/>
+      <c r="BE6" s="39"/>
+      <c r="BF6" s="37"/>
+      <c r="BG6" s="38"/>
+      <c r="BH6" s="22"/>
+      <c r="BI6" s="22"/>
+      <c r="BJ6" s="22"/>
+      <c r="BK6" s="22"/>
+      <c r="BL6" s="22"/>
+      <c r="BM6" s="22"/>
+      <c r="BN6" s="22"/>
+      <c r="BO6" s="22"/>
+      <c r="BP6" s="22"/>
+      <c r="BQ6" s="39"/>
+      <c r="BR6" s="37"/>
+      <c r="BS6" s="38"/>
+      <c r="BT6" s="22"/>
+      <c r="BU6" s="22"/>
+      <c r="BV6" s="22"/>
+      <c r="BW6" s="22"/>
+      <c r="BX6" s="22"/>
+      <c r="BY6" s="22"/>
+      <c r="BZ6" s="22"/>
       <c r="CA6" s="22"/>
       <c r="CB6" s="22"/>
-      <c r="CC6" s="13"/>
-      <c r="CD6" s="17"/>
-      <c r="CE6" s="39"/>
-      <c r="CF6" s="10"/>
-      <c r="CG6" s="10"/>
-      <c r="CH6" s="10"/>
-      <c r="CI6" s="10"/>
-      <c r="CJ6" s="10"/>
-      <c r="CK6" s="10"/>
-      <c r="CL6" s="10"/>
-      <c r="CM6" s="23"/>
-      <c r="CN6" s="23"/>
-      <c r="CO6" s="14"/>
-      <c r="CP6" s="17"/>
-      <c r="CQ6" s="42"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="37"/>
+      <c r="CE6" s="38"/>
+      <c r="CF6" s="22"/>
+      <c r="CG6" s="22"/>
+      <c r="CH6" s="22"/>
+      <c r="CI6" s="22"/>
+      <c r="CJ6" s="22"/>
+      <c r="CK6" s="22"/>
+      <c r="CL6" s="22"/>
+      <c r="CM6" s="22"/>
+      <c r="CN6" s="22"/>
+      <c r="CO6" s="39"/>
+      <c r="CP6" s="37"/>
+      <c r="CQ6" s="38"/>
       <c r="CR6" s="22"/>
       <c r="CS6" s="22"/>
       <c r="CT6" s="22"/>
@@ -4918,78 +4522,78 @@
       <c r="CV6" s="22"/>
       <c r="CW6" s="22"/>
       <c r="CX6" s="22"/>
-      <c r="CY6" s="27"/>
-      <c r="CZ6" s="27"/>
-      <c r="DA6" s="13"/>
-      <c r="DB6" s="17"/>
-      <c r="DC6" s="39"/>
-      <c r="DD6" s="10"/>
-      <c r="DE6" s="10"/>
-      <c r="DF6" s="10"/>
-      <c r="DG6" s="10"/>
-      <c r="DH6" s="10"/>
-      <c r="DI6" s="10"/>
-      <c r="DJ6" s="10"/>
-      <c r="DK6" s="23"/>
-      <c r="DL6" s="23"/>
-      <c r="DM6" s="14"/>
-      <c r="DN6" s="17"/>
-      <c r="DO6" s="39"/>
-      <c r="DP6" s="10"/>
-      <c r="DQ6" s="10"/>
-      <c r="DR6" s="10"/>
-      <c r="DS6" s="10"/>
-      <c r="DT6" s="10"/>
-      <c r="DU6" s="10"/>
-      <c r="DV6" s="10"/>
-      <c r="DW6" s="23"/>
-      <c r="DX6" s="23"/>
-      <c r="DY6" s="14"/>
-      <c r="DZ6" s="17"/>
-      <c r="EA6" s="39"/>
-      <c r="EB6" s="10"/>
-      <c r="EC6" s="10"/>
-      <c r="ED6" s="10"/>
-      <c r="EE6" s="10"/>
-      <c r="EF6" s="10"/>
-      <c r="EG6" s="10"/>
-      <c r="EH6" s="10"/>
-      <c r="EI6" s="23"/>
-      <c r="EJ6" s="23"/>
-      <c r="EK6" s="14"/>
-      <c r="EL6" s="17"/>
-      <c r="EM6" s="39"/>
-      <c r="EN6" s="10"/>
-      <c r="EO6" s="10"/>
-      <c r="EP6" s="10"/>
-      <c r="EQ6" s="10"/>
-      <c r="ER6" s="10"/>
-      <c r="ES6" s="10"/>
-      <c r="ET6" s="10"/>
-      <c r="EU6" s="23"/>
-      <c r="EV6" s="23"/>
-      <c r="EW6" s="14"/>
-      <c r="EX6" s="17"/>
-      <c r="EY6" s="39"/>
-      <c r="EZ6" s="10"/>
-      <c r="FA6" s="10"/>
-      <c r="FB6" s="10"/>
-      <c r="FC6" s="10"/>
-      <c r="FD6" s="10"/>
-      <c r="FE6" s="10"/>
-      <c r="FF6" s="10"/>
-      <c r="FG6" s="23"/>
-      <c r="FH6" s="23"/>
-      <c r="FI6" s="14"/>
+      <c r="CY6" s="22"/>
+      <c r="CZ6" s="22"/>
+      <c r="DA6" s="39"/>
+      <c r="DB6" s="37"/>
+      <c r="DC6" s="38"/>
+      <c r="DD6" s="22"/>
+      <c r="DE6" s="22"/>
+      <c r="DF6" s="22"/>
+      <c r="DG6" s="22"/>
+      <c r="DH6" s="22"/>
+      <c r="DI6" s="22"/>
+      <c r="DJ6" s="22"/>
+      <c r="DK6" s="22"/>
+      <c r="DL6" s="22"/>
+      <c r="DM6" s="39"/>
+      <c r="DN6" s="37"/>
+      <c r="DO6" s="38"/>
+      <c r="DP6" s="22"/>
+      <c r="DQ6" s="22"/>
+      <c r="DR6" s="22"/>
+      <c r="DS6" s="22"/>
+      <c r="DT6" s="22"/>
+      <c r="DU6" s="22"/>
+      <c r="DV6" s="22"/>
+      <c r="DW6" s="22"/>
+      <c r="DX6" s="22"/>
+      <c r="DY6" s="39"/>
+      <c r="DZ6" s="37"/>
+      <c r="EA6" s="38"/>
+      <c r="EB6" s="22"/>
+      <c r="EC6" s="22"/>
+      <c r="ED6" s="22"/>
+      <c r="EE6" s="22"/>
+      <c r="EF6" s="22"/>
+      <c r="EG6" s="22"/>
+      <c r="EH6" s="22"/>
+      <c r="EI6" s="22"/>
+      <c r="EJ6" s="22"/>
+      <c r="EK6" s="39"/>
+      <c r="EL6" s="37"/>
+      <c r="EM6" s="38"/>
+      <c r="EN6" s="22"/>
+      <c r="EO6" s="22"/>
+      <c r="EP6" s="22"/>
+      <c r="EQ6" s="22"/>
+      <c r="ER6" s="22"/>
+      <c r="ES6" s="22"/>
+      <c r="ET6" s="22"/>
+      <c r="EU6" s="22"/>
+      <c r="EV6" s="22"/>
+      <c r="EW6" s="39"/>
+      <c r="EX6" s="37"/>
+      <c r="EY6" s="38"/>
+      <c r="EZ6" s="22"/>
+      <c r="FA6" s="22"/>
+      <c r="FB6" s="22"/>
+      <c r="FC6" s="22"/>
+      <c r="FD6" s="22"/>
+      <c r="FE6" s="22"/>
+      <c r="FF6" s="22"/>
+      <c r="FG6" s="22"/>
+      <c r="FH6" s="22"/>
+      <c r="FI6" s="39"/>
     </row>
     <row r="7" spans="1:165" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="25">
+        <v>40</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="21">
         <v>37.47</v>
       </c>
       <c r="E7" s="10">
@@ -5006,193 +4610,73 @@
       <c r="H7" s="9">
         <v>1273.7525479999999</v>
       </c>
-      <c r="I7" s="23">
+      <c r="I7" s="20">
         <f>(((G7-H7)/1000)*(D7*(1000*1000)))/(365*24*60*60)</f>
         <v>0.29358798665525127</v>
       </c>
-      <c r="J7" s="17">
-        <v>9</v>
-      </c>
-      <c r="K7" s="42">
-        <v>26.1</v>
-      </c>
-      <c r="L7" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="M7" s="22">
-        <v>48.3</v>
-      </c>
-      <c r="N7" s="22">
-        <v>70</v>
-      </c>
-      <c r="O7" s="22">
-        <v>88.7</v>
-      </c>
-      <c r="P7" s="22">
-        <v>113.5</v>
-      </c>
-      <c r="Q7" s="22">
-        <v>132.30000000000001</v>
-      </c>
-      <c r="R7" s="22">
-        <v>151.4</v>
-      </c>
-      <c r="S7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U7" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="V7" s="17">
-        <v>9</v>
-      </c>
-      <c r="W7" s="39">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="X7" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="10">
-        <v>60</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>86.2</v>
-      </c>
-      <c r="AA7" s="10">
-        <v>108.7</v>
-      </c>
-      <c r="AB7" s="10">
-        <v>138.30000000000001</v>
-      </c>
-      <c r="AC7" s="10">
-        <v>160.69999999999999</v>
-      </c>
-      <c r="AD7" s="10">
-        <v>183.4</v>
-      </c>
-      <c r="AE7" s="10">
-        <v>1518.45</v>
-      </c>
-      <c r="AF7" s="10">
-        <v>1273.71</v>
-      </c>
-      <c r="AG7" s="14">
-        <v>0.31</v>
-      </c>
-      <c r="AH7" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI7" s="39">
-        <v>37.47</v>
-      </c>
-      <c r="AJ7" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="AK7" s="10">
-        <v>55.32</v>
-      </c>
-      <c r="AL7" s="10">
-        <v>79.89</v>
-      </c>
-      <c r="AM7" s="10">
-        <v>101.12</v>
-      </c>
-      <c r="AN7" s="10">
-        <v>129.06</v>
-      </c>
-      <c r="AO7" s="10">
-        <v>150.17000000000002</v>
-      </c>
-      <c r="AP7" s="10">
-        <v>171.66</v>
-      </c>
-      <c r="AQ7" s="39">
-        <v>1520.8459760000001</v>
-      </c>
-      <c r="AR7" s="39">
-        <v>1273.7525479999999</v>
-      </c>
-      <c r="AS7" s="39">
-        <v>0.29358798665525127</v>
-      </c>
-      <c r="AT7" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU7" s="39">
-        <v>37.47</v>
-      </c>
-      <c r="AV7" s="10">
-        <v>0.96</v>
-      </c>
-      <c r="AW7" s="10">
-        <v>55.74</v>
-      </c>
-      <c r="AX7" s="10">
-        <v>80.45</v>
-      </c>
-      <c r="AY7" s="10">
-        <v>101.79</v>
-      </c>
-      <c r="AZ7" s="10">
-        <v>129.87</v>
-      </c>
-      <c r="BA7" s="10">
-        <v>151.13</v>
-      </c>
-      <c r="BB7" s="10">
-        <v>172.71</v>
-      </c>
-      <c r="BC7" s="39">
-        <v>1520.85</v>
-      </c>
-      <c r="BD7" s="39">
-        <v>1273.75</v>
-      </c>
-      <c r="BE7" s="14">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="BF7" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BM7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP7" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BQ7" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="BR7" s="17"/>
-      <c r="BS7" s="39"/>
-      <c r="BT7" s="10"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="22"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="22"/>
+      <c r="S7" s="22"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="39"/>
+      <c r="V7" s="37"/>
+      <c r="W7" s="38"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="22"/>
+      <c r="AA7" s="22"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="22"/>
+      <c r="AE7" s="22"/>
+      <c r="AF7" s="22"/>
+      <c r="AG7" s="39"/>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="38"/>
+      <c r="AJ7" s="22"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="22"/>
+      <c r="AM7" s="22"/>
+      <c r="AN7" s="22"/>
+      <c r="AO7" s="22"/>
+      <c r="AP7" s="22"/>
+      <c r="AQ7" s="22"/>
+      <c r="AR7" s="22"/>
+      <c r="AS7" s="39"/>
+      <c r="AT7" s="37"/>
+      <c r="AU7" s="38"/>
+      <c r="AV7" s="22"/>
+      <c r="AW7" s="22"/>
+      <c r="AX7" s="22"/>
+      <c r="AY7" s="22"/>
+      <c r="AZ7" s="22"/>
+      <c r="BA7" s="22"/>
+      <c r="BB7" s="22"/>
+      <c r="BC7" s="22"/>
+      <c r="BD7" s="22"/>
+      <c r="BE7" s="39"/>
+      <c r="BF7" s="37"/>
+      <c r="BG7" s="38"/>
+      <c r="BH7" s="22"/>
+      <c r="BI7" s="22"/>
+      <c r="BJ7" s="22"/>
+      <c r="BK7" s="22"/>
+      <c r="BL7" s="22"/>
+      <c r="BM7" s="22"/>
+      <c r="BN7" s="22"/>
+      <c r="BO7" s="22"/>
+      <c r="BP7" s="22"/>
+      <c r="BQ7" s="39"/>
+      <c r="BR7" s="37"/>
+      <c r="BS7" s="38"/>
+      <c r="BT7" s="22"/>
       <c r="BU7" s="22"/>
       <c r="BV7" s="22"/>
       <c r="BW7" s="22"/>
@@ -5201,106 +4685,106 @@
       <c r="BZ7" s="22"/>
       <c r="CA7" s="22"/>
       <c r="CB7" s="22"/>
-      <c r="CC7" s="13"/>
-      <c r="CD7" s="17"/>
-      <c r="CE7" s="42"/>
-      <c r="CF7" s="10"/>
-      <c r="CG7" s="10"/>
-      <c r="CH7" s="10"/>
-      <c r="CI7" s="10"/>
-      <c r="CJ7" s="10"/>
-      <c r="CK7" s="10"/>
-      <c r="CL7" s="10"/>
-      <c r="CM7" s="23"/>
-      <c r="CN7" s="23"/>
-      <c r="CO7" s="13"/>
-      <c r="CP7" s="17"/>
-      <c r="CQ7" s="39"/>
-      <c r="CR7" s="10"/>
-      <c r="CS7" s="10"/>
-      <c r="CT7" s="10"/>
-      <c r="CU7" s="10"/>
-      <c r="CV7" s="10"/>
-      <c r="CW7" s="10"/>
-      <c r="CX7" s="10"/>
-      <c r="CY7" s="27"/>
-      <c r="CZ7" s="27"/>
-      <c r="DA7" s="13"/>
-      <c r="DB7" s="17"/>
-      <c r="DC7" s="39"/>
-      <c r="DD7" s="10"/>
-      <c r="DE7" s="10"/>
-      <c r="DF7" s="10"/>
-      <c r="DG7" s="10"/>
-      <c r="DH7" s="10"/>
-      <c r="DI7" s="10"/>
-      <c r="DJ7" s="10"/>
-      <c r="DK7" s="23"/>
-      <c r="DL7" s="23"/>
-      <c r="DM7" s="14"/>
-      <c r="DN7" s="17"/>
-      <c r="DO7" s="39"/>
-      <c r="DP7" s="10"/>
-      <c r="DQ7" s="10"/>
-      <c r="DR7" s="10"/>
-      <c r="DS7" s="10"/>
-      <c r="DT7" s="10"/>
-      <c r="DU7" s="10"/>
-      <c r="DV7" s="10"/>
-      <c r="DW7" s="23"/>
-      <c r="DX7" s="23"/>
-      <c r="DY7" s="14"/>
-      <c r="DZ7" s="17"/>
-      <c r="EA7" s="39"/>
-      <c r="EB7" s="10"/>
-      <c r="EC7" s="10"/>
-      <c r="ED7" s="10"/>
-      <c r="EE7" s="10"/>
-      <c r="EF7" s="10"/>
-      <c r="EG7" s="10"/>
-      <c r="EH7" s="10"/>
-      <c r="EI7" s="23"/>
-      <c r="EJ7" s="23"/>
-      <c r="EK7" s="14"/>
-      <c r="EL7" s="17"/>
-      <c r="EM7" s="39"/>
-      <c r="EN7" s="10"/>
-      <c r="EO7" s="10"/>
-      <c r="EP7" s="10"/>
-      <c r="EQ7" s="10"/>
-      <c r="ER7" s="10"/>
-      <c r="ES7" s="10"/>
-      <c r="ET7" s="10"/>
-      <c r="EU7" s="23"/>
-      <c r="EV7" s="23"/>
-      <c r="EW7" s="14"/>
-      <c r="EX7" s="17"/>
-      <c r="EY7" s="39"/>
-      <c r="EZ7" s="10"/>
-      <c r="FA7" s="10"/>
-      <c r="FB7" s="10"/>
-      <c r="FC7" s="10"/>
-      <c r="FD7" s="10"/>
-      <c r="FE7" s="10"/>
-      <c r="FF7" s="10"/>
-      <c r="FG7" s="23"/>
-      <c r="FH7" s="23"/>
-      <c r="FI7" s="14"/>
+      <c r="CC7" s="39"/>
+      <c r="CD7" s="37"/>
+      <c r="CE7" s="38"/>
+      <c r="CF7" s="22"/>
+      <c r="CG7" s="22"/>
+      <c r="CH7" s="22"/>
+      <c r="CI7" s="22"/>
+      <c r="CJ7" s="22"/>
+      <c r="CK7" s="22"/>
+      <c r="CL7" s="22"/>
+      <c r="CM7" s="22"/>
+      <c r="CN7" s="22"/>
+      <c r="CO7" s="39"/>
+      <c r="CP7" s="37"/>
+      <c r="CQ7" s="38"/>
+      <c r="CR7" s="22"/>
+      <c r="CS7" s="22"/>
+      <c r="CT7" s="22"/>
+      <c r="CU7" s="22"/>
+      <c r="CV7" s="22"/>
+      <c r="CW7" s="22"/>
+      <c r="CX7" s="22"/>
+      <c r="CY7" s="22"/>
+      <c r="CZ7" s="22"/>
+      <c r="DA7" s="39"/>
+      <c r="DB7" s="37"/>
+      <c r="DC7" s="38"/>
+      <c r="DD7" s="22"/>
+      <c r="DE7" s="22"/>
+      <c r="DF7" s="22"/>
+      <c r="DG7" s="22"/>
+      <c r="DH7" s="22"/>
+      <c r="DI7" s="22"/>
+      <c r="DJ7" s="22"/>
+      <c r="DK7" s="22"/>
+      <c r="DL7" s="22"/>
+      <c r="DM7" s="39"/>
+      <c r="DN7" s="37"/>
+      <c r="DO7" s="38"/>
+      <c r="DP7" s="22"/>
+      <c r="DQ7" s="22"/>
+      <c r="DR7" s="22"/>
+      <c r="DS7" s="22"/>
+      <c r="DT7" s="22"/>
+      <c r="DU7" s="22"/>
+      <c r="DV7" s="22"/>
+      <c r="DW7" s="22"/>
+      <c r="DX7" s="22"/>
+      <c r="DY7" s="39"/>
+      <c r="DZ7" s="37"/>
+      <c r="EA7" s="38"/>
+      <c r="EB7" s="22"/>
+      <c r="EC7" s="22"/>
+      <c r="ED7" s="22"/>
+      <c r="EE7" s="22"/>
+      <c r="EF7" s="22"/>
+      <c r="EG7" s="22"/>
+      <c r="EH7" s="22"/>
+      <c r="EI7" s="22"/>
+      <c r="EJ7" s="22"/>
+      <c r="EK7" s="39"/>
+      <c r="EL7" s="37"/>
+      <c r="EM7" s="38"/>
+      <c r="EN7" s="22"/>
+      <c r="EO7" s="22"/>
+      <c r="EP7" s="22"/>
+      <c r="EQ7" s="22"/>
+      <c r="ER7" s="22"/>
+      <c r="ES7" s="22"/>
+      <c r="ET7" s="22"/>
+      <c r="EU7" s="22"/>
+      <c r="EV7" s="22"/>
+      <c r="EW7" s="39"/>
+      <c r="EX7" s="37"/>
+      <c r="EY7" s="38"/>
+      <c r="EZ7" s="22"/>
+      <c r="FA7" s="22"/>
+      <c r="FB7" s="22"/>
+      <c r="FC7" s="22"/>
+      <c r="FD7" s="22"/>
+      <c r="FE7" s="22"/>
+      <c r="FF7" s="22"/>
+      <c r="FG7" s="22"/>
+      <c r="FH7" s="22"/>
+      <c r="FI7" s="39"/>
     </row>
     <row r="8" spans="1:165" ht="46.15" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="25">
+        <v>40</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="21">
         <v>37.47</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="22">
         <v>0.60232582597250739</v>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="22">
         <v>0.64366221390623002</v>
       </c>
       <c r="G8" s="9">
@@ -5309,192 +4793,72 @@
       <c r="H8" s="9">
         <v>1273.7525479999999</v>
       </c>
-      <c r="I8" s="23">
+      <c r="I8" s="20">
         <f t="shared" si="2"/>
         <v>0.29358798665525127</v>
       </c>
-      <c r="J8" s="17">
-        <v>9</v>
-      </c>
-      <c r="K8" s="42">
-        <v>26.1</v>
-      </c>
-      <c r="L8" s="10">
-        <v>0.64</v>
-      </c>
-      <c r="M8" s="22">
-        <v>21.5</v>
-      </c>
-      <c r="N8" s="22">
-        <v>33.4</v>
-      </c>
-      <c r="O8" s="22">
-        <v>44.1</v>
-      </c>
-      <c r="P8" s="22">
-        <v>58.5</v>
-      </c>
-      <c r="Q8" s="22">
-        <v>69.7</v>
-      </c>
-      <c r="R8" s="22">
-        <v>81.3</v>
-      </c>
-      <c r="S8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="V8" s="17">
-        <v>9</v>
-      </c>
-      <c r="W8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="X8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH8" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI8" s="39">
-        <v>37.47</v>
-      </c>
-      <c r="AJ8" s="39">
-        <v>0.64</v>
-      </c>
-      <c r="AK8" s="39">
-        <v>25.09</v>
-      </c>
-      <c r="AL8" s="39">
-        <v>38.72</v>
-      </c>
-      <c r="AM8" s="39">
-        <v>50.92</v>
-      </c>
-      <c r="AN8" s="39">
-        <v>67.38</v>
-      </c>
-      <c r="AO8" s="39">
-        <v>80.03</v>
-      </c>
-      <c r="AP8" s="39">
-        <v>93.070000000000007</v>
-      </c>
-      <c r="AQ8" s="39">
-        <v>1520.8459760000001</v>
-      </c>
-      <c r="AR8" s="39">
-        <v>1273.7525479999999</v>
-      </c>
-      <c r="AS8" s="39">
-        <v>0.29358798665525127</v>
-      </c>
-      <c r="AT8" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU8" s="39">
-        <v>225.36</v>
-      </c>
-      <c r="AV8" s="39">
-        <v>0.64</v>
-      </c>
-      <c r="AW8" s="39">
-        <v>25.31</v>
-      </c>
-      <c r="AX8" s="39">
-        <v>39.04</v>
-      </c>
-      <c r="AY8" s="39">
-        <v>51.31</v>
-      </c>
-      <c r="AZ8" s="39">
-        <v>67.86</v>
-      </c>
-      <c r="BA8" s="39">
-        <v>80.61</v>
-      </c>
-      <c r="BB8" s="39">
-        <v>93.71</v>
-      </c>
-      <c r="BC8" s="39">
-        <v>1520.85</v>
-      </c>
-      <c r="BD8" s="39">
-        <v>1273.75</v>
-      </c>
-      <c r="BE8" s="14">
-        <v>1.77</v>
-      </c>
-      <c r="BF8" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BM8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BQ8" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="BR8" s="17"/>
-      <c r="BS8" s="39"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="22"/>
+      <c r="S8" s="22"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="39"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="38"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="22"/>
+      <c r="AA8" s="22"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="22"/>
+      <c r="AE8" s="22"/>
+      <c r="AF8" s="22"/>
+      <c r="AG8" s="39"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="38"/>
+      <c r="AJ8" s="22"/>
+      <c r="AK8" s="22"/>
+      <c r="AL8" s="22"/>
+      <c r="AM8" s="22"/>
+      <c r="AN8" s="22"/>
+      <c r="AO8" s="22"/>
+      <c r="AP8" s="22"/>
+      <c r="AQ8" s="22"/>
+      <c r="AR8" s="22"/>
+      <c r="AS8" s="39"/>
+      <c r="AT8" s="37"/>
+      <c r="AU8" s="38"/>
+      <c r="AV8" s="22"/>
+      <c r="AW8" s="22"/>
+      <c r="AX8" s="22"/>
+      <c r="AY8" s="22"/>
+      <c r="AZ8" s="22"/>
+      <c r="BA8" s="22"/>
+      <c r="BB8" s="22"/>
+      <c r="BC8" s="22"/>
+      <c r="BD8" s="22"/>
+      <c r="BE8" s="39"/>
+      <c r="BF8" s="37"/>
+      <c r="BG8" s="38"/>
+      <c r="BH8" s="22"/>
+      <c r="BI8" s="22"/>
+      <c r="BJ8" s="22"/>
+      <c r="BK8" s="22"/>
+      <c r="BL8" s="22"/>
+      <c r="BM8" s="22"/>
+      <c r="BN8" s="22"/>
+      <c r="BO8" s="22"/>
+      <c r="BP8" s="22"/>
+      <c r="BQ8" s="39"/>
+      <c r="BR8" s="37"/>
+      <c r="BS8" s="38"/>
       <c r="BT8" s="22"/>
       <c r="BU8" s="22"/>
       <c r="BV8" s="22"/>
@@ -5504,100 +4868,100 @@
       <c r="BZ8" s="22"/>
       <c r="CA8" s="22"/>
       <c r="CB8" s="22"/>
-      <c r="CC8" s="13"/>
-      <c r="CD8" s="17"/>
-      <c r="CE8" s="42"/>
-      <c r="CF8" s="10"/>
-      <c r="CG8" s="10"/>
-      <c r="CH8" s="10"/>
-      <c r="CI8" s="10"/>
-      <c r="CJ8" s="10"/>
-      <c r="CK8" s="10"/>
-      <c r="CL8" s="10"/>
-      <c r="CM8" s="23"/>
-      <c r="CN8" s="23"/>
-      <c r="CO8" s="13"/>
-      <c r="CP8" s="17"/>
-      <c r="CQ8" s="39"/>
+      <c r="CC8" s="39"/>
+      <c r="CD8" s="37"/>
+      <c r="CE8" s="38"/>
+      <c r="CF8" s="22"/>
+      <c r="CG8" s="22"/>
+      <c r="CH8" s="22"/>
+      <c r="CI8" s="22"/>
+      <c r="CJ8" s="22"/>
+      <c r="CK8" s="22"/>
+      <c r="CL8" s="22"/>
+      <c r="CM8" s="22"/>
+      <c r="CN8" s="22"/>
+      <c r="CO8" s="39"/>
+      <c r="CP8" s="37"/>
+      <c r="CQ8" s="38"/>
       <c r="CR8" s="22"/>
-      <c r="CS8" s="10"/>
-      <c r="CT8" s="10"/>
-      <c r="CU8" s="10"/>
-      <c r="CV8" s="10"/>
-      <c r="CW8" s="10"/>
-      <c r="CX8" s="10"/>
-      <c r="CY8" s="27"/>
-      <c r="CZ8" s="27"/>
-      <c r="DA8" s="13"/>
-      <c r="DB8" s="17"/>
-      <c r="DC8" s="39"/>
-      <c r="DD8" s="10"/>
-      <c r="DE8" s="10"/>
-      <c r="DF8" s="10"/>
-      <c r="DG8" s="10"/>
-      <c r="DH8" s="10"/>
-      <c r="DI8" s="10"/>
-      <c r="DJ8" s="10"/>
-      <c r="DK8" s="23"/>
-      <c r="DL8" s="23"/>
-      <c r="DM8" s="14"/>
-      <c r="DN8" s="17"/>
-      <c r="DO8" s="39"/>
-      <c r="DP8" s="10"/>
-      <c r="DQ8" s="10"/>
-      <c r="DR8" s="10"/>
-      <c r="DS8" s="10"/>
-      <c r="DT8" s="10"/>
-      <c r="DU8" s="10"/>
-      <c r="DV8" s="10"/>
-      <c r="DW8" s="23"/>
-      <c r="DX8" s="23"/>
-      <c r="DY8" s="14"/>
-      <c r="DZ8" s="17"/>
-      <c r="EA8" s="39"/>
-      <c r="EB8" s="10"/>
-      <c r="EC8" s="10"/>
-      <c r="ED8" s="10"/>
-      <c r="EE8" s="10"/>
-      <c r="EF8" s="10"/>
-      <c r="EG8" s="10"/>
-      <c r="EH8" s="10"/>
-      <c r="EI8" s="23"/>
-      <c r="EJ8" s="23"/>
-      <c r="EK8" s="14"/>
-      <c r="EL8" s="17"/>
-      <c r="EM8" s="39"/>
-      <c r="EN8" s="10"/>
-      <c r="EO8" s="10"/>
-      <c r="EP8" s="10"/>
-      <c r="EQ8" s="10"/>
-      <c r="ER8" s="10"/>
-      <c r="ES8" s="10"/>
-      <c r="ET8" s="10"/>
-      <c r="EU8" s="23"/>
-      <c r="EV8" s="23"/>
-      <c r="EW8" s="14"/>
-      <c r="EX8" s="17"/>
-      <c r="EY8" s="39"/>
-      <c r="EZ8" s="10"/>
-      <c r="FA8" s="10"/>
-      <c r="FB8" s="10"/>
-      <c r="FC8" s="10"/>
-      <c r="FD8" s="10"/>
-      <c r="FE8" s="10"/>
-      <c r="FF8" s="10"/>
-      <c r="FG8" s="23"/>
-      <c r="FH8" s="23"/>
-      <c r="FI8" s="14"/>
+      <c r="CS8" s="22"/>
+      <c r="CT8" s="22"/>
+      <c r="CU8" s="22"/>
+      <c r="CV8" s="22"/>
+      <c r="CW8" s="22"/>
+      <c r="CX8" s="22"/>
+      <c r="CY8" s="22"/>
+      <c r="CZ8" s="22"/>
+      <c r="DA8" s="39"/>
+      <c r="DB8" s="37"/>
+      <c r="DC8" s="38"/>
+      <c r="DD8" s="22"/>
+      <c r="DE8" s="22"/>
+      <c r="DF8" s="22"/>
+      <c r="DG8" s="22"/>
+      <c r="DH8" s="22"/>
+      <c r="DI8" s="22"/>
+      <c r="DJ8" s="22"/>
+      <c r="DK8" s="22"/>
+      <c r="DL8" s="22"/>
+      <c r="DM8" s="39"/>
+      <c r="DN8" s="37"/>
+      <c r="DO8" s="38"/>
+      <c r="DP8" s="22"/>
+      <c r="DQ8" s="22"/>
+      <c r="DR8" s="22"/>
+      <c r="DS8" s="22"/>
+      <c r="DT8" s="22"/>
+      <c r="DU8" s="22"/>
+      <c r="DV8" s="22"/>
+      <c r="DW8" s="22"/>
+      <c r="DX8" s="22"/>
+      <c r="DY8" s="39"/>
+      <c r="DZ8" s="37"/>
+      <c r="EA8" s="38"/>
+      <c r="EB8" s="22"/>
+      <c r="EC8" s="22"/>
+      <c r="ED8" s="22"/>
+      <c r="EE8" s="22"/>
+      <c r="EF8" s="22"/>
+      <c r="EG8" s="22"/>
+      <c r="EH8" s="22"/>
+      <c r="EI8" s="22"/>
+      <c r="EJ8" s="22"/>
+      <c r="EK8" s="39"/>
+      <c r="EL8" s="37"/>
+      <c r="EM8" s="38"/>
+      <c r="EN8" s="22"/>
+      <c r="EO8" s="22"/>
+      <c r="EP8" s="22"/>
+      <c r="EQ8" s="22"/>
+      <c r="ER8" s="22"/>
+      <c r="ES8" s="22"/>
+      <c r="ET8" s="22"/>
+      <c r="EU8" s="22"/>
+      <c r="EV8" s="22"/>
+      <c r="EW8" s="39"/>
+      <c r="EX8" s="37"/>
+      <c r="EY8" s="38"/>
+      <c r="EZ8" s="22"/>
+      <c r="FA8" s="22"/>
+      <c r="FB8" s="22"/>
+      <c r="FC8" s="22"/>
+      <c r="FD8" s="22"/>
+      <c r="FE8" s="22"/>
+      <c r="FF8" s="22"/>
+      <c r="FG8" s="22"/>
+      <c r="FH8" s="22"/>
+      <c r="FI8" s="39"/>
     </row>
     <row r="9" spans="1:165" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="21">
         <v>243.1141016</v>
       </c>
       <c r="E9" s="10">
@@ -5614,193 +4978,73 @@
       <c r="H9" s="9">
         <v>1243.210047</v>
       </c>
-      <c r="I9" s="23">
+      <c r="I9" s="20">
         <f t="shared" si="2"/>
         <v>2.0463901158709374</v>
       </c>
-      <c r="J9" s="17">
-        <v>9</v>
-      </c>
-      <c r="K9" s="39">
-        <v>243.11</v>
-      </c>
-      <c r="L9" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="M9" s="10">
-        <v>129</v>
-      </c>
-      <c r="N9" s="10">
-        <v>204.6</v>
-      </c>
-      <c r="O9" s="10">
-        <v>274</v>
-      </c>
-      <c r="P9" s="10">
-        <v>368.5</v>
-      </c>
-      <c r="Q9" s="10">
-        <v>442.9</v>
-      </c>
-      <c r="R9" s="10">
-        <v>520</v>
-      </c>
-      <c r="S9" s="10">
-        <v>1508.6613649999999</v>
-      </c>
-      <c r="T9" s="10">
-        <v>1243.210047</v>
-      </c>
-      <c r="U9" s="14">
-        <v>2.0463555910381777</v>
-      </c>
-      <c r="V9" s="17">
-        <v>9</v>
-      </c>
-      <c r="W9" s="39">
-        <v>243.11</v>
-      </c>
-      <c r="X9" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="Y9" s="10">
-        <v>129.6</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>204.8</v>
-      </c>
-      <c r="AA9" s="10">
-        <v>273.7</v>
-      </c>
-      <c r="AB9" s="10">
-        <v>368.8</v>
-      </c>
-      <c r="AC9" s="10">
-        <v>443.3</v>
-      </c>
-      <c r="AD9" s="10">
-        <v>519.70000000000005</v>
-      </c>
-      <c r="AE9" s="10">
-        <v>1508.6613649999999</v>
-      </c>
-      <c r="AF9" s="10">
-        <v>1243.210047</v>
-      </c>
-      <c r="AG9" s="14">
-        <v>2.0463555910381777</v>
-      </c>
-      <c r="AH9" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI9" s="39">
-        <v>243.11</v>
-      </c>
-      <c r="AJ9" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="AK9" s="10">
-        <v>129.01</v>
-      </c>
-      <c r="AL9" s="10">
-        <v>204.6</v>
-      </c>
-      <c r="AM9" s="10">
-        <v>274.01</v>
-      </c>
-      <c r="AN9" s="10">
-        <v>368.55</v>
-      </c>
-      <c r="AO9" s="10">
-        <v>442.89</v>
-      </c>
-      <c r="AP9" s="10">
-        <v>519.99</v>
-      </c>
-      <c r="AQ9" s="10">
-        <v>1508.66136543323</v>
-      </c>
-      <c r="AR9" s="10">
-        <v>1243.210047</v>
-      </c>
-      <c r="AS9" s="14">
-        <v>2.0463555943779346</v>
-      </c>
-      <c r="AT9" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU9" s="39">
-        <v>243.11</v>
-      </c>
-      <c r="AV9" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="AW9" s="10">
-        <v>130.32</v>
-      </c>
-      <c r="AX9" s="10">
-        <v>206.49</v>
-      </c>
-      <c r="AY9" s="10">
-        <v>276.41000000000003</v>
-      </c>
-      <c r="AZ9" s="10">
-        <v>371.55</v>
-      </c>
-      <c r="BA9" s="10">
-        <v>446.36</v>
-      </c>
-      <c r="BB9" s="10">
-        <v>523.91</v>
-      </c>
-      <c r="BC9" s="39">
-        <v>1508.66</v>
-      </c>
-      <c r="BD9" s="39">
-        <v>1243.21</v>
-      </c>
-      <c r="BE9" s="39">
-        <v>2.0499999999999998</v>
-      </c>
-      <c r="BF9" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG9" s="10">
-        <v>243.1141016</v>
-      </c>
-      <c r="BH9" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="BI9" s="10">
-        <v>129.6</v>
-      </c>
-      <c r="BJ9" s="10">
-        <v>204.8</v>
-      </c>
-      <c r="BK9" s="10">
-        <v>273.7</v>
-      </c>
-      <c r="BL9" s="10">
-        <v>368.8</v>
-      </c>
-      <c r="BM9" s="10">
-        <v>443.3</v>
-      </c>
-      <c r="BN9" s="10">
-        <v>519.70000000000005</v>
-      </c>
-      <c r="BO9" s="10">
-        <v>1508.66136543323</v>
-      </c>
-      <c r="BP9" s="10">
-        <v>1243.210047</v>
-      </c>
-      <c r="BQ9" s="14">
-        <v>2.0463901192107503</v>
-      </c>
-      <c r="BR9" s="17"/>
-      <c r="BS9" s="39"/>
-      <c r="BT9" s="10"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="22"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="22"/>
+      <c r="S9" s="22"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="39"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="22"/>
+      <c r="AA9" s="22"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="22"/>
+      <c r="AE9" s="22"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="39"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="22"/>
+      <c r="AM9" s="22"/>
+      <c r="AN9" s="22"/>
+      <c r="AO9" s="22"/>
+      <c r="AP9" s="22"/>
+      <c r="AQ9" s="22"/>
+      <c r="AR9" s="22"/>
+      <c r="AS9" s="39"/>
+      <c r="AT9" s="37"/>
+      <c r="AU9" s="38"/>
+      <c r="AV9" s="22"/>
+      <c r="AW9" s="22"/>
+      <c r="AX9" s="22"/>
+      <c r="AY9" s="22"/>
+      <c r="AZ9" s="22"/>
+      <c r="BA9" s="22"/>
+      <c r="BB9" s="22"/>
+      <c r="BC9" s="22"/>
+      <c r="BD9" s="22"/>
+      <c r="BE9" s="39"/>
+      <c r="BF9" s="37"/>
+      <c r="BG9" s="38"/>
+      <c r="BH9" s="22"/>
+      <c r="BI9" s="22"/>
+      <c r="BJ9" s="22"/>
+      <c r="BK9" s="22"/>
+      <c r="BL9" s="22"/>
+      <c r="BM9" s="22"/>
+      <c r="BN9" s="22"/>
+      <c r="BO9" s="22"/>
+      <c r="BP9" s="22"/>
+      <c r="BQ9" s="39"/>
+      <c r="BR9" s="37"/>
+      <c r="BS9" s="38"/>
+      <c r="BT9" s="22"/>
       <c r="BU9" s="22"/>
       <c r="BV9" s="22"/>
       <c r="BW9" s="22"/>
@@ -5809,100 +5053,100 @@
       <c r="BZ9" s="22"/>
       <c r="CA9" s="22"/>
       <c r="CB9" s="22"/>
-      <c r="CC9" s="13"/>
-      <c r="CD9" s="17"/>
-      <c r="CE9" s="39"/>
-      <c r="CF9" s="10"/>
-      <c r="CG9" s="10"/>
-      <c r="CH9" s="10"/>
-      <c r="CI9" s="10"/>
-      <c r="CJ9" s="10"/>
-      <c r="CK9" s="10"/>
-      <c r="CL9" s="10"/>
-      <c r="CM9" s="23"/>
-      <c r="CN9" s="23"/>
-      <c r="CO9" s="14"/>
-      <c r="CP9" s="17"/>
-      <c r="CQ9" s="39"/>
-      <c r="CR9" s="10"/>
-      <c r="CS9" s="10"/>
-      <c r="CT9" s="10"/>
-      <c r="CU9" s="10"/>
-      <c r="CV9" s="10"/>
-      <c r="CW9" s="10"/>
-      <c r="CX9" s="10"/>
-      <c r="CY9" s="27"/>
-      <c r="CZ9" s="27"/>
-      <c r="DA9" s="13"/>
-      <c r="DB9" s="17"/>
-      <c r="DC9" s="39"/>
-      <c r="DD9" s="10"/>
-      <c r="DE9" s="10"/>
-      <c r="DF9" s="10"/>
-      <c r="DG9" s="10"/>
-      <c r="DH9" s="10"/>
-      <c r="DI9" s="10"/>
-      <c r="DJ9" s="10"/>
-      <c r="DK9" s="23"/>
-      <c r="DL9" s="23"/>
-      <c r="DM9" s="14"/>
-      <c r="DN9" s="17"/>
-      <c r="DO9" s="39"/>
-      <c r="DP9" s="10"/>
-      <c r="DQ9" s="10"/>
-      <c r="DR9" s="10"/>
-      <c r="DS9" s="10"/>
-      <c r="DT9" s="10"/>
-      <c r="DU9" s="10"/>
-      <c r="DV9" s="10"/>
-      <c r="DW9" s="23"/>
-      <c r="DX9" s="23"/>
-      <c r="DY9" s="14"/>
-      <c r="DZ9" s="17"/>
-      <c r="EA9" s="39"/>
-      <c r="EB9" s="10"/>
-      <c r="EC9" s="10"/>
-      <c r="ED9" s="10"/>
-      <c r="EE9" s="10"/>
-      <c r="EF9" s="10"/>
-      <c r="EG9" s="10"/>
-      <c r="EH9" s="10"/>
-      <c r="EI9" s="23"/>
-      <c r="EJ9" s="23"/>
-      <c r="EK9" s="14"/>
-      <c r="EL9" s="17"/>
-      <c r="EM9" s="39"/>
-      <c r="EN9" s="10"/>
-      <c r="EO9" s="10"/>
-      <c r="EP9" s="10"/>
-      <c r="EQ9" s="10"/>
-      <c r="ER9" s="10"/>
-      <c r="ES9" s="10"/>
-      <c r="ET9" s="10"/>
-      <c r="EU9" s="23"/>
-      <c r="EV9" s="23"/>
-      <c r="EW9" s="14"/>
-      <c r="EX9" s="17"/>
-      <c r="EY9" s="39"/>
-      <c r="EZ9" s="10"/>
-      <c r="FA9" s="10"/>
-      <c r="FB9" s="10"/>
-      <c r="FC9" s="10"/>
-      <c r="FD9" s="10"/>
-      <c r="FE9" s="10"/>
-      <c r="FF9" s="10"/>
-      <c r="FG9" s="23"/>
-      <c r="FH9" s="23"/>
-      <c r="FI9" s="14"/>
+      <c r="CC9" s="39"/>
+      <c r="CD9" s="37"/>
+      <c r="CE9" s="38"/>
+      <c r="CF9" s="22"/>
+      <c r="CG9" s="22"/>
+      <c r="CH9" s="22"/>
+      <c r="CI9" s="22"/>
+      <c r="CJ9" s="22"/>
+      <c r="CK9" s="22"/>
+      <c r="CL9" s="22"/>
+      <c r="CM9" s="22"/>
+      <c r="CN9" s="22"/>
+      <c r="CO9" s="39"/>
+      <c r="CP9" s="37"/>
+      <c r="CQ9" s="38"/>
+      <c r="CR9" s="22"/>
+      <c r="CS9" s="22"/>
+      <c r="CT9" s="22"/>
+      <c r="CU9" s="22"/>
+      <c r="CV9" s="22"/>
+      <c r="CW9" s="22"/>
+      <c r="CX9" s="22"/>
+      <c r="CY9" s="22"/>
+      <c r="CZ9" s="22"/>
+      <c r="DA9" s="39"/>
+      <c r="DB9" s="37"/>
+      <c r="DC9" s="38"/>
+      <c r="DD9" s="22"/>
+      <c r="DE9" s="22"/>
+      <c r="DF9" s="22"/>
+      <c r="DG9" s="22"/>
+      <c r="DH9" s="22"/>
+      <c r="DI9" s="22"/>
+      <c r="DJ9" s="22"/>
+      <c r="DK9" s="22"/>
+      <c r="DL9" s="22"/>
+      <c r="DM9" s="39"/>
+      <c r="DN9" s="37"/>
+      <c r="DO9" s="38"/>
+      <c r="DP9" s="22"/>
+      <c r="DQ9" s="22"/>
+      <c r="DR9" s="22"/>
+      <c r="DS9" s="22"/>
+      <c r="DT9" s="22"/>
+      <c r="DU9" s="22"/>
+      <c r="DV9" s="22"/>
+      <c r="DW9" s="22"/>
+      <c r="DX9" s="22"/>
+      <c r="DY9" s="39"/>
+      <c r="DZ9" s="37"/>
+      <c r="EA9" s="38"/>
+      <c r="EB9" s="22"/>
+      <c r="EC9" s="22"/>
+      <c r="ED9" s="22"/>
+      <c r="EE9" s="22"/>
+      <c r="EF9" s="22"/>
+      <c r="EG9" s="22"/>
+      <c r="EH9" s="22"/>
+      <c r="EI9" s="22"/>
+      <c r="EJ9" s="22"/>
+      <c r="EK9" s="39"/>
+      <c r="EL9" s="37"/>
+      <c r="EM9" s="38"/>
+      <c r="EN9" s="22"/>
+      <c r="EO9" s="22"/>
+      <c r="EP9" s="22"/>
+      <c r="EQ9" s="22"/>
+      <c r="ER9" s="22"/>
+      <c r="ES9" s="22"/>
+      <c r="ET9" s="22"/>
+      <c r="EU9" s="22"/>
+      <c r="EV9" s="22"/>
+      <c r="EW9" s="39"/>
+      <c r="EX9" s="37"/>
+      <c r="EY9" s="38"/>
+      <c r="EZ9" s="22"/>
+      <c r="FA9" s="22"/>
+      <c r="FB9" s="22"/>
+      <c r="FC9" s="22"/>
+      <c r="FD9" s="22"/>
+      <c r="FE9" s="22"/>
+      <c r="FF9" s="22"/>
+      <c r="FG9" s="22"/>
+      <c r="FH9" s="22"/>
+      <c r="FI9" s="39"/>
     </row>
     <row r="10" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="25">
+      <c r="C10" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="21">
         <v>15.195</v>
       </c>
       <c r="E10" s="10">
@@ -5919,193 +5163,73 @@
       <c r="H10" s="9">
         <v>1285.808869</v>
       </c>
-      <c r="I10" s="23">
+      <c r="I10" s="20">
         <f t="shared" si="2"/>
         <v>0.11204452683266743</v>
       </c>
-      <c r="J10" s="17">
-        <v>9</v>
-      </c>
-      <c r="K10" s="39">
-        <v>15.195</v>
-      </c>
-      <c r="L10" s="10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="10">
-        <v>42</v>
-      </c>
-      <c r="N10" s="10">
-        <v>59.5</v>
-      </c>
-      <c r="O10" s="10">
-        <v>74.2</v>
-      </c>
-      <c r="P10" s="10">
-        <v>93.3</v>
-      </c>
-      <c r="Q10" s="10">
-        <v>107.7</v>
-      </c>
-      <c r="R10" s="10">
-        <v>122.2</v>
-      </c>
-      <c r="S10" s="10">
-        <v>1518.34827</v>
-      </c>
-      <c r="T10" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="U10" s="14">
-        <v>0.11204452683266743</v>
-      </c>
-      <c r="V10" s="17">
-        <v>9</v>
-      </c>
-      <c r="W10" s="39">
-        <v>15.195</v>
-      </c>
-      <c r="X10" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="10">
-        <v>42</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>59.5</v>
-      </c>
-      <c r="AA10" s="10">
-        <v>74.2</v>
-      </c>
-      <c r="AB10" s="10">
-        <v>93.3</v>
-      </c>
-      <c r="AC10" s="10">
-        <v>107.7</v>
-      </c>
-      <c r="AD10" s="10">
-        <v>122.2</v>
-      </c>
-      <c r="AE10" s="10">
-        <v>1518.35</v>
-      </c>
-      <c r="AF10" s="10">
-        <v>1285.81</v>
-      </c>
-      <c r="AG10" s="14">
-        <v>0.11</v>
-      </c>
-      <c r="AH10" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI10" s="39">
-        <v>15.195</v>
-      </c>
-      <c r="AJ10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK10" s="10">
-        <v>41.96</v>
-      </c>
-      <c r="AL10" s="10">
-        <v>59.49</v>
-      </c>
-      <c r="AM10" s="10">
-        <v>74.209999999999994</v>
-      </c>
-      <c r="AN10" s="10">
-        <v>93.34</v>
-      </c>
-      <c r="AO10" s="10">
-        <v>107.72</v>
-      </c>
-      <c r="AP10" s="10">
-        <v>122.17</v>
-      </c>
-      <c r="AQ10" s="10">
-        <v>1518.34826973808</v>
-      </c>
-      <c r="AR10" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="AS10" s="14">
-        <v>0.11204452670646647</v>
-      </c>
-      <c r="AT10" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU10" s="39">
-        <v>15.2</v>
-      </c>
-      <c r="AV10" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW10" s="10">
-        <v>42.26</v>
-      </c>
-      <c r="AX10" s="10">
-        <v>59.87</v>
-      </c>
-      <c r="AY10" s="10">
-        <v>74.67</v>
-      </c>
-      <c r="AZ10" s="10">
-        <v>93.87</v>
-      </c>
-      <c r="BA10" s="10">
-        <v>108.34</v>
-      </c>
-      <c r="BB10" s="10">
-        <v>122.86</v>
-      </c>
-      <c r="BC10" s="10">
-        <v>1518.35</v>
-      </c>
-      <c r="BD10" s="10">
-        <v>1285.81</v>
-      </c>
-      <c r="BE10" s="14">
-        <v>0.11</v>
-      </c>
-      <c r="BF10" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG10" s="10">
-        <v>15.195</v>
-      </c>
-      <c r="BH10" s="10">
-        <v>1</v>
-      </c>
-      <c r="BI10" s="10">
-        <v>42</v>
-      </c>
-      <c r="BJ10" s="10">
-        <v>59.5</v>
-      </c>
-      <c r="BK10" s="10">
-        <v>74.2</v>
-      </c>
-      <c r="BL10" s="10">
-        <v>93.3</v>
-      </c>
-      <c r="BM10" s="10">
-        <v>107.7</v>
-      </c>
-      <c r="BN10" s="10">
-        <v>122.2</v>
-      </c>
-      <c r="BO10" s="10">
-        <v>1518.34827</v>
-      </c>
-      <c r="BP10" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="BQ10" s="14">
-        <v>0.11204452683266743</v>
-      </c>
-      <c r="BR10" s="17"/>
-      <c r="BS10" s="39"/>
-      <c r="BT10" s="10"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="38"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="22"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="22"/>
+      <c r="S10" s="22"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="39"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="38"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="22"/>
+      <c r="AA10" s="22"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="22"/>
+      <c r="AE10" s="22"/>
+      <c r="AF10" s="22"/>
+      <c r="AG10" s="39"/>
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="38"/>
+      <c r="AJ10" s="22"/>
+      <c r="AK10" s="22"/>
+      <c r="AL10" s="22"/>
+      <c r="AM10" s="22"/>
+      <c r="AN10" s="22"/>
+      <c r="AO10" s="22"/>
+      <c r="AP10" s="22"/>
+      <c r="AQ10" s="22"/>
+      <c r="AR10" s="22"/>
+      <c r="AS10" s="39"/>
+      <c r="AT10" s="37"/>
+      <c r="AU10" s="38"/>
+      <c r="AV10" s="22"/>
+      <c r="AW10" s="22"/>
+      <c r="AX10" s="22"/>
+      <c r="AY10" s="22"/>
+      <c r="AZ10" s="22"/>
+      <c r="BA10" s="22"/>
+      <c r="BB10" s="22"/>
+      <c r="BC10" s="22"/>
+      <c r="BD10" s="22"/>
+      <c r="BE10" s="39"/>
+      <c r="BF10" s="37"/>
+      <c r="BG10" s="38"/>
+      <c r="BH10" s="22"/>
+      <c r="BI10" s="22"/>
+      <c r="BJ10" s="22"/>
+      <c r="BK10" s="22"/>
+      <c r="BL10" s="22"/>
+      <c r="BM10" s="22"/>
+      <c r="BN10" s="22"/>
+      <c r="BO10" s="22"/>
+      <c r="BP10" s="22"/>
+      <c r="BQ10" s="39"/>
+      <c r="BR10" s="37"/>
+      <c r="BS10" s="38"/>
+      <c r="BT10" s="22"/>
       <c r="BU10" s="22"/>
       <c r="BV10" s="22"/>
       <c r="BW10" s="22"/>
@@ -6114,106 +5238,106 @@
       <c r="BZ10" s="22"/>
       <c r="CA10" s="22"/>
       <c r="CB10" s="22"/>
-      <c r="CC10" s="13"/>
-      <c r="CD10" s="17"/>
-      <c r="CE10" s="39"/>
-      <c r="CF10" s="10"/>
-      <c r="CG10" s="10"/>
-      <c r="CH10" s="10"/>
-      <c r="CI10" s="10"/>
-      <c r="CJ10" s="10"/>
-      <c r="CK10" s="10"/>
-      <c r="CL10" s="10"/>
-      <c r="CM10" s="23"/>
-      <c r="CN10" s="23"/>
-      <c r="CO10" s="14"/>
-      <c r="CP10" s="17"/>
-      <c r="CQ10" s="39"/>
-      <c r="CR10" s="10"/>
-      <c r="CS10" s="10"/>
-      <c r="CT10" s="10"/>
-      <c r="CU10" s="10"/>
-      <c r="CV10" s="10"/>
-      <c r="CW10" s="10"/>
-      <c r="CX10" s="10"/>
-      <c r="CY10" s="27"/>
-      <c r="CZ10" s="27"/>
-      <c r="DA10" s="13"/>
-      <c r="DB10" s="17"/>
-      <c r="DC10" s="39"/>
-      <c r="DD10" s="10"/>
-      <c r="DE10" s="10"/>
-      <c r="DF10" s="10"/>
-      <c r="DG10" s="10"/>
-      <c r="DH10" s="10"/>
-      <c r="DI10" s="10"/>
-      <c r="DJ10" s="10"/>
-      <c r="DK10" s="23"/>
-      <c r="DL10" s="23"/>
-      <c r="DM10" s="14"/>
-      <c r="DN10" s="17"/>
-      <c r="DO10" s="39"/>
-      <c r="DP10" s="10"/>
-      <c r="DQ10" s="10"/>
-      <c r="DR10" s="10"/>
-      <c r="DS10" s="10"/>
-      <c r="DT10" s="10"/>
-      <c r="DU10" s="10"/>
-      <c r="DV10" s="10"/>
-      <c r="DW10" s="23"/>
-      <c r="DX10" s="23"/>
-      <c r="DY10" s="14"/>
-      <c r="DZ10" s="17"/>
-      <c r="EA10" s="39"/>
-      <c r="EB10" s="10"/>
-      <c r="EC10" s="10"/>
-      <c r="ED10" s="10"/>
-      <c r="EE10" s="10"/>
-      <c r="EF10" s="10"/>
-      <c r="EG10" s="10"/>
-      <c r="EH10" s="10"/>
-      <c r="EI10" s="23"/>
-      <c r="EJ10" s="23"/>
-      <c r="EK10" s="14"/>
-      <c r="EL10" s="17"/>
-      <c r="EM10" s="39"/>
-      <c r="EN10" s="10"/>
-      <c r="EO10" s="10"/>
-      <c r="EP10" s="10"/>
-      <c r="EQ10" s="10"/>
-      <c r="ER10" s="10"/>
-      <c r="ES10" s="10"/>
-      <c r="ET10" s="10"/>
-      <c r="EU10" s="23"/>
-      <c r="EV10" s="23"/>
-      <c r="EW10" s="14"/>
-      <c r="EX10" s="17"/>
-      <c r="EY10" s="39"/>
-      <c r="EZ10" s="10"/>
-      <c r="FA10" s="10"/>
-      <c r="FB10" s="10"/>
-      <c r="FC10" s="10"/>
-      <c r="FD10" s="10"/>
-      <c r="FE10" s="10"/>
-      <c r="FF10" s="10"/>
-      <c r="FG10" s="23"/>
-      <c r="FH10" s="23"/>
-      <c r="FI10" s="14"/>
+      <c r="CC10" s="39"/>
+      <c r="CD10" s="37"/>
+      <c r="CE10" s="38"/>
+      <c r="CF10" s="22"/>
+      <c r="CG10" s="22"/>
+      <c r="CH10" s="22"/>
+      <c r="CI10" s="22"/>
+      <c r="CJ10" s="22"/>
+      <c r="CK10" s="22"/>
+      <c r="CL10" s="22"/>
+      <c r="CM10" s="22"/>
+      <c r="CN10" s="22"/>
+      <c r="CO10" s="39"/>
+      <c r="CP10" s="37"/>
+      <c r="CQ10" s="38"/>
+      <c r="CR10" s="22"/>
+      <c r="CS10" s="22"/>
+      <c r="CT10" s="22"/>
+      <c r="CU10" s="22"/>
+      <c r="CV10" s="22"/>
+      <c r="CW10" s="22"/>
+      <c r="CX10" s="22"/>
+      <c r="CY10" s="22"/>
+      <c r="CZ10" s="22"/>
+      <c r="DA10" s="39"/>
+      <c r="DB10" s="37"/>
+      <c r="DC10" s="38"/>
+      <c r="DD10" s="22"/>
+      <c r="DE10" s="22"/>
+      <c r="DF10" s="22"/>
+      <c r="DG10" s="22"/>
+      <c r="DH10" s="22"/>
+      <c r="DI10" s="22"/>
+      <c r="DJ10" s="22"/>
+      <c r="DK10" s="22"/>
+      <c r="DL10" s="22"/>
+      <c r="DM10" s="39"/>
+      <c r="DN10" s="37"/>
+      <c r="DO10" s="38"/>
+      <c r="DP10" s="22"/>
+      <c r="DQ10" s="22"/>
+      <c r="DR10" s="22"/>
+      <c r="DS10" s="22"/>
+      <c r="DT10" s="22"/>
+      <c r="DU10" s="22"/>
+      <c r="DV10" s="22"/>
+      <c r="DW10" s="22"/>
+      <c r="DX10" s="22"/>
+      <c r="DY10" s="39"/>
+      <c r="DZ10" s="37"/>
+      <c r="EA10" s="38"/>
+      <c r="EB10" s="22"/>
+      <c r="EC10" s="22"/>
+      <c r="ED10" s="22"/>
+      <c r="EE10" s="22"/>
+      <c r="EF10" s="22"/>
+      <c r="EG10" s="22"/>
+      <c r="EH10" s="22"/>
+      <c r="EI10" s="22"/>
+      <c r="EJ10" s="22"/>
+      <c r="EK10" s="39"/>
+      <c r="EL10" s="37"/>
+      <c r="EM10" s="38"/>
+      <c r="EN10" s="22"/>
+      <c r="EO10" s="22"/>
+      <c r="EP10" s="22"/>
+      <c r="EQ10" s="22"/>
+      <c r="ER10" s="22"/>
+      <c r="ES10" s="22"/>
+      <c r="ET10" s="22"/>
+      <c r="EU10" s="22"/>
+      <c r="EV10" s="22"/>
+      <c r="EW10" s="39"/>
+      <c r="EX10" s="37"/>
+      <c r="EY10" s="38"/>
+      <c r="EZ10" s="22"/>
+      <c r="FA10" s="22"/>
+      <c r="FB10" s="22"/>
+      <c r="FC10" s="22"/>
+      <c r="FD10" s="22"/>
+      <c r="FE10" s="22"/>
+      <c r="FF10" s="22"/>
+      <c r="FG10" s="22"/>
+      <c r="FH10" s="22"/>
+      <c r="FI10" s="39"/>
     </row>
     <row r="11" spans="1:165" ht="33" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="25">
+      <c r="C11" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="21">
         <v>15.195</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="22">
         <v>0.59070732800410519</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="22">
         <v>0.63282037249019918</v>
       </c>
       <c r="G11" s="9">
@@ -6222,193 +5346,73 @@
       <c r="H11" s="9">
         <v>1285.808869</v>
       </c>
-      <c r="I11" s="23">
+      <c r="I11" s="20">
         <f t="shared" si="2"/>
         <v>0.11204452683266743</v>
       </c>
-      <c r="J11" s="17">
-        <v>9</v>
-      </c>
-      <c r="K11" s="39">
-        <v>15.195</v>
-      </c>
-      <c r="L11" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="M11" s="10">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="N11" s="10">
-        <v>29.1</v>
-      </c>
-      <c r="O11" s="10">
-        <v>37.4</v>
-      </c>
-      <c r="P11" s="10">
-        <v>48.5</v>
-      </c>
-      <c r="Q11" s="10">
-        <v>57</v>
-      </c>
-      <c r="R11" s="10">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="S11" s="10">
-        <v>1518.34827</v>
-      </c>
-      <c r="T11" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="U11" s="14">
-        <v>0.11204452683266743</v>
-      </c>
-      <c r="V11" s="17">
-        <v>9</v>
-      </c>
-      <c r="W11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="X11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Y11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="Z11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AA11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AB11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AF11" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AG11" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="AH11" s="17">
-        <v>9</v>
-      </c>
-      <c r="AI11" s="39">
-        <v>15.195</v>
-      </c>
-      <c r="AJ11" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="AK11" s="10">
-        <v>19.37</v>
-      </c>
-      <c r="AL11" s="10">
-        <v>29.08</v>
-      </c>
-      <c r="AM11" s="10">
-        <v>37.47</v>
-      </c>
-      <c r="AN11" s="10">
-        <v>48.59</v>
-      </c>
-      <c r="AO11" s="10">
-        <v>57.07</v>
-      </c>
-      <c r="AP11" s="10">
-        <v>65.67</v>
-      </c>
-      <c r="AQ11" s="10">
-        <v>1518.34826973808</v>
-      </c>
-      <c r="AR11" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="AS11" s="14">
-        <v>0.11204452670646647</v>
-      </c>
-      <c r="AT11" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU11" s="39">
-        <v>243.11</v>
-      </c>
-      <c r="AV11" s="39">
-        <v>0.63</v>
-      </c>
-      <c r="AW11" s="39">
-        <v>19.53</v>
-      </c>
-      <c r="AX11" s="39">
-        <v>29.29</v>
-      </c>
-      <c r="AY11" s="39">
-        <v>37.729999999999997</v>
-      </c>
-      <c r="AZ11" s="39">
-        <v>48.9</v>
-      </c>
-      <c r="BA11" s="39">
-        <v>57.44</v>
-      </c>
-      <c r="BB11" s="39">
-        <v>66.09</v>
-      </c>
-      <c r="BC11" s="10">
-        <v>1518.35</v>
-      </c>
-      <c r="BD11" s="10">
-        <v>1285.81</v>
-      </c>
-      <c r="BE11" s="14">
-        <v>1.79</v>
-      </c>
-      <c r="BF11" s="17">
-        <v>9</v>
-      </c>
-      <c r="BG11" s="10">
-        <v>15.195</v>
-      </c>
-      <c r="BH11" s="10">
-        <v>0.63</v>
-      </c>
-      <c r="BI11" s="10">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="BJ11" s="10">
-        <v>29.1</v>
-      </c>
-      <c r="BK11" s="10">
-        <v>37.4</v>
-      </c>
-      <c r="BL11" s="10">
-        <v>48.5</v>
-      </c>
-      <c r="BM11" s="10">
-        <v>57</v>
-      </c>
-      <c r="BN11" s="10">
-        <v>65.599999999999994</v>
-      </c>
-      <c r="BO11" s="10">
-        <v>1518.34827</v>
-      </c>
-      <c r="BP11" s="10">
-        <v>1285.808869</v>
-      </c>
-      <c r="BQ11" s="14">
-        <v>0.11204452683266743</v>
-      </c>
-      <c r="BR11" s="17"/>
-      <c r="BS11" s="39"/>
-      <c r="BT11" s="10"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="38"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="22"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="22"/>
+      <c r="S11" s="22"/>
+      <c r="T11" s="22"/>
+      <c r="U11" s="39"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="38"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="22"/>
+      <c r="AA11" s="22"/>
+      <c r="AB11" s="22"/>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="22"/>
+      <c r="AE11" s="22"/>
+      <c r="AF11" s="22"/>
+      <c r="AG11" s="39"/>
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="38"/>
+      <c r="AJ11" s="22"/>
+      <c r="AK11" s="22"/>
+      <c r="AL11" s="22"/>
+      <c r="AM11" s="22"/>
+      <c r="AN11" s="22"/>
+      <c r="AO11" s="22"/>
+      <c r="AP11" s="22"/>
+      <c r="AQ11" s="22"/>
+      <c r="AR11" s="22"/>
+      <c r="AS11" s="39"/>
+      <c r="AT11" s="37"/>
+      <c r="AU11" s="38"/>
+      <c r="AV11" s="22"/>
+      <c r="AW11" s="22"/>
+      <c r="AX11" s="22"/>
+      <c r="AY11" s="22"/>
+      <c r="AZ11" s="22"/>
+      <c r="BA11" s="22"/>
+      <c r="BB11" s="22"/>
+      <c r="BC11" s="22"/>
+      <c r="BD11" s="22"/>
+      <c r="BE11" s="39"/>
+      <c r="BF11" s="37"/>
+      <c r="BG11" s="38"/>
+      <c r="BH11" s="22"/>
+      <c r="BI11" s="22"/>
+      <c r="BJ11" s="22"/>
+      <c r="BK11" s="22"/>
+      <c r="BL11" s="22"/>
+      <c r="BM11" s="22"/>
+      <c r="BN11" s="22"/>
+      <c r="BO11" s="22"/>
+      <c r="BP11" s="22"/>
+      <c r="BQ11" s="39"/>
+      <c r="BR11" s="37"/>
+      <c r="BS11" s="38"/>
+      <c r="BT11" s="22"/>
       <c r="BU11" s="22"/>
       <c r="BV11" s="22"/>
       <c r="BW11" s="22"/>
@@ -6417,100 +5421,100 @@
       <c r="BZ11" s="22"/>
       <c r="CA11" s="22"/>
       <c r="CB11" s="22"/>
-      <c r="CC11" s="13"/>
-      <c r="CD11" s="17"/>
-      <c r="CE11" s="39"/>
-      <c r="CF11" s="10"/>
-      <c r="CG11" s="10"/>
-      <c r="CH11" s="10"/>
-      <c r="CI11" s="10"/>
-      <c r="CJ11" s="10"/>
-      <c r="CK11" s="10"/>
-      <c r="CL11" s="10"/>
-      <c r="CM11" s="23"/>
-      <c r="CN11" s="23"/>
-      <c r="CO11" s="14"/>
-      <c r="CP11" s="17"/>
-      <c r="CQ11" s="39"/>
-      <c r="CR11" s="10"/>
-      <c r="CS11" s="10"/>
-      <c r="CT11" s="10"/>
-      <c r="CU11" s="10"/>
-      <c r="CV11" s="10"/>
-      <c r="CW11" s="10"/>
-      <c r="CX11" s="10"/>
-      <c r="CY11" s="27"/>
-      <c r="CZ11" s="27"/>
-      <c r="DA11" s="13"/>
-      <c r="DB11" s="17"/>
-      <c r="DC11" s="39"/>
-      <c r="DD11" s="10"/>
-      <c r="DE11" s="10"/>
-      <c r="DF11" s="10"/>
-      <c r="DG11" s="10"/>
-      <c r="DH11" s="10"/>
-      <c r="DI11" s="10"/>
-      <c r="DJ11" s="10"/>
-      <c r="DK11" s="23"/>
-      <c r="DL11" s="23"/>
-      <c r="DM11" s="14"/>
-      <c r="DN11" s="17"/>
-      <c r="DO11" s="39"/>
-      <c r="DP11" s="10"/>
-      <c r="DQ11" s="10"/>
-      <c r="DR11" s="10"/>
-      <c r="DS11" s="10"/>
-      <c r="DT11" s="10"/>
-      <c r="DU11" s="10"/>
-      <c r="DV11" s="10"/>
-      <c r="DW11" s="23"/>
-      <c r="DX11" s="23"/>
-      <c r="DY11" s="14"/>
-      <c r="DZ11" s="17"/>
-      <c r="EA11" s="39"/>
-      <c r="EB11" s="10"/>
-      <c r="EC11" s="10"/>
-      <c r="ED11" s="10"/>
-      <c r="EE11" s="10"/>
-      <c r="EF11" s="10"/>
-      <c r="EG11" s="10"/>
-      <c r="EH11" s="10"/>
-      <c r="EI11" s="23"/>
-      <c r="EJ11" s="23"/>
-      <c r="EK11" s="14"/>
-      <c r="EL11" s="17"/>
-      <c r="EM11" s="39"/>
-      <c r="EN11" s="10"/>
-      <c r="EO11" s="10"/>
-      <c r="EP11" s="10"/>
-      <c r="EQ11" s="10"/>
-      <c r="ER11" s="10"/>
-      <c r="ES11" s="10"/>
-      <c r="ET11" s="10"/>
-      <c r="EU11" s="23"/>
-      <c r="EV11" s="23"/>
-      <c r="EW11" s="14"/>
-      <c r="EX11" s="17"/>
-      <c r="EY11" s="39"/>
-      <c r="EZ11" s="10"/>
-      <c r="FA11" s="10"/>
-      <c r="FB11" s="10"/>
-      <c r="FC11" s="10"/>
-      <c r="FD11" s="10"/>
-      <c r="FE11" s="10"/>
-      <c r="FF11" s="10"/>
-      <c r="FG11" s="23"/>
-      <c r="FH11" s="23"/>
-      <c r="FI11" s="14"/>
+      <c r="CC11" s="39"/>
+      <c r="CD11" s="37"/>
+      <c r="CE11" s="38"/>
+      <c r="CF11" s="22"/>
+      <c r="CG11" s="22"/>
+      <c r="CH11" s="22"/>
+      <c r="CI11" s="22"/>
+      <c r="CJ11" s="22"/>
+      <c r="CK11" s="22"/>
+      <c r="CL11" s="22"/>
+      <c r="CM11" s="22"/>
+      <c r="CN11" s="22"/>
+      <c r="CO11" s="39"/>
+      <c r="CP11" s="37"/>
+      <c r="CQ11" s="38"/>
+      <c r="CR11" s="22"/>
+      <c r="CS11" s="22"/>
+      <c r="CT11" s="22"/>
+      <c r="CU11" s="22"/>
+      <c r="CV11" s="22"/>
+      <c r="CW11" s="22"/>
+      <c r="CX11" s="22"/>
+      <c r="CY11" s="22"/>
+      <c r="CZ11" s="22"/>
+      <c r="DA11" s="39"/>
+      <c r="DB11" s="37"/>
+      <c r="DC11" s="38"/>
+      <c r="DD11" s="22"/>
+      <c r="DE11" s="22"/>
+      <c r="DF11" s="22"/>
+      <c r="DG11" s="22"/>
+      <c r="DH11" s="22"/>
+      <c r="DI11" s="22"/>
+      <c r="DJ11" s="22"/>
+      <c r="DK11" s="22"/>
+      <c r="DL11" s="22"/>
+      <c r="DM11" s="39"/>
+      <c r="DN11" s="37"/>
+      <c r="DO11" s="38"/>
+      <c r="DP11" s="22"/>
+      <c r="DQ11" s="22"/>
+      <c r="DR11" s="22"/>
+      <c r="DS11" s="22"/>
+      <c r="DT11" s="22"/>
+      <c r="DU11" s="22"/>
+      <c r="DV11" s="22"/>
+      <c r="DW11" s="22"/>
+      <c r="DX11" s="22"/>
+      <c r="DY11" s="39"/>
+      <c r="DZ11" s="37"/>
+      <c r="EA11" s="38"/>
+      <c r="EB11" s="22"/>
+      <c r="EC11" s="22"/>
+      <c r="ED11" s="22"/>
+      <c r="EE11" s="22"/>
+      <c r="EF11" s="22"/>
+      <c r="EG11" s="22"/>
+      <c r="EH11" s="22"/>
+      <c r="EI11" s="22"/>
+      <c r="EJ11" s="22"/>
+      <c r="EK11" s="39"/>
+      <c r="EL11" s="37"/>
+      <c r="EM11" s="38"/>
+      <c r="EN11" s="22"/>
+      <c r="EO11" s="22"/>
+      <c r="EP11" s="22"/>
+      <c r="EQ11" s="22"/>
+      <c r="ER11" s="22"/>
+      <c r="ES11" s="22"/>
+      <c r="ET11" s="22"/>
+      <c r="EU11" s="22"/>
+      <c r="EV11" s="22"/>
+      <c r="EW11" s="39"/>
+      <c r="EX11" s="37"/>
+      <c r="EY11" s="38"/>
+      <c r="EZ11" s="22"/>
+      <c r="FA11" s="22"/>
+      <c r="FB11" s="22"/>
+      <c r="FC11" s="22"/>
+      <c r="FD11" s="22"/>
+      <c r="FE11" s="22"/>
+      <c r="FF11" s="22"/>
+      <c r="FG11" s="22"/>
+      <c r="FH11" s="22"/>
+      <c r="FI11" s="39"/>
     </row>
     <row r="12" spans="1:165" ht="65.55" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="25">
+        <v>34</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="21">
         <v>2.6736</v>
       </c>
       <c r="E12" s="10">
@@ -6523,292 +5527,172 @@
       </c>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="23"/>
-      <c r="J12" s="17">
-        <v>9</v>
-      </c>
-      <c r="K12" s="39">
-        <v>2.7</v>
-      </c>
-      <c r="L12" s="10">
-        <v>1</v>
-      </c>
-      <c r="M12" s="10">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="N12" s="10">
-        <v>12.2</v>
-      </c>
-      <c r="O12" s="10">
-        <v>15.7</v>
-      </c>
-      <c r="P12" s="10">
-        <v>20.2</v>
-      </c>
-      <c r="Q12" s="10">
-        <v>23.8</v>
-      </c>
-      <c r="R12" s="10">
-        <v>27.3</v>
-      </c>
-      <c r="S12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U12" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="V12" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="W12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="X12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AB12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AE12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AF12" s="39" t="s">
-        <v>66</v>
-      </c>
-      <c r="AG12" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="AH12" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI12" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR12" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AS12" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT12" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU12" s="39">
-        <v>2.67</v>
-      </c>
-      <c r="AV12" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW12" s="10">
-        <v>8.34</v>
-      </c>
-      <c r="AX12" s="10">
-        <v>12.25</v>
-      </c>
-      <c r="AY12" s="10">
-        <v>15.79</v>
-      </c>
-      <c r="AZ12" s="10">
-        <v>20.350000000000001</v>
-      </c>
-      <c r="BA12" s="10">
-        <v>23.95</v>
-      </c>
-      <c r="BB12" s="10">
-        <v>27.46</v>
-      </c>
-      <c r="BC12" s="10">
-        <v>1484.87</v>
-      </c>
-      <c r="BD12" s="10">
-        <v>1273.1300000000001</v>
-      </c>
-      <c r="BE12" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="BF12" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="BG12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BM12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP12" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BQ12" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="BR12" s="17"/>
-      <c r="BS12" s="39"/>
-      <c r="BT12" s="10"/>
-      <c r="BU12" s="10"/>
-      <c r="BV12" s="10"/>
-      <c r="BW12" s="10"/>
-      <c r="BX12" s="10"/>
-      <c r="BY12" s="10"/>
-      <c r="BZ12" s="10"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="22"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="22"/>
+      <c r="U12" s="39"/>
+      <c r="V12" s="37"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="22"/>
+      <c r="Z12" s="22"/>
+      <c r="AA12" s="22"/>
+      <c r="AB12" s="22"/>
+      <c r="AC12" s="22"/>
+      <c r="AD12" s="22"/>
+      <c r="AE12" s="22"/>
+      <c r="AF12" s="22"/>
+      <c r="AG12" s="39"/>
+      <c r="AH12" s="37"/>
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="22"/>
+      <c r="AK12" s="22"/>
+      <c r="AL12" s="22"/>
+      <c r="AM12" s="22"/>
+      <c r="AN12" s="22"/>
+      <c r="AO12" s="22"/>
+      <c r="AP12" s="22"/>
+      <c r="AQ12" s="22"/>
+      <c r="AR12" s="22"/>
+      <c r="AS12" s="39"/>
+      <c r="AT12" s="37"/>
+      <c r="AU12" s="38"/>
+      <c r="AV12" s="22"/>
+      <c r="AW12" s="22"/>
+      <c r="AX12" s="22"/>
+      <c r="AY12" s="22"/>
+      <c r="AZ12" s="22"/>
+      <c r="BA12" s="22"/>
+      <c r="BB12" s="22"/>
+      <c r="BC12" s="22"/>
+      <c r="BD12" s="22"/>
+      <c r="BE12" s="39"/>
+      <c r="BF12" s="37"/>
+      <c r="BG12" s="38"/>
+      <c r="BH12" s="22"/>
+      <c r="BI12" s="22"/>
+      <c r="BJ12" s="22"/>
+      <c r="BK12" s="22"/>
+      <c r="BL12" s="22"/>
+      <c r="BM12" s="22"/>
+      <c r="BN12" s="22"/>
+      <c r="BO12" s="22"/>
+      <c r="BP12" s="22"/>
+      <c r="BQ12" s="39"/>
+      <c r="BR12" s="37"/>
+      <c r="BS12" s="38"/>
+      <c r="BT12" s="22"/>
+      <c r="BU12" s="22"/>
+      <c r="BV12" s="22"/>
+      <c r="BW12" s="22"/>
+      <c r="BX12" s="22"/>
+      <c r="BY12" s="22"/>
+      <c r="BZ12" s="22"/>
       <c r="CA12" s="22"/>
       <c r="CB12" s="22"/>
-      <c r="CC12" s="14"/>
-      <c r="CD12" s="17"/>
-      <c r="CE12" s="39"/>
-      <c r="CF12" s="10"/>
-      <c r="CG12" s="10"/>
-      <c r="CH12" s="10"/>
-      <c r="CI12" s="10"/>
-      <c r="CJ12" s="10"/>
-      <c r="CK12" s="10"/>
-      <c r="CL12" s="10"/>
-      <c r="CM12" s="23"/>
-      <c r="CN12" s="23"/>
-      <c r="CO12" s="14"/>
-      <c r="CP12" s="17"/>
-      <c r="CQ12" s="39"/>
-      <c r="CR12" s="10"/>
-      <c r="CS12" s="10"/>
-      <c r="CT12" s="10"/>
-      <c r="CU12" s="10"/>
-      <c r="CV12" s="10"/>
-      <c r="CW12" s="10"/>
-      <c r="CX12" s="10"/>
-      <c r="CY12" s="23"/>
-      <c r="CZ12" s="23"/>
-      <c r="DA12" s="13"/>
-      <c r="DB12" s="17"/>
-      <c r="DC12" s="39"/>
-      <c r="DD12" s="10"/>
-      <c r="DE12" s="10"/>
-      <c r="DF12" s="10"/>
-      <c r="DG12" s="10"/>
-      <c r="DH12" s="10"/>
-      <c r="DI12" s="10"/>
-      <c r="DJ12" s="10"/>
-      <c r="DK12" s="23"/>
-      <c r="DL12" s="23"/>
-      <c r="DM12" s="14"/>
-      <c r="DN12" s="17"/>
-      <c r="DO12" s="39"/>
-      <c r="DP12" s="10"/>
-      <c r="DQ12" s="10"/>
-      <c r="DR12" s="10"/>
-      <c r="DS12" s="10"/>
-      <c r="DT12" s="10"/>
-      <c r="DU12" s="10"/>
-      <c r="DV12" s="10"/>
-      <c r="DW12" s="23"/>
-      <c r="DX12" s="23"/>
-      <c r="DY12" s="14"/>
-      <c r="DZ12" s="17"/>
-      <c r="EA12" s="39"/>
-      <c r="EB12" s="10"/>
-      <c r="EC12" s="10"/>
-      <c r="ED12" s="10"/>
-      <c r="EE12" s="10"/>
-      <c r="EF12" s="10"/>
-      <c r="EG12" s="10"/>
-      <c r="EH12" s="10"/>
-      <c r="EI12" s="23"/>
-      <c r="EJ12" s="23"/>
-      <c r="EK12" s="14"/>
-      <c r="EL12" s="17"/>
-      <c r="EM12" s="39"/>
-      <c r="EN12" s="10"/>
-      <c r="EO12" s="10"/>
-      <c r="EP12" s="10"/>
-      <c r="EQ12" s="10"/>
-      <c r="ER12" s="10"/>
-      <c r="ES12" s="10"/>
-      <c r="ET12" s="10"/>
-      <c r="EU12" s="23"/>
-      <c r="EV12" s="23"/>
-      <c r="EW12" s="14"/>
-      <c r="EX12" s="17"/>
-      <c r="EY12" s="39"/>
-      <c r="EZ12" s="10"/>
-      <c r="FA12" s="10"/>
-      <c r="FB12" s="10"/>
-      <c r="FC12" s="10"/>
-      <c r="FD12" s="10"/>
-      <c r="FE12" s="10"/>
-      <c r="FF12" s="10"/>
-      <c r="FG12" s="23"/>
-      <c r="FH12" s="23"/>
-      <c r="FI12" s="14"/>
+      <c r="CC12" s="39"/>
+      <c r="CD12" s="37"/>
+      <c r="CE12" s="38"/>
+      <c r="CF12" s="22"/>
+      <c r="CG12" s="22"/>
+      <c r="CH12" s="22"/>
+      <c r="CI12" s="22"/>
+      <c r="CJ12" s="22"/>
+      <c r="CK12" s="22"/>
+      <c r="CL12" s="22"/>
+      <c r="CM12" s="22"/>
+      <c r="CN12" s="22"/>
+      <c r="CO12" s="39"/>
+      <c r="CP12" s="37"/>
+      <c r="CQ12" s="38"/>
+      <c r="CR12" s="22"/>
+      <c r="CS12" s="22"/>
+      <c r="CT12" s="22"/>
+      <c r="CU12" s="22"/>
+      <c r="CV12" s="22"/>
+      <c r="CW12" s="22"/>
+      <c r="CX12" s="22"/>
+      <c r="CY12" s="22"/>
+      <c r="CZ12" s="22"/>
+      <c r="DA12" s="39"/>
+      <c r="DB12" s="37"/>
+      <c r="DC12" s="38"/>
+      <c r="DD12" s="22"/>
+      <c r="DE12" s="22"/>
+      <c r="DF12" s="22"/>
+      <c r="DG12" s="22"/>
+      <c r="DH12" s="22"/>
+      <c r="DI12" s="22"/>
+      <c r="DJ12" s="22"/>
+      <c r="DK12" s="22"/>
+      <c r="DL12" s="22"/>
+      <c r="DM12" s="39"/>
+      <c r="DN12" s="37"/>
+      <c r="DO12" s="38"/>
+      <c r="DP12" s="22"/>
+      <c r="DQ12" s="22"/>
+      <c r="DR12" s="22"/>
+      <c r="DS12" s="22"/>
+      <c r="DT12" s="22"/>
+      <c r="DU12" s="22"/>
+      <c r="DV12" s="22"/>
+      <c r="DW12" s="22"/>
+      <c r="DX12" s="22"/>
+      <c r="DY12" s="39"/>
+      <c r="DZ12" s="37"/>
+      <c r="EA12" s="38"/>
+      <c r="EB12" s="22"/>
+      <c r="EC12" s="22"/>
+      <c r="ED12" s="22"/>
+      <c r="EE12" s="22"/>
+      <c r="EF12" s="22"/>
+      <c r="EG12" s="22"/>
+      <c r="EH12" s="22"/>
+      <c r="EI12" s="22"/>
+      <c r="EJ12" s="22"/>
+      <c r="EK12" s="39"/>
+      <c r="EL12" s="37"/>
+      <c r="EM12" s="38"/>
+      <c r="EN12" s="22"/>
+      <c r="EO12" s="22"/>
+      <c r="EP12" s="22"/>
+      <c r="EQ12" s="22"/>
+      <c r="ER12" s="22"/>
+      <c r="ES12" s="22"/>
+      <c r="ET12" s="22"/>
+      <c r="EU12" s="22"/>
+      <c r="EV12" s="22"/>
+      <c r="EW12" s="39"/>
+      <c r="EX12" s="37"/>
+      <c r="EY12" s="38"/>
+      <c r="EZ12" s="22"/>
+      <c r="FA12" s="22"/>
+      <c r="FB12" s="22"/>
+      <c r="FC12" s="22"/>
+      <c r="FD12" s="22"/>
+      <c r="FE12" s="22"/>
+      <c r="FF12" s="22"/>
+      <c r="FG12" s="22"/>
+      <c r="FH12" s="22"/>
+      <c r="FI12" s="39"/>
     </row>
     <row r="13" spans="1:165" ht="55.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B13" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="25">
+        <v>35</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="21">
         <v>2.56</v>
       </c>
       <c r="E13" s="10">
@@ -6821,1912 +5705,1712 @@
       </c>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="17">
-        <v>9</v>
-      </c>
-      <c r="K13" s="39">
-        <v>2.6</v>
-      </c>
-      <c r="L13" s="10">
-        <v>1</v>
-      </c>
-      <c r="M13" s="10">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="N13" s="10">
-        <v>13.2</v>
-      </c>
-      <c r="O13" s="10">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="P13" s="10">
-        <v>21.1</v>
-      </c>
-      <c r="Q13" s="10">
-        <v>24.5</v>
-      </c>
-      <c r="R13" s="10">
-        <v>27.9</v>
-      </c>
-      <c r="S13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="T13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="U13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="V13" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="W13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="X13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AB13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AD13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AF13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AG13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AH13" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="AI13" s="39" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AK13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AL13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AM13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AN13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AP13" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="AQ13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AR13" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="AS13" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AT13" s="17">
-        <v>9</v>
-      </c>
-      <c r="AU13" s="39">
-        <v>2.56</v>
-      </c>
-      <c r="AV13" s="10">
-        <v>1</v>
-      </c>
-      <c r="AW13" s="10">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="AX13" s="10">
-        <v>13.32</v>
-      </c>
-      <c r="AY13" s="10">
-        <v>16.73</v>
-      </c>
-      <c r="AZ13" s="10">
-        <v>21.21</v>
-      </c>
-      <c r="BA13" s="10">
-        <v>24.65</v>
-      </c>
-      <c r="BB13" s="10">
-        <v>28.08</v>
-      </c>
-      <c r="BC13" s="9">
-        <v>1467.2</v>
-      </c>
-      <c r="BD13" s="9">
-        <v>1262.42</v>
-      </c>
-      <c r="BE13" s="14">
-        <v>0.02</v>
-      </c>
-      <c r="BF13" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="BG13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BI13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BJ13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BK13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BL13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BM13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BN13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BO13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP13" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="BQ13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="BR13" s="17"/>
-      <c r="BS13" s="39"/>
-      <c r="BT13" s="10"/>
-      <c r="BU13" s="10"/>
-      <c r="BV13" s="10"/>
-      <c r="BW13" s="10"/>
-      <c r="BX13" s="10"/>
-      <c r="BY13" s="10"/>
-      <c r="BZ13" s="10"/>
-      <c r="CA13" s="9"/>
-      <c r="CB13" s="9"/>
-      <c r="CC13" s="14"/>
-      <c r="CD13" s="17"/>
-      <c r="CE13" s="39"/>
-      <c r="CF13" s="10"/>
-      <c r="CG13" s="10"/>
-      <c r="CH13" s="10"/>
-      <c r="CI13" s="10"/>
-      <c r="CJ13" s="10"/>
-      <c r="CK13" s="10"/>
-      <c r="CL13" s="10"/>
-      <c r="CM13" s="23"/>
-      <c r="CN13" s="23"/>
-      <c r="CO13" s="14"/>
-      <c r="CP13" s="17"/>
-      <c r="CQ13" s="39"/>
-      <c r="CR13" s="10"/>
-      <c r="CS13" s="10"/>
-      <c r="CT13" s="10"/>
-      <c r="CU13" s="10"/>
-      <c r="CV13" s="10"/>
-      <c r="CW13" s="10"/>
-      <c r="CX13" s="10"/>
-      <c r="CY13" s="23"/>
-      <c r="CZ13" s="23"/>
-      <c r="DA13" s="13"/>
-      <c r="DB13" s="17"/>
-      <c r="DC13" s="39"/>
-      <c r="DD13" s="10"/>
-      <c r="DE13" s="10"/>
-      <c r="DF13" s="10"/>
-      <c r="DG13" s="10"/>
-      <c r="DH13" s="10"/>
-      <c r="DI13" s="10"/>
-      <c r="DJ13" s="10"/>
-      <c r="DK13" s="23"/>
-      <c r="DL13" s="23"/>
-      <c r="DM13" s="14"/>
-      <c r="DN13" s="17"/>
-      <c r="DO13" s="39"/>
-      <c r="DP13" s="10"/>
-      <c r="DQ13" s="10"/>
-      <c r="DR13" s="10"/>
-      <c r="DS13" s="10"/>
-      <c r="DT13" s="10"/>
-      <c r="DU13" s="10"/>
-      <c r="DV13" s="10"/>
-      <c r="DW13" s="23"/>
-      <c r="DX13" s="23"/>
-      <c r="DY13" s="14"/>
-      <c r="DZ13" s="17"/>
-      <c r="EA13" s="39"/>
-      <c r="EB13" s="10"/>
-      <c r="EC13" s="10"/>
-      <c r="ED13" s="10"/>
-      <c r="EE13" s="10"/>
-      <c r="EF13" s="10"/>
-      <c r="EG13" s="10"/>
-      <c r="EH13" s="10"/>
-      <c r="EI13" s="23"/>
-      <c r="EJ13" s="23"/>
-      <c r="EK13" s="14"/>
-      <c r="EL13" s="17"/>
-      <c r="EM13" s="39"/>
-      <c r="EN13" s="10"/>
-      <c r="EO13" s="10"/>
-      <c r="EP13" s="10"/>
-      <c r="EQ13" s="10"/>
-      <c r="ER13" s="10"/>
-      <c r="ES13" s="10"/>
-      <c r="ET13" s="10"/>
-      <c r="EU13" s="23"/>
-      <c r="EV13" s="23"/>
-      <c r="EW13" s="14"/>
-      <c r="EX13" s="17"/>
-      <c r="EY13" s="39"/>
-      <c r="EZ13" s="10"/>
-      <c r="FA13" s="10"/>
-      <c r="FB13" s="10"/>
-      <c r="FC13" s="10"/>
-      <c r="FD13" s="10"/>
-      <c r="FE13" s="10"/>
-      <c r="FF13" s="10"/>
-      <c r="FG13" s="23"/>
-      <c r="FH13" s="23"/>
-      <c r="FI13" s="14"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="38"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="22"/>
+      <c r="P13" s="22"/>
+      <c r="Q13" s="22"/>
+      <c r="R13" s="22"/>
+      <c r="S13" s="22"/>
+      <c r="T13" s="22"/>
+      <c r="U13" s="39"/>
+      <c r="V13" s="37"/>
+      <c r="W13" s="38"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="22"/>
+      <c r="Z13" s="22"/>
+      <c r="AA13" s="22"/>
+      <c r="AB13" s="22"/>
+      <c r="AC13" s="22"/>
+      <c r="AD13" s="22"/>
+      <c r="AE13" s="22"/>
+      <c r="AF13" s="22"/>
+      <c r="AG13" s="39"/>
+      <c r="AH13" s="37"/>
+      <c r="AI13" s="38"/>
+      <c r="AJ13" s="22"/>
+      <c r="AK13" s="22"/>
+      <c r="AL13" s="22"/>
+      <c r="AM13" s="22"/>
+      <c r="AN13" s="22"/>
+      <c r="AO13" s="22"/>
+      <c r="AP13" s="22"/>
+      <c r="AQ13" s="22"/>
+      <c r="AR13" s="22"/>
+      <c r="AS13" s="39"/>
+      <c r="AT13" s="37"/>
+      <c r="AU13" s="38"/>
+      <c r="AV13" s="22"/>
+      <c r="AW13" s="22"/>
+      <c r="AX13" s="22"/>
+      <c r="AY13" s="22"/>
+      <c r="AZ13" s="22"/>
+      <c r="BA13" s="22"/>
+      <c r="BB13" s="22"/>
+      <c r="BC13" s="22"/>
+      <c r="BD13" s="22"/>
+      <c r="BE13" s="39"/>
+      <c r="BF13" s="37"/>
+      <c r="BG13" s="38"/>
+      <c r="BH13" s="22"/>
+      <c r="BI13" s="22"/>
+      <c r="BJ13" s="22"/>
+      <c r="BK13" s="22"/>
+      <c r="BL13" s="22"/>
+      <c r="BM13" s="22"/>
+      <c r="BN13" s="22"/>
+      <c r="BO13" s="22"/>
+      <c r="BP13" s="22"/>
+      <c r="BQ13" s="39"/>
+      <c r="BR13" s="37"/>
+      <c r="BS13" s="38"/>
+      <c r="BT13" s="22"/>
+      <c r="BU13" s="22"/>
+      <c r="BV13" s="22"/>
+      <c r="BW13" s="22"/>
+      <c r="BX13" s="22"/>
+      <c r="BY13" s="22"/>
+      <c r="BZ13" s="22"/>
+      <c r="CA13" s="22"/>
+      <c r="CB13" s="22"/>
+      <c r="CC13" s="39"/>
+      <c r="CD13" s="37"/>
+      <c r="CE13" s="38"/>
+      <c r="CF13" s="22"/>
+      <c r="CG13" s="22"/>
+      <c r="CH13" s="22"/>
+      <c r="CI13" s="22"/>
+      <c r="CJ13" s="22"/>
+      <c r="CK13" s="22"/>
+      <c r="CL13" s="22"/>
+      <c r="CM13" s="22"/>
+      <c r="CN13" s="22"/>
+      <c r="CO13" s="39"/>
+      <c r="CP13" s="37"/>
+      <c r="CQ13" s="38"/>
+      <c r="CR13" s="22"/>
+      <c r="CS13" s="22"/>
+      <c r="CT13" s="22"/>
+      <c r="CU13" s="22"/>
+      <c r="CV13" s="22"/>
+      <c r="CW13" s="22"/>
+      <c r="CX13" s="22"/>
+      <c r="CY13" s="22"/>
+      <c r="CZ13" s="22"/>
+      <c r="DA13" s="39"/>
+      <c r="DB13" s="37"/>
+      <c r="DC13" s="38"/>
+      <c r="DD13" s="22"/>
+      <c r="DE13" s="22"/>
+      <c r="DF13" s="22"/>
+      <c r="DG13" s="22"/>
+      <c r="DH13" s="22"/>
+      <c r="DI13" s="22"/>
+      <c r="DJ13" s="22"/>
+      <c r="DK13" s="22"/>
+      <c r="DL13" s="22"/>
+      <c r="DM13" s="39"/>
+      <c r="DN13" s="37"/>
+      <c r="DO13" s="38"/>
+      <c r="DP13" s="22"/>
+      <c r="DQ13" s="22"/>
+      <c r="DR13" s="22"/>
+      <c r="DS13" s="22"/>
+      <c r="DT13" s="22"/>
+      <c r="DU13" s="22"/>
+      <c r="DV13" s="22"/>
+      <c r="DW13" s="22"/>
+      <c r="DX13" s="22"/>
+      <c r="DY13" s="39"/>
+      <c r="DZ13" s="37"/>
+      <c r="EA13" s="38"/>
+      <c r="EB13" s="22"/>
+      <c r="EC13" s="22"/>
+      <c r="ED13" s="22"/>
+      <c r="EE13" s="22"/>
+      <c r="EF13" s="22"/>
+      <c r="EG13" s="22"/>
+      <c r="EH13" s="22"/>
+      <c r="EI13" s="22"/>
+      <c r="EJ13" s="22"/>
+      <c r="EK13" s="39"/>
+      <c r="EL13" s="37"/>
+      <c r="EM13" s="38"/>
+      <c r="EN13" s="22"/>
+      <c r="EO13" s="22"/>
+      <c r="EP13" s="22"/>
+      <c r="EQ13" s="22"/>
+      <c r="ER13" s="22"/>
+      <c r="ES13" s="22"/>
+      <c r="ET13" s="22"/>
+      <c r="EU13" s="22"/>
+      <c r="EV13" s="22"/>
+      <c r="EW13" s="39"/>
+      <c r="EX13" s="37"/>
+      <c r="EY13" s="38"/>
+      <c r="EZ13" s="22"/>
+      <c r="FA13" s="22"/>
+      <c r="FB13" s="22"/>
+      <c r="FC13" s="22"/>
+      <c r="FD13" s="22"/>
+      <c r="FE13" s="22"/>
+      <c r="FF13" s="22"/>
+      <c r="FG13" s="22"/>
+      <c r="FH13" s="22"/>
+      <c r="FI13" s="39"/>
     </row>
-    <row r="14" spans="1:165" s="36" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="K14" s="40"/>
-      <c r="L14" s="33"/>
-      <c r="M14" s="33"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="30"/>
-      <c r="T14" s="30"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="W14" s="40"/>
-      <c r="X14" s="33"/>
-      <c r="Y14" s="33"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="33"/>
-      <c r="AB14" s="33"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="33"/>
-      <c r="AE14" s="30"/>
-      <c r="AF14" s="30"/>
-      <c r="AG14" s="37"/>
-      <c r="AH14" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI14" s="40"/>
-      <c r="AJ14" s="33"/>
-      <c r="AK14" s="33"/>
-      <c r="AL14" s="33"/>
-      <c r="AM14" s="33"/>
-      <c r="AN14" s="33"/>
-      <c r="AO14" s="33"/>
-      <c r="AP14" s="33"/>
-      <c r="AQ14" s="30"/>
-      <c r="AR14" s="30"/>
-      <c r="AS14" s="37"/>
-      <c r="AT14" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU14" s="40"/>
-      <c r="AV14" s="33"/>
-      <c r="AW14" s="33"/>
-      <c r="AX14" s="33"/>
-      <c r="AY14" s="33"/>
-      <c r="AZ14" s="33"/>
-      <c r="BA14" s="33"/>
-      <c r="BB14" s="33"/>
-      <c r="BC14" s="30"/>
-      <c r="BD14" s="30"/>
-      <c r="BE14" s="37"/>
-      <c r="BF14" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG14" s="33"/>
-      <c r="BH14" s="33"/>
-      <c r="BI14" s="33"/>
-      <c r="BJ14" s="33"/>
-      <c r="BK14" s="33"/>
-      <c r="BL14" s="33"/>
-      <c r="BM14" s="33"/>
-      <c r="BN14" s="33"/>
-      <c r="BO14" s="30"/>
-      <c r="BP14" s="30"/>
-      <c r="BQ14" s="37"/>
-      <c r="BR14" s="28"/>
-      <c r="BS14" s="40"/>
-      <c r="BT14" s="33"/>
-      <c r="BU14" s="33"/>
-      <c r="BV14" s="33"/>
-      <c r="BW14" s="33"/>
-      <c r="BX14" s="33"/>
-      <c r="BY14" s="33"/>
-      <c r="BZ14" s="33"/>
-      <c r="CA14" s="30"/>
-      <c r="CB14" s="30"/>
-      <c r="CC14" s="37"/>
-      <c r="CD14" s="28"/>
-      <c r="CE14" s="40"/>
-      <c r="CF14" s="33"/>
-      <c r="CG14" s="33"/>
-      <c r="CH14" s="33"/>
-      <c r="CI14" s="33"/>
-      <c r="CJ14" s="33"/>
-      <c r="CK14" s="33"/>
-      <c r="CL14" s="33"/>
-      <c r="CM14" s="35"/>
-      <c r="CN14" s="35"/>
-      <c r="CO14" s="37"/>
-      <c r="CP14" s="28"/>
-      <c r="CQ14" s="40"/>
-      <c r="CR14" s="33"/>
-      <c r="CS14" s="33"/>
-      <c r="CT14" s="33"/>
-      <c r="CU14" s="33"/>
-      <c r="CV14" s="33"/>
-      <c r="CW14" s="33"/>
-      <c r="CX14" s="33"/>
-      <c r="CY14" s="35"/>
-      <c r="CZ14" s="35"/>
-      <c r="DA14" s="37"/>
-      <c r="DB14" s="28"/>
-      <c r="DC14" s="40"/>
-      <c r="DD14" s="33"/>
-      <c r="DE14" s="33"/>
-      <c r="DF14" s="33"/>
-      <c r="DG14" s="33"/>
-      <c r="DH14" s="33"/>
-      <c r="DI14" s="33"/>
-      <c r="DJ14" s="33"/>
-      <c r="DK14" s="35"/>
-      <c r="DL14" s="35"/>
-      <c r="DM14" s="37"/>
-      <c r="DN14" s="28"/>
-      <c r="DO14" s="40"/>
-      <c r="DP14" s="33"/>
-      <c r="DQ14" s="33"/>
-      <c r="DR14" s="33"/>
-      <c r="DS14" s="33"/>
-      <c r="DT14" s="33"/>
-      <c r="DU14" s="33"/>
-      <c r="DV14" s="33"/>
-      <c r="DW14" s="35"/>
-      <c r="DX14" s="35"/>
-      <c r="DY14" s="37"/>
-      <c r="DZ14" s="28"/>
-      <c r="EA14" s="40"/>
-      <c r="EB14" s="33"/>
-      <c r="EC14" s="33"/>
-      <c r="ED14" s="33"/>
-      <c r="EE14" s="33"/>
-      <c r="EF14" s="33"/>
-      <c r="EG14" s="33"/>
-      <c r="EH14" s="33"/>
-      <c r="EI14" s="35"/>
-      <c r="EJ14" s="35"/>
-      <c r="EK14" s="37"/>
-      <c r="EL14" s="28"/>
-      <c r="EM14" s="40"/>
-      <c r="EN14" s="33"/>
-      <c r="EO14" s="33"/>
-      <c r="EP14" s="33"/>
-      <c r="EQ14" s="33"/>
-      <c r="ER14" s="33"/>
-      <c r="ES14" s="33"/>
-      <c r="ET14" s="33"/>
-      <c r="EU14" s="35"/>
-      <c r="EV14" s="35"/>
-      <c r="EW14" s="37"/>
-      <c r="EX14" s="28"/>
-      <c r="EY14" s="40"/>
-      <c r="EZ14" s="33"/>
-      <c r="FA14" s="33"/>
-      <c r="FB14" s="33"/>
-      <c r="FC14" s="33"/>
-      <c r="FD14" s="33"/>
-      <c r="FE14" s="33"/>
-      <c r="FF14" s="33"/>
-      <c r="FG14" s="35"/>
-      <c r="FH14" s="35"/>
-      <c r="FI14" s="37"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="42"/>
+      <c r="N14" s="42"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="43"/>
+      <c r="U14" s="44"/>
+      <c r="V14" s="40"/>
+      <c r="W14" s="41"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="42"/>
+      <c r="Z14" s="42"/>
+      <c r="AA14" s="42"/>
+      <c r="AB14" s="42"/>
+      <c r="AC14" s="42"/>
+      <c r="AD14" s="42"/>
+      <c r="AE14" s="43"/>
+      <c r="AF14" s="43"/>
+      <c r="AG14" s="44"/>
+      <c r="AH14" s="40"/>
+      <c r="AI14" s="41"/>
+      <c r="AJ14" s="42"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="42"/>
+      <c r="AM14" s="42"/>
+      <c r="AN14" s="42"/>
+      <c r="AO14" s="42"/>
+      <c r="AP14" s="42"/>
+      <c r="AQ14" s="43"/>
+      <c r="AR14" s="43"/>
+      <c r="AS14" s="44"/>
+      <c r="AT14" s="40"/>
+      <c r="AU14" s="41"/>
+      <c r="AV14" s="42"/>
+      <c r="AW14" s="42"/>
+      <c r="AX14" s="42"/>
+      <c r="AY14" s="42"/>
+      <c r="AZ14" s="42"/>
+      <c r="BA14" s="42"/>
+      <c r="BB14" s="42"/>
+      <c r="BC14" s="43"/>
+      <c r="BD14" s="43"/>
+      <c r="BE14" s="44"/>
+      <c r="BF14" s="40"/>
+      <c r="BG14" s="41"/>
+      <c r="BH14" s="42"/>
+      <c r="BI14" s="42"/>
+      <c r="BJ14" s="42"/>
+      <c r="BK14" s="42"/>
+      <c r="BL14" s="42"/>
+      <c r="BM14" s="42"/>
+      <c r="BN14" s="42"/>
+      <c r="BO14" s="43"/>
+      <c r="BP14" s="43"/>
+      <c r="BQ14" s="44"/>
+      <c r="BR14" s="40"/>
+      <c r="BS14" s="41"/>
+      <c r="BT14" s="42"/>
+      <c r="BU14" s="42"/>
+      <c r="BV14" s="42"/>
+      <c r="BW14" s="42"/>
+      <c r="BX14" s="42"/>
+      <c r="BY14" s="42"/>
+      <c r="BZ14" s="42"/>
+      <c r="CA14" s="43"/>
+      <c r="CB14" s="43"/>
+      <c r="CC14" s="44"/>
+      <c r="CD14" s="40"/>
+      <c r="CE14" s="41"/>
+      <c r="CF14" s="42"/>
+      <c r="CG14" s="42"/>
+      <c r="CH14" s="42"/>
+      <c r="CI14" s="42"/>
+      <c r="CJ14" s="42"/>
+      <c r="CK14" s="42"/>
+      <c r="CL14" s="42"/>
+      <c r="CM14" s="43"/>
+      <c r="CN14" s="43"/>
+      <c r="CO14" s="44"/>
+      <c r="CP14" s="40"/>
+      <c r="CQ14" s="41"/>
+      <c r="CR14" s="42"/>
+      <c r="CS14" s="42"/>
+      <c r="CT14" s="42"/>
+      <c r="CU14" s="42"/>
+      <c r="CV14" s="42"/>
+      <c r="CW14" s="42"/>
+      <c r="CX14" s="42"/>
+      <c r="CY14" s="43"/>
+      <c r="CZ14" s="43"/>
+      <c r="DA14" s="44"/>
+      <c r="DB14" s="40"/>
+      <c r="DC14" s="41"/>
+      <c r="DD14" s="42"/>
+      <c r="DE14" s="42"/>
+      <c r="DF14" s="42"/>
+      <c r="DG14" s="42"/>
+      <c r="DH14" s="42"/>
+      <c r="DI14" s="42"/>
+      <c r="DJ14" s="42"/>
+      <c r="DK14" s="43"/>
+      <c r="DL14" s="43"/>
+      <c r="DM14" s="44"/>
+      <c r="DN14" s="40"/>
+      <c r="DO14" s="41"/>
+      <c r="DP14" s="42"/>
+      <c r="DQ14" s="42"/>
+      <c r="DR14" s="42"/>
+      <c r="DS14" s="42"/>
+      <c r="DT14" s="42"/>
+      <c r="DU14" s="42"/>
+      <c r="DV14" s="42"/>
+      <c r="DW14" s="43"/>
+      <c r="DX14" s="43"/>
+      <c r="DY14" s="44"/>
+      <c r="DZ14" s="40"/>
+      <c r="EA14" s="41"/>
+      <c r="EB14" s="42"/>
+      <c r="EC14" s="42"/>
+      <c r="ED14" s="42"/>
+      <c r="EE14" s="42"/>
+      <c r="EF14" s="42"/>
+      <c r="EG14" s="42"/>
+      <c r="EH14" s="42"/>
+      <c r="EI14" s="43"/>
+      <c r="EJ14" s="43"/>
+      <c r="EK14" s="44"/>
+      <c r="EL14" s="40"/>
+      <c r="EM14" s="41"/>
+      <c r="EN14" s="42"/>
+      <c r="EO14" s="42"/>
+      <c r="EP14" s="42"/>
+      <c r="EQ14" s="42"/>
+      <c r="ER14" s="42"/>
+      <c r="ES14" s="42"/>
+      <c r="ET14" s="42"/>
+      <c r="EU14" s="43"/>
+      <c r="EV14" s="43"/>
+      <c r="EW14" s="44"/>
+      <c r="EX14" s="40"/>
+      <c r="EY14" s="41"/>
+      <c r="EZ14" s="42"/>
+      <c r="FA14" s="42"/>
+      <c r="FB14" s="42"/>
+      <c r="FC14" s="42"/>
+      <c r="FD14" s="42"/>
+      <c r="FE14" s="42"/>
+      <c r="FF14" s="42"/>
+      <c r="FG14" s="43"/>
+      <c r="FH14" s="43"/>
+      <c r="FI14" s="44"/>
     </row>
-    <row r="15" spans="1:165" s="36" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="33"/>
-      <c r="M15" s="33"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="30"/>
-      <c r="T15" s="30"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="W15" s="40"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="33"/>
-      <c r="AB15" s="33"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="33"/>
-      <c r="AE15" s="30"/>
-      <c r="AF15" s="30"/>
-      <c r="AG15" s="34"/>
-      <c r="AH15" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI15" s="40"/>
-      <c r="AJ15" s="33"/>
-      <c r="AK15" s="33"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="33"/>
-      <c r="AN15" s="33"/>
-      <c r="AO15" s="33"/>
-      <c r="AP15" s="33"/>
-      <c r="AQ15" s="30"/>
-      <c r="AR15" s="30"/>
-      <c r="AS15" s="34"/>
-      <c r="AT15" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="AU15" s="40"/>
-      <c r="AV15" s="33"/>
-      <c r="AW15" s="33"/>
-      <c r="AX15" s="33"/>
-      <c r="AY15" s="33"/>
-      <c r="AZ15" s="33"/>
-      <c r="BA15" s="33"/>
-      <c r="BB15" s="33"/>
-      <c r="BC15" s="30"/>
-      <c r="BD15" s="30"/>
-      <c r="BE15" s="34"/>
-      <c r="BF15" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="BG15" s="33"/>
-      <c r="BH15" s="33"/>
-      <c r="BI15" s="33"/>
-      <c r="BJ15" s="33"/>
-      <c r="BK15" s="33"/>
-      <c r="BL15" s="33"/>
-      <c r="BM15" s="33"/>
-      <c r="BN15" s="33"/>
-      <c r="BO15" s="30"/>
-      <c r="BP15" s="30"/>
-      <c r="BQ15" s="34"/>
-      <c r="BR15" s="28"/>
-      <c r="BS15" s="40"/>
-      <c r="BT15" s="33"/>
-      <c r="BU15" s="33"/>
-      <c r="BV15" s="33"/>
-      <c r="BW15" s="33"/>
-      <c r="BX15" s="33"/>
-      <c r="BY15" s="33"/>
-      <c r="BZ15" s="33"/>
-      <c r="CA15" s="30"/>
-      <c r="CB15" s="30"/>
-      <c r="CC15" s="34"/>
-      <c r="CD15" s="28"/>
-      <c r="CE15" s="40"/>
-      <c r="CF15" s="33"/>
-      <c r="CG15" s="33"/>
-      <c r="CH15" s="33"/>
-      <c r="CI15" s="33"/>
-      <c r="CJ15" s="33"/>
-      <c r="CK15" s="33"/>
-      <c r="CL15" s="33"/>
-      <c r="CM15" s="35"/>
-      <c r="CN15" s="35"/>
-      <c r="CO15" s="34"/>
-      <c r="CP15" s="28"/>
-      <c r="CQ15" s="40"/>
-      <c r="CR15" s="33"/>
-      <c r="CS15" s="33"/>
-      <c r="CT15" s="33"/>
-      <c r="CU15" s="33"/>
-      <c r="CV15" s="33"/>
-      <c r="CW15" s="33"/>
-      <c r="CX15" s="33"/>
-      <c r="CY15" s="35"/>
-      <c r="CZ15" s="35"/>
-      <c r="DA15" s="34"/>
-      <c r="DB15" s="28"/>
-      <c r="DC15" s="40"/>
-      <c r="DD15" s="33"/>
-      <c r="DE15" s="33"/>
-      <c r="DF15" s="33"/>
-      <c r="DG15" s="33"/>
-      <c r="DH15" s="33"/>
-      <c r="DI15" s="33"/>
-      <c r="DJ15" s="33"/>
-      <c r="DK15" s="35"/>
-      <c r="DL15" s="35"/>
-      <c r="DM15" s="34"/>
-      <c r="DN15" s="28"/>
-      <c r="DO15" s="40"/>
-      <c r="DP15" s="33"/>
-      <c r="DQ15" s="33"/>
-      <c r="DR15" s="33"/>
-      <c r="DS15" s="33"/>
-      <c r="DT15" s="33"/>
-      <c r="DU15" s="33"/>
-      <c r="DV15" s="33"/>
-      <c r="DW15" s="35"/>
-      <c r="DX15" s="35"/>
-      <c r="DY15" s="34"/>
-      <c r="DZ15" s="28"/>
-      <c r="EA15" s="40"/>
-      <c r="EB15" s="33"/>
-      <c r="EC15" s="33"/>
-      <c r="ED15" s="33"/>
-      <c r="EE15" s="33"/>
-      <c r="EF15" s="33"/>
-      <c r="EG15" s="33"/>
-      <c r="EH15" s="33"/>
-      <c r="EI15" s="35"/>
-      <c r="EJ15" s="35"/>
-      <c r="EK15" s="34"/>
-      <c r="EL15" s="28"/>
-      <c r="EM15" s="40"/>
-      <c r="EN15" s="33"/>
-      <c r="EO15" s="33"/>
-      <c r="EP15" s="33"/>
-      <c r="EQ15" s="33"/>
-      <c r="ER15" s="33"/>
-      <c r="ES15" s="33"/>
-      <c r="ET15" s="33"/>
-      <c r="EU15" s="35"/>
-      <c r="EV15" s="35"/>
-      <c r="EW15" s="34"/>
-      <c r="EX15" s="28"/>
-      <c r="EY15" s="40"/>
-      <c r="EZ15" s="33"/>
-      <c r="FA15" s="33"/>
-      <c r="FB15" s="33"/>
-      <c r="FC15" s="33"/>
-      <c r="FD15" s="33"/>
-      <c r="FE15" s="33"/>
-      <c r="FF15" s="33"/>
-      <c r="FG15" s="35"/>
-      <c r="FH15" s="35"/>
-      <c r="FI15" s="34"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="44"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="43"/>
+      <c r="AF15" s="43"/>
+      <c r="AG15" s="44"/>
+      <c r="AH15" s="40"/>
+      <c r="AI15" s="41"/>
+      <c r="AJ15" s="42"/>
+      <c r="AK15" s="42"/>
+      <c r="AL15" s="42"/>
+      <c r="AM15" s="42"/>
+      <c r="AN15" s="42"/>
+      <c r="AO15" s="42"/>
+      <c r="AP15" s="42"/>
+      <c r="AQ15" s="43"/>
+      <c r="AR15" s="43"/>
+      <c r="AS15" s="44"/>
+      <c r="AT15" s="40"/>
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="42"/>
+      <c r="AW15" s="42"/>
+      <c r="AX15" s="42"/>
+      <c r="AY15" s="42"/>
+      <c r="AZ15" s="42"/>
+      <c r="BA15" s="42"/>
+      <c r="BB15" s="42"/>
+      <c r="BC15" s="43"/>
+      <c r="BD15" s="43"/>
+      <c r="BE15" s="44"/>
+      <c r="BF15" s="40"/>
+      <c r="BG15" s="41"/>
+      <c r="BH15" s="42"/>
+      <c r="BI15" s="42"/>
+      <c r="BJ15" s="42"/>
+      <c r="BK15" s="42"/>
+      <c r="BL15" s="42"/>
+      <c r="BM15" s="42"/>
+      <c r="BN15" s="42"/>
+      <c r="BO15" s="43"/>
+      <c r="BP15" s="43"/>
+      <c r="BQ15" s="44"/>
+      <c r="BR15" s="40"/>
+      <c r="BS15" s="41"/>
+      <c r="BT15" s="42"/>
+      <c r="BU15" s="42"/>
+      <c r="BV15" s="42"/>
+      <c r="BW15" s="42"/>
+      <c r="BX15" s="42"/>
+      <c r="BY15" s="42"/>
+      <c r="BZ15" s="42"/>
+      <c r="CA15" s="43"/>
+      <c r="CB15" s="43"/>
+      <c r="CC15" s="44"/>
+      <c r="CD15" s="40"/>
+      <c r="CE15" s="41"/>
+      <c r="CF15" s="42"/>
+      <c r="CG15" s="42"/>
+      <c r="CH15" s="42"/>
+      <c r="CI15" s="42"/>
+      <c r="CJ15" s="42"/>
+      <c r="CK15" s="42"/>
+      <c r="CL15" s="42"/>
+      <c r="CM15" s="43"/>
+      <c r="CN15" s="43"/>
+      <c r="CO15" s="44"/>
+      <c r="CP15" s="40"/>
+      <c r="CQ15" s="41"/>
+      <c r="CR15" s="42"/>
+      <c r="CS15" s="42"/>
+      <c r="CT15" s="42"/>
+      <c r="CU15" s="42"/>
+      <c r="CV15" s="42"/>
+      <c r="CW15" s="42"/>
+      <c r="CX15" s="42"/>
+      <c r="CY15" s="43"/>
+      <c r="CZ15" s="43"/>
+      <c r="DA15" s="44"/>
+      <c r="DB15" s="40"/>
+      <c r="DC15" s="41"/>
+      <c r="DD15" s="42"/>
+      <c r="DE15" s="42"/>
+      <c r="DF15" s="42"/>
+      <c r="DG15" s="42"/>
+      <c r="DH15" s="42"/>
+      <c r="DI15" s="42"/>
+      <c r="DJ15" s="42"/>
+      <c r="DK15" s="43"/>
+      <c r="DL15" s="43"/>
+      <c r="DM15" s="44"/>
+      <c r="DN15" s="40"/>
+      <c r="DO15" s="41"/>
+      <c r="DP15" s="42"/>
+      <c r="DQ15" s="42"/>
+      <c r="DR15" s="42"/>
+      <c r="DS15" s="42"/>
+      <c r="DT15" s="42"/>
+      <c r="DU15" s="42"/>
+      <c r="DV15" s="42"/>
+      <c r="DW15" s="43"/>
+      <c r="DX15" s="43"/>
+      <c r="DY15" s="44"/>
+      <c r="DZ15" s="40"/>
+      <c r="EA15" s="41"/>
+      <c r="EB15" s="42"/>
+      <c r="EC15" s="42"/>
+      <c r="ED15" s="42"/>
+      <c r="EE15" s="42"/>
+      <c r="EF15" s="42"/>
+      <c r="EG15" s="42"/>
+      <c r="EH15" s="42"/>
+      <c r="EI15" s="43"/>
+      <c r="EJ15" s="43"/>
+      <c r="EK15" s="44"/>
+      <c r="EL15" s="40"/>
+      <c r="EM15" s="41"/>
+      <c r="EN15" s="42"/>
+      <c r="EO15" s="42"/>
+      <c r="EP15" s="42"/>
+      <c r="EQ15" s="42"/>
+      <c r="ER15" s="42"/>
+      <c r="ES15" s="42"/>
+      <c r="ET15" s="42"/>
+      <c r="EU15" s="43"/>
+      <c r="EV15" s="43"/>
+      <c r="EW15" s="44"/>
+      <c r="EX15" s="40"/>
+      <c r="EY15" s="41"/>
+      <c r="EZ15" s="42"/>
+      <c r="FA15" s="42"/>
+      <c r="FB15" s="42"/>
+      <c r="FC15" s="42"/>
+      <c r="FD15" s="42"/>
+      <c r="FE15" s="42"/>
+      <c r="FF15" s="42"/>
+      <c r="FG15" s="43"/>
+      <c r="FH15" s="43"/>
+      <c r="FI15" s="44"/>
     </row>
-    <row r="16" spans="1:165" s="36" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="33"/>
-      <c r="M16" s="33"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="28" t="s">
-        <v>59</v>
-      </c>
+      <c r="B16" s="23"/>
+      <c r="C16" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="42"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="42"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="44"/>
+      <c r="V16" s="40"/>
       <c r="W16" s="41"/>
-      <c r="X16" s="33"/>
-      <c r="Y16" s="33"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="33"/>
-      <c r="AB16" s="33"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="33"/>
-      <c r="AE16" s="30"/>
-      <c r="AF16" s="30"/>
-      <c r="AG16" s="34"/>
-      <c r="AH16" s="28" t="s">
-        <v>60</v>
-      </c>
+      <c r="X16" s="42"/>
+      <c r="Y16" s="42"/>
+      <c r="Z16" s="42"/>
+      <c r="AA16" s="42"/>
+      <c r="AB16" s="42"/>
+      <c r="AC16" s="42"/>
+      <c r="AD16" s="42"/>
+      <c r="AE16" s="43"/>
+      <c r="AF16" s="43"/>
+      <c r="AG16" s="44"/>
+      <c r="AH16" s="40"/>
       <c r="AI16" s="41"/>
-      <c r="AJ16" s="33"/>
-      <c r="AK16" s="33"/>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="33"/>
-      <c r="AN16" s="33"/>
-      <c r="AO16" s="33"/>
-      <c r="AP16" s="33"/>
-      <c r="AQ16" s="30"/>
-      <c r="AR16" s="30"/>
-      <c r="AS16" s="34"/>
-      <c r="AT16" s="31" t="s">
-        <v>74</v>
-      </c>
+      <c r="AJ16" s="42"/>
+      <c r="AK16" s="42"/>
+      <c r="AL16" s="42"/>
+      <c r="AM16" s="42"/>
+      <c r="AN16" s="42"/>
+      <c r="AO16" s="42"/>
+      <c r="AP16" s="42"/>
+      <c r="AQ16" s="43"/>
+      <c r="AR16" s="43"/>
+      <c r="AS16" s="44"/>
+      <c r="AT16" s="40"/>
       <c r="AU16" s="41"/>
-      <c r="AV16" s="33"/>
-      <c r="AW16" s="33"/>
-      <c r="AX16" s="33"/>
-      <c r="AY16" s="33"/>
-      <c r="AZ16" s="33"/>
-      <c r="BA16" s="33"/>
-      <c r="BB16" s="33"/>
-      <c r="BC16" s="30"/>
-      <c r="BD16" s="30"/>
-      <c r="BE16" s="34"/>
-      <c r="BF16" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="BG16" s="33"/>
-      <c r="BH16" s="33"/>
-      <c r="BI16" s="33"/>
-      <c r="BJ16" s="33"/>
-      <c r="BK16" s="33"/>
-      <c r="BL16" s="33"/>
-      <c r="BM16" s="33"/>
-      <c r="BN16" s="33"/>
-      <c r="BO16" s="30"/>
-      <c r="BP16" s="30"/>
-      <c r="BQ16" s="34"/>
-      <c r="BR16" s="31"/>
-      <c r="BS16" s="40"/>
-      <c r="BT16" s="33"/>
-      <c r="BU16" s="33"/>
-      <c r="BV16" s="33"/>
-      <c r="BW16" s="33"/>
-      <c r="BX16" s="33"/>
-      <c r="BY16" s="33"/>
-      <c r="BZ16" s="33"/>
-      <c r="CA16" s="30"/>
-      <c r="CB16" s="30"/>
-      <c r="CC16" s="34"/>
-      <c r="CD16" s="31"/>
+      <c r="AV16" s="42"/>
+      <c r="AW16" s="42"/>
+      <c r="AX16" s="42"/>
+      <c r="AY16" s="42"/>
+      <c r="AZ16" s="42"/>
+      <c r="BA16" s="42"/>
+      <c r="BB16" s="42"/>
+      <c r="BC16" s="43"/>
+      <c r="BD16" s="43"/>
+      <c r="BE16" s="44"/>
+      <c r="BF16" s="40"/>
+      <c r="BG16" s="41"/>
+      <c r="BH16" s="42"/>
+      <c r="BI16" s="42"/>
+      <c r="BJ16" s="42"/>
+      <c r="BK16" s="42"/>
+      <c r="BL16" s="42"/>
+      <c r="BM16" s="42"/>
+      <c r="BN16" s="42"/>
+      <c r="BO16" s="43"/>
+      <c r="BP16" s="43"/>
+      <c r="BQ16" s="44"/>
+      <c r="BR16" s="40"/>
+      <c r="BS16" s="41"/>
+      <c r="BT16" s="42"/>
+      <c r="BU16" s="42"/>
+      <c r="BV16" s="42"/>
+      <c r="BW16" s="42"/>
+      <c r="BX16" s="42"/>
+      <c r="BY16" s="42"/>
+      <c r="BZ16" s="42"/>
+      <c r="CA16" s="43"/>
+      <c r="CB16" s="43"/>
+      <c r="CC16" s="44"/>
+      <c r="CD16" s="40"/>
       <c r="CE16" s="41"/>
-      <c r="CF16" s="33"/>
-      <c r="CG16" s="33"/>
-      <c r="CH16" s="33"/>
-      <c r="CI16" s="33"/>
-      <c r="CJ16" s="33"/>
-      <c r="CK16" s="33"/>
-      <c r="CL16" s="33"/>
-      <c r="CM16" s="35"/>
-      <c r="CN16" s="35"/>
-      <c r="CO16" s="34"/>
-      <c r="CP16" s="31"/>
+      <c r="CF16" s="42"/>
+      <c r="CG16" s="42"/>
+      <c r="CH16" s="42"/>
+      <c r="CI16" s="42"/>
+      <c r="CJ16" s="42"/>
+      <c r="CK16" s="42"/>
+      <c r="CL16" s="42"/>
+      <c r="CM16" s="43"/>
+      <c r="CN16" s="43"/>
+      <c r="CO16" s="44"/>
+      <c r="CP16" s="40"/>
       <c r="CQ16" s="41"/>
-      <c r="CR16" s="33"/>
-      <c r="CS16" s="33"/>
-      <c r="CT16" s="33"/>
-      <c r="CU16" s="33"/>
-      <c r="CV16" s="33"/>
-      <c r="CW16" s="33"/>
-      <c r="CX16" s="33"/>
-      <c r="CY16" s="35"/>
-      <c r="CZ16" s="35"/>
-      <c r="DA16" s="34"/>
-      <c r="DB16" s="28"/>
-      <c r="DC16" s="40"/>
-      <c r="DD16" s="33"/>
-      <c r="DE16" s="33"/>
-      <c r="DF16" s="33"/>
-      <c r="DG16" s="33"/>
-      <c r="DH16" s="33"/>
-      <c r="DI16" s="33"/>
-      <c r="DJ16" s="33"/>
-      <c r="DK16" s="35"/>
-      <c r="DL16" s="35"/>
-      <c r="DM16" s="34"/>
-      <c r="DN16" s="28"/>
-      <c r="DO16" s="40"/>
-      <c r="DP16" s="33"/>
-      <c r="DQ16" s="33"/>
-      <c r="DR16" s="33"/>
-      <c r="DS16" s="33"/>
-      <c r="DT16" s="33"/>
-      <c r="DU16" s="33"/>
-      <c r="DV16" s="33"/>
-      <c r="DW16" s="35"/>
-      <c r="DX16" s="35"/>
-      <c r="DY16" s="34"/>
-      <c r="DZ16" s="28"/>
-      <c r="EA16" s="40"/>
-      <c r="EB16" s="33"/>
-      <c r="EC16" s="33"/>
-      <c r="ED16" s="33"/>
-      <c r="EE16" s="33"/>
-      <c r="EF16" s="33"/>
-      <c r="EG16" s="33"/>
-      <c r="EH16" s="33"/>
-      <c r="EI16" s="35"/>
-      <c r="EJ16" s="35"/>
-      <c r="EK16" s="34"/>
-      <c r="EL16" s="28"/>
-      <c r="EM16" s="40"/>
-      <c r="EN16" s="33"/>
-      <c r="EO16" s="33"/>
-      <c r="EP16" s="33"/>
-      <c r="EQ16" s="33"/>
-      <c r="ER16" s="33"/>
-      <c r="ES16" s="33"/>
-      <c r="ET16" s="33"/>
-      <c r="EU16" s="35"/>
-      <c r="EV16" s="35"/>
-      <c r="EW16" s="34"/>
-      <c r="EX16" s="28"/>
-      <c r="EY16" s="40"/>
-      <c r="EZ16" s="33"/>
-      <c r="FA16" s="33"/>
-      <c r="FB16" s="33"/>
-      <c r="FC16" s="33"/>
-      <c r="FD16" s="33"/>
-      <c r="FE16" s="33"/>
-      <c r="FF16" s="33"/>
-      <c r="FG16" s="35"/>
-      <c r="FH16" s="35"/>
-      <c r="FI16" s="34"/>
+      <c r="CR16" s="42"/>
+      <c r="CS16" s="42"/>
+      <c r="CT16" s="42"/>
+      <c r="CU16" s="42"/>
+      <c r="CV16" s="42"/>
+      <c r="CW16" s="42"/>
+      <c r="CX16" s="42"/>
+      <c r="CY16" s="43"/>
+      <c r="CZ16" s="43"/>
+      <c r="DA16" s="44"/>
+      <c r="DB16" s="40"/>
+      <c r="DC16" s="41"/>
+      <c r="DD16" s="42"/>
+      <c r="DE16" s="42"/>
+      <c r="DF16" s="42"/>
+      <c r="DG16" s="42"/>
+      <c r="DH16" s="42"/>
+      <c r="DI16" s="42"/>
+      <c r="DJ16" s="42"/>
+      <c r="DK16" s="43"/>
+      <c r="DL16" s="43"/>
+      <c r="DM16" s="44"/>
+      <c r="DN16" s="40"/>
+      <c r="DO16" s="41"/>
+      <c r="DP16" s="42"/>
+      <c r="DQ16" s="42"/>
+      <c r="DR16" s="42"/>
+      <c r="DS16" s="42"/>
+      <c r="DT16" s="42"/>
+      <c r="DU16" s="42"/>
+      <c r="DV16" s="42"/>
+      <c r="DW16" s="43"/>
+      <c r="DX16" s="43"/>
+      <c r="DY16" s="44"/>
+      <c r="DZ16" s="40"/>
+      <c r="EA16" s="41"/>
+      <c r="EB16" s="42"/>
+      <c r="EC16" s="42"/>
+      <c r="ED16" s="42"/>
+      <c r="EE16" s="42"/>
+      <c r="EF16" s="42"/>
+      <c r="EG16" s="42"/>
+      <c r="EH16" s="42"/>
+      <c r="EI16" s="43"/>
+      <c r="EJ16" s="43"/>
+      <c r="EK16" s="44"/>
+      <c r="EL16" s="40"/>
+      <c r="EM16" s="41"/>
+      <c r="EN16" s="42"/>
+      <c r="EO16" s="42"/>
+      <c r="EP16" s="42"/>
+      <c r="EQ16" s="42"/>
+      <c r="ER16" s="42"/>
+      <c r="ES16" s="42"/>
+      <c r="ET16" s="42"/>
+      <c r="EU16" s="43"/>
+      <c r="EV16" s="43"/>
+      <c r="EW16" s="44"/>
+      <c r="EX16" s="40"/>
+      <c r="EY16" s="41"/>
+      <c r="EZ16" s="42"/>
+      <c r="FA16" s="42"/>
+      <c r="FB16" s="42"/>
+      <c r="FC16" s="42"/>
+      <c r="FD16" s="42"/>
+      <c r="FE16" s="42"/>
+      <c r="FF16" s="42"/>
+      <c r="FG16" s="43"/>
+      <c r="FH16" s="43"/>
+      <c r="FI16" s="44"/>
     </row>
-    <row r="17" spans="1:165" s="36" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
-      <c r="B17" s="29"/>
-      <c r="C17" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="33"/>
-      <c r="M17" s="33"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="30"/>
-      <c r="T17" s="30"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="W17" s="40"/>
-      <c r="X17" s="33"/>
-      <c r="Y17" s="33"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="33"/>
-      <c r="AB17" s="33"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="33"/>
-      <c r="AE17" s="30"/>
-      <c r="AF17" s="30"/>
-      <c r="AG17" s="34"/>
-      <c r="AH17" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI17" s="40"/>
-      <c r="AJ17" s="33"/>
-      <c r="AK17" s="33"/>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="33"/>
-      <c r="AN17" s="33"/>
-      <c r="AO17" s="33"/>
-      <c r="AP17" s="33"/>
-      <c r="AQ17" s="30"/>
-      <c r="AR17" s="30"/>
-      <c r="AS17" s="34"/>
-      <c r="AT17" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="AU17" s="40"/>
-      <c r="AV17" s="33"/>
-      <c r="AW17" s="33"/>
-      <c r="AX17" s="33"/>
-      <c r="AY17" s="33"/>
-      <c r="AZ17" s="33"/>
-      <c r="BA17" s="33"/>
-      <c r="BB17" s="33"/>
-      <c r="BC17" s="30"/>
-      <c r="BD17" s="30"/>
-      <c r="BE17" s="34"/>
-      <c r="BF17" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="BG17" s="33"/>
-      <c r="BH17" s="33"/>
-      <c r="BI17" s="33"/>
-      <c r="BJ17" s="33"/>
-      <c r="BK17" s="33"/>
-      <c r="BL17" s="33"/>
-      <c r="BM17" s="33"/>
-      <c r="BN17" s="33"/>
-      <c r="BO17" s="30"/>
-      <c r="BP17" s="30"/>
-      <c r="BQ17" s="34"/>
-      <c r="BR17" s="28"/>
-      <c r="BS17" s="40"/>
-      <c r="BT17" s="33"/>
-      <c r="BU17" s="33"/>
-      <c r="BV17" s="33"/>
-      <c r="BW17" s="33"/>
-      <c r="BX17" s="33"/>
-      <c r="BY17" s="33"/>
-      <c r="BZ17" s="33"/>
-      <c r="CA17" s="30"/>
-      <c r="CB17" s="30"/>
-      <c r="CC17" s="34"/>
-      <c r="CD17" s="28"/>
-      <c r="CE17" s="40"/>
-      <c r="CF17" s="33"/>
-      <c r="CG17" s="33"/>
-      <c r="CH17" s="33"/>
-      <c r="CI17" s="33"/>
-      <c r="CJ17" s="33"/>
-      <c r="CK17" s="33"/>
-      <c r="CL17" s="33"/>
-      <c r="CM17" s="35"/>
-      <c r="CN17" s="35"/>
-      <c r="CO17" s="34"/>
-      <c r="CP17" s="28"/>
-      <c r="CQ17" s="40"/>
-      <c r="CR17" s="33"/>
-      <c r="CS17" s="33"/>
-      <c r="CT17" s="33"/>
-      <c r="CU17" s="33"/>
-      <c r="CV17" s="33"/>
-      <c r="CW17" s="33"/>
-      <c r="CX17" s="33"/>
-      <c r="CY17" s="35"/>
-      <c r="CZ17" s="35"/>
-      <c r="DA17" s="34"/>
-      <c r="DB17" s="28"/>
-      <c r="DC17" s="40"/>
-      <c r="DD17" s="33"/>
-      <c r="DE17" s="33"/>
-      <c r="DF17" s="33"/>
-      <c r="DG17" s="33"/>
-      <c r="DH17" s="33"/>
-      <c r="DI17" s="33"/>
-      <c r="DJ17" s="33"/>
-      <c r="DK17" s="35"/>
-      <c r="DL17" s="35"/>
-      <c r="DM17" s="34"/>
-      <c r="DN17" s="28"/>
-      <c r="DO17" s="40"/>
-      <c r="DP17" s="33"/>
-      <c r="DQ17" s="33"/>
-      <c r="DR17" s="33"/>
-      <c r="DS17" s="33"/>
-      <c r="DT17" s="33"/>
-      <c r="DU17" s="33"/>
-      <c r="DV17" s="33"/>
-      <c r="DW17" s="35"/>
-      <c r="DX17" s="35"/>
-      <c r="DY17" s="34"/>
-      <c r="DZ17" s="28"/>
-      <c r="EA17" s="40"/>
-      <c r="EB17" s="33"/>
-      <c r="EC17" s="33"/>
-      <c r="ED17" s="33"/>
-      <c r="EE17" s="33"/>
-      <c r="EF17" s="33"/>
-      <c r="EG17" s="33"/>
-      <c r="EH17" s="33"/>
-      <c r="EI17" s="35"/>
-      <c r="EJ17" s="35"/>
-      <c r="EK17" s="34"/>
-      <c r="EL17" s="28"/>
-      <c r="EM17" s="40"/>
-      <c r="EN17" s="33"/>
-      <c r="EO17" s="33"/>
-      <c r="EP17" s="33"/>
-      <c r="EQ17" s="33"/>
-      <c r="ER17" s="33"/>
-      <c r="ES17" s="33"/>
-      <c r="ET17" s="33"/>
-      <c r="EU17" s="35"/>
-      <c r="EV17" s="35"/>
-      <c r="EW17" s="34"/>
-      <c r="EX17" s="28"/>
-      <c r="EY17" s="40"/>
-      <c r="EZ17" s="33"/>
-      <c r="FA17" s="33"/>
-      <c r="FB17" s="33"/>
-      <c r="FC17" s="33"/>
-      <c r="FD17" s="33"/>
-      <c r="FE17" s="33"/>
-      <c r="FF17" s="33"/>
-      <c r="FG17" s="35"/>
-      <c r="FH17" s="35"/>
-      <c r="FI17" s="34"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="42"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="42"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="42"/>
+      <c r="R17" s="42"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="44"/>
+      <c r="V17" s="40"/>
+      <c r="W17" s="41"/>
+      <c r="X17" s="42"/>
+      <c r="Y17" s="42"/>
+      <c r="Z17" s="42"/>
+      <c r="AA17" s="42"/>
+      <c r="AB17" s="42"/>
+      <c r="AC17" s="42"/>
+      <c r="AD17" s="42"/>
+      <c r="AE17" s="43"/>
+      <c r="AF17" s="43"/>
+      <c r="AG17" s="44"/>
+      <c r="AH17" s="40"/>
+      <c r="AI17" s="41"/>
+      <c r="AJ17" s="42"/>
+      <c r="AK17" s="42"/>
+      <c r="AL17" s="42"/>
+      <c r="AM17" s="42"/>
+      <c r="AN17" s="42"/>
+      <c r="AO17" s="42"/>
+      <c r="AP17" s="42"/>
+      <c r="AQ17" s="43"/>
+      <c r="AR17" s="43"/>
+      <c r="AS17" s="44"/>
+      <c r="AT17" s="40"/>
+      <c r="AU17" s="41"/>
+      <c r="AV17" s="42"/>
+      <c r="AW17" s="42"/>
+      <c r="AX17" s="42"/>
+      <c r="AY17" s="42"/>
+      <c r="AZ17" s="42"/>
+      <c r="BA17" s="42"/>
+      <c r="BB17" s="42"/>
+      <c r="BC17" s="43"/>
+      <c r="BD17" s="43"/>
+      <c r="BE17" s="44"/>
+      <c r="BF17" s="40"/>
+      <c r="BG17" s="41"/>
+      <c r="BH17" s="42"/>
+      <c r="BI17" s="42"/>
+      <c r="BJ17" s="42"/>
+      <c r="BK17" s="42"/>
+      <c r="BL17" s="42"/>
+      <c r="BM17" s="42"/>
+      <c r="BN17" s="42"/>
+      <c r="BO17" s="43"/>
+      <c r="BP17" s="43"/>
+      <c r="BQ17" s="44"/>
+      <c r="BR17" s="40"/>
+      <c r="BS17" s="41"/>
+      <c r="BT17" s="42"/>
+      <c r="BU17" s="42"/>
+      <c r="BV17" s="42"/>
+      <c r="BW17" s="42"/>
+      <c r="BX17" s="42"/>
+      <c r="BY17" s="42"/>
+      <c r="BZ17" s="42"/>
+      <c r="CA17" s="43"/>
+      <c r="CB17" s="43"/>
+      <c r="CC17" s="44"/>
+      <c r="CD17" s="40"/>
+      <c r="CE17" s="41"/>
+      <c r="CF17" s="42"/>
+      <c r="CG17" s="42"/>
+      <c r="CH17" s="42"/>
+      <c r="CI17" s="42"/>
+      <c r="CJ17" s="42"/>
+      <c r="CK17" s="42"/>
+      <c r="CL17" s="42"/>
+      <c r="CM17" s="43"/>
+      <c r="CN17" s="43"/>
+      <c r="CO17" s="44"/>
+      <c r="CP17" s="40"/>
+      <c r="CQ17" s="41"/>
+      <c r="CR17" s="42"/>
+      <c r="CS17" s="42"/>
+      <c r="CT17" s="42"/>
+      <c r="CU17" s="42"/>
+      <c r="CV17" s="42"/>
+      <c r="CW17" s="42"/>
+      <c r="CX17" s="42"/>
+      <c r="CY17" s="43"/>
+      <c r="CZ17" s="43"/>
+      <c r="DA17" s="44"/>
+      <c r="DB17" s="40"/>
+      <c r="DC17" s="41"/>
+      <c r="DD17" s="42"/>
+      <c r="DE17" s="42"/>
+      <c r="DF17" s="42"/>
+      <c r="DG17" s="42"/>
+      <c r="DH17" s="42"/>
+      <c r="DI17" s="42"/>
+      <c r="DJ17" s="42"/>
+      <c r="DK17" s="43"/>
+      <c r="DL17" s="43"/>
+      <c r="DM17" s="44"/>
+      <c r="DN17" s="40"/>
+      <c r="DO17" s="41"/>
+      <c r="DP17" s="42"/>
+      <c r="DQ17" s="42"/>
+      <c r="DR17" s="42"/>
+      <c r="DS17" s="42"/>
+      <c r="DT17" s="42"/>
+      <c r="DU17" s="42"/>
+      <c r="DV17" s="42"/>
+      <c r="DW17" s="43"/>
+      <c r="DX17" s="43"/>
+      <c r="DY17" s="44"/>
+      <c r="DZ17" s="40"/>
+      <c r="EA17" s="41"/>
+      <c r="EB17" s="42"/>
+      <c r="EC17" s="42"/>
+      <c r="ED17" s="42"/>
+      <c r="EE17" s="42"/>
+      <c r="EF17" s="42"/>
+      <c r="EG17" s="42"/>
+      <c r="EH17" s="42"/>
+      <c r="EI17" s="43"/>
+      <c r="EJ17" s="43"/>
+      <c r="EK17" s="44"/>
+      <c r="EL17" s="40"/>
+      <c r="EM17" s="41"/>
+      <c r="EN17" s="42"/>
+      <c r="EO17" s="42"/>
+      <c r="EP17" s="42"/>
+      <c r="EQ17" s="42"/>
+      <c r="ER17" s="42"/>
+      <c r="ES17" s="42"/>
+      <c r="ET17" s="42"/>
+      <c r="EU17" s="43"/>
+      <c r="EV17" s="43"/>
+      <c r="EW17" s="44"/>
+      <c r="EX17" s="40"/>
+      <c r="EY17" s="41"/>
+      <c r="EZ17" s="42"/>
+      <c r="FA17" s="42"/>
+      <c r="FB17" s="42"/>
+      <c r="FC17" s="42"/>
+      <c r="FD17" s="42"/>
+      <c r="FE17" s="42"/>
+      <c r="FF17" s="42"/>
+      <c r="FG17" s="43"/>
+      <c r="FH17" s="43"/>
+      <c r="FI17" s="44"/>
     </row>
-    <row r="18" spans="1:165" s="36" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A18" s="1"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="K18" s="40"/>
-      <c r="L18" s="33"/>
-      <c r="M18" s="33"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="30"/>
-      <c r="T18" s="30"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="31" t="s">
-        <v>65</v>
-      </c>
+      <c r="B18" s="23"/>
+      <c r="C18" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="42"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="42"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="42"/>
+      <c r="R18" s="42"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="44"/>
+      <c r="V18" s="40"/>
       <c r="W18" s="41"/>
-      <c r="X18" s="33"/>
-      <c r="Y18" s="33"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="33"/>
-      <c r="AB18" s="33"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="33"/>
-      <c r="AE18" s="30"/>
-      <c r="AF18" s="30"/>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI18" s="40"/>
-      <c r="AJ18" s="33"/>
-      <c r="AK18" s="33"/>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="33"/>
-      <c r="AN18" s="33"/>
-      <c r="AO18" s="33"/>
-      <c r="AP18" s="33"/>
-      <c r="AQ18" s="30"/>
-      <c r="AR18" s="30"/>
-      <c r="AS18" s="34"/>
-      <c r="AT18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="AU18" s="40"/>
-      <c r="AV18" s="33"/>
-      <c r="AW18" s="33"/>
-      <c r="AX18" s="33"/>
-      <c r="AY18" s="33"/>
-      <c r="AZ18" s="33"/>
-      <c r="BA18" s="33"/>
-      <c r="BB18" s="33"/>
-      <c r="BC18" s="30"/>
-      <c r="BD18" s="30"/>
-      <c r="BE18" s="34"/>
-      <c r="BF18" s="31" t="s">
-        <v>64</v>
-      </c>
-      <c r="BG18" s="33"/>
-      <c r="BH18" s="33"/>
-      <c r="BI18" s="33"/>
-      <c r="BJ18" s="33"/>
-      <c r="BK18" s="33"/>
-      <c r="BL18" s="33"/>
-      <c r="BM18" s="33"/>
-      <c r="BN18" s="33"/>
-      <c r="BO18" s="30"/>
-      <c r="BP18" s="30"/>
-      <c r="BQ18" s="34"/>
-      <c r="BR18" s="31"/>
-      <c r="BS18" s="40"/>
-      <c r="BT18" s="33"/>
-      <c r="BU18" s="33"/>
-      <c r="BV18" s="33"/>
-      <c r="BW18" s="33"/>
-      <c r="BX18" s="33"/>
-      <c r="BY18" s="33"/>
-      <c r="BZ18" s="33"/>
-      <c r="CA18" s="30"/>
-      <c r="CB18" s="30"/>
-      <c r="CC18" s="34"/>
-      <c r="CD18" s="31"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="43"/>
+      <c r="AF18" s="43"/>
+      <c r="AG18" s="44"/>
+      <c r="AH18" s="40"/>
+      <c r="AI18" s="41"/>
+      <c r="AJ18" s="42"/>
+      <c r="AK18" s="42"/>
+      <c r="AL18" s="42"/>
+      <c r="AM18" s="42"/>
+      <c r="AN18" s="42"/>
+      <c r="AO18" s="42"/>
+      <c r="AP18" s="42"/>
+      <c r="AQ18" s="43"/>
+      <c r="AR18" s="43"/>
+      <c r="AS18" s="44"/>
+      <c r="AT18" s="40"/>
+      <c r="AU18" s="41"/>
+      <c r="AV18" s="42"/>
+      <c r="AW18" s="42"/>
+      <c r="AX18" s="42"/>
+      <c r="AY18" s="42"/>
+      <c r="AZ18" s="42"/>
+      <c r="BA18" s="42"/>
+      <c r="BB18" s="42"/>
+      <c r="BC18" s="43"/>
+      <c r="BD18" s="43"/>
+      <c r="BE18" s="44"/>
+      <c r="BF18" s="40"/>
+      <c r="BG18" s="41"/>
+      <c r="BH18" s="42"/>
+      <c r="BI18" s="42"/>
+      <c r="BJ18" s="42"/>
+      <c r="BK18" s="42"/>
+      <c r="BL18" s="42"/>
+      <c r="BM18" s="42"/>
+      <c r="BN18" s="42"/>
+      <c r="BO18" s="43"/>
+      <c r="BP18" s="43"/>
+      <c r="BQ18" s="44"/>
+      <c r="BR18" s="40"/>
+      <c r="BS18" s="41"/>
+      <c r="BT18" s="42"/>
+      <c r="BU18" s="42"/>
+      <c r="BV18" s="42"/>
+      <c r="BW18" s="42"/>
+      <c r="BX18" s="42"/>
+      <c r="BY18" s="42"/>
+      <c r="BZ18" s="42"/>
+      <c r="CA18" s="43"/>
+      <c r="CB18" s="43"/>
+      <c r="CC18" s="44"/>
+      <c r="CD18" s="40"/>
       <c r="CE18" s="41"/>
-      <c r="CF18" s="33"/>
-      <c r="CG18" s="33"/>
-      <c r="CH18" s="33"/>
-      <c r="CI18" s="33"/>
-      <c r="CJ18" s="33"/>
-      <c r="CK18" s="33"/>
-      <c r="CL18" s="33"/>
-      <c r="CM18" s="35"/>
-      <c r="CN18" s="35"/>
-      <c r="CO18" s="34"/>
-      <c r="CP18" s="31"/>
+      <c r="CF18" s="42"/>
+      <c r="CG18" s="42"/>
+      <c r="CH18" s="42"/>
+      <c r="CI18" s="42"/>
+      <c r="CJ18" s="42"/>
+      <c r="CK18" s="42"/>
+      <c r="CL18" s="42"/>
+      <c r="CM18" s="43"/>
+      <c r="CN18" s="43"/>
+      <c r="CO18" s="44"/>
+      <c r="CP18" s="40"/>
       <c r="CQ18" s="41"/>
-      <c r="CR18" s="33"/>
-      <c r="CS18" s="33"/>
-      <c r="CT18" s="33"/>
-      <c r="CU18" s="33"/>
-      <c r="CV18" s="33"/>
-      <c r="CW18" s="33"/>
-      <c r="CX18" s="33"/>
-      <c r="CY18" s="35"/>
-      <c r="CZ18" s="35"/>
-      <c r="DA18" s="34"/>
-      <c r="DB18" s="28"/>
-      <c r="DC18" s="40"/>
-      <c r="DD18" s="33"/>
-      <c r="DE18" s="33"/>
-      <c r="DF18" s="33"/>
-      <c r="DG18" s="33"/>
-      <c r="DH18" s="33"/>
-      <c r="DI18" s="33"/>
-      <c r="DJ18" s="33"/>
-      <c r="DK18" s="35"/>
-      <c r="DL18" s="35"/>
-      <c r="DM18" s="34"/>
-      <c r="DN18" s="28"/>
-      <c r="DO18" s="40"/>
-      <c r="DP18" s="33"/>
-      <c r="DQ18" s="33"/>
-      <c r="DR18" s="33"/>
-      <c r="DS18" s="33"/>
-      <c r="DT18" s="33"/>
-      <c r="DU18" s="33"/>
-      <c r="DV18" s="33"/>
-      <c r="DW18" s="35"/>
-      <c r="DX18" s="35"/>
-      <c r="DY18" s="34"/>
-      <c r="DZ18" s="28"/>
-      <c r="EA18" s="40"/>
-      <c r="EB18" s="33"/>
-      <c r="EC18" s="33"/>
-      <c r="ED18" s="33"/>
-      <c r="EE18" s="33"/>
-      <c r="EF18" s="33"/>
-      <c r="EG18" s="33"/>
-      <c r="EH18" s="33"/>
-      <c r="EI18" s="35"/>
-      <c r="EJ18" s="35"/>
-      <c r="EK18" s="34"/>
-      <c r="EL18" s="28"/>
-      <c r="EM18" s="40"/>
-      <c r="EN18" s="33"/>
-      <c r="EO18" s="33"/>
-      <c r="EP18" s="33"/>
-      <c r="EQ18" s="33"/>
-      <c r="ER18" s="33"/>
-      <c r="ES18" s="33"/>
-      <c r="ET18" s="33"/>
-      <c r="EU18" s="35"/>
-      <c r="EV18" s="35"/>
-      <c r="EW18" s="34"/>
-      <c r="EX18" s="28"/>
-      <c r="EY18" s="40"/>
-      <c r="EZ18" s="33"/>
-      <c r="FA18" s="33"/>
-      <c r="FB18" s="33"/>
-      <c r="FC18" s="33"/>
-      <c r="FD18" s="33"/>
-      <c r="FE18" s="33"/>
-      <c r="FF18" s="33"/>
-      <c r="FG18" s="35"/>
-      <c r="FH18" s="35"/>
-      <c r="FI18" s="34"/>
+      <c r="CR18" s="42"/>
+      <c r="CS18" s="42"/>
+      <c r="CT18" s="42"/>
+      <c r="CU18" s="42"/>
+      <c r="CV18" s="42"/>
+      <c r="CW18" s="42"/>
+      <c r="CX18" s="42"/>
+      <c r="CY18" s="43"/>
+      <c r="CZ18" s="43"/>
+      <c r="DA18" s="44"/>
+      <c r="DB18" s="40"/>
+      <c r="DC18" s="41"/>
+      <c r="DD18" s="42"/>
+      <c r="DE18" s="42"/>
+      <c r="DF18" s="42"/>
+      <c r="DG18" s="42"/>
+      <c r="DH18" s="42"/>
+      <c r="DI18" s="42"/>
+      <c r="DJ18" s="42"/>
+      <c r="DK18" s="43"/>
+      <c r="DL18" s="43"/>
+      <c r="DM18" s="44"/>
+      <c r="DN18" s="40"/>
+      <c r="DO18" s="41"/>
+      <c r="DP18" s="42"/>
+      <c r="DQ18" s="42"/>
+      <c r="DR18" s="42"/>
+      <c r="DS18" s="42"/>
+      <c r="DT18" s="42"/>
+      <c r="DU18" s="42"/>
+      <c r="DV18" s="42"/>
+      <c r="DW18" s="43"/>
+      <c r="DX18" s="43"/>
+      <c r="DY18" s="44"/>
+      <c r="DZ18" s="40"/>
+      <c r="EA18" s="41"/>
+      <c r="EB18" s="42"/>
+      <c r="EC18" s="42"/>
+      <c r="ED18" s="42"/>
+      <c r="EE18" s="42"/>
+      <c r="EF18" s="42"/>
+      <c r="EG18" s="42"/>
+      <c r="EH18" s="42"/>
+      <c r="EI18" s="43"/>
+      <c r="EJ18" s="43"/>
+      <c r="EK18" s="44"/>
+      <c r="EL18" s="40"/>
+      <c r="EM18" s="41"/>
+      <c r="EN18" s="42"/>
+      <c r="EO18" s="42"/>
+      <c r="EP18" s="42"/>
+      <c r="EQ18" s="42"/>
+      <c r="ER18" s="42"/>
+      <c r="ES18" s="42"/>
+      <c r="ET18" s="42"/>
+      <c r="EU18" s="43"/>
+      <c r="EV18" s="43"/>
+      <c r="EW18" s="44"/>
+      <c r="EX18" s="40"/>
+      <c r="EY18" s="41"/>
+      <c r="EZ18" s="42"/>
+      <c r="FA18" s="42"/>
+      <c r="FB18" s="42"/>
+      <c r="FC18" s="42"/>
+      <c r="FD18" s="42"/>
+      <c r="FE18" s="42"/>
+      <c r="FF18" s="42"/>
+      <c r="FG18" s="43"/>
+      <c r="FH18" s="43"/>
+      <c r="FI18" s="44"/>
     </row>
-    <row r="19" spans="1:165" s="36" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A19" s="1"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="K19" s="40"/>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="30"/>
-      <c r="T19" s="30"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="W19" s="40"/>
-      <c r="X19" s="33"/>
-      <c r="Y19" s="33"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="33"/>
-      <c r="AB19" s="33"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="33"/>
-      <c r="AE19" s="30"/>
-      <c r="AF19" s="30"/>
-      <c r="AG19" s="34"/>
-      <c r="AH19" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI19" s="40"/>
-      <c r="AJ19" s="33"/>
-      <c r="AK19" s="33"/>
-      <c r="AL19" s="33"/>
-      <c r="AM19" s="33"/>
-      <c r="AN19" s="33"/>
-      <c r="AO19" s="33"/>
-      <c r="AP19" s="33"/>
-      <c r="AQ19" s="30"/>
-      <c r="AR19" s="30"/>
-      <c r="AS19" s="34"/>
-      <c r="AT19" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="AU19" s="40"/>
-      <c r="AV19" s="33"/>
-      <c r="AW19" s="33"/>
-      <c r="AX19" s="33"/>
-      <c r="AY19" s="33"/>
-      <c r="AZ19" s="33"/>
-      <c r="BA19" s="33"/>
-      <c r="BB19" s="33"/>
-      <c r="BC19" s="30"/>
-      <c r="BD19" s="30"/>
-      <c r="BE19" s="34"/>
-      <c r="BF19" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="BG19" s="33"/>
-      <c r="BH19" s="33"/>
-      <c r="BI19" s="33"/>
-      <c r="BJ19" s="33"/>
-      <c r="BK19" s="33"/>
-      <c r="BL19" s="33"/>
-      <c r="BM19" s="33"/>
-      <c r="BN19" s="33"/>
-      <c r="BO19" s="30"/>
-      <c r="BP19" s="30"/>
-      <c r="BQ19" s="34"/>
-      <c r="BR19" s="31"/>
-      <c r="BS19" s="40"/>
-      <c r="BT19" s="33"/>
-      <c r="BU19" s="33"/>
-      <c r="BV19" s="33"/>
-      <c r="BW19" s="33"/>
-      <c r="BX19" s="33"/>
-      <c r="BY19" s="33"/>
-      <c r="BZ19" s="33"/>
-      <c r="CA19" s="30"/>
-      <c r="CB19" s="30"/>
-      <c r="CC19" s="34"/>
-      <c r="CD19" s="31"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="41"/>
+      <c r="L19" s="42"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="42"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="44"/>
+      <c r="V19" s="40"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="42"/>
+      <c r="Y19" s="42"/>
+      <c r="Z19" s="42"/>
+      <c r="AA19" s="42"/>
+      <c r="AB19" s="42"/>
+      <c r="AC19" s="42"/>
+      <c r="AD19" s="42"/>
+      <c r="AE19" s="43"/>
+      <c r="AF19" s="43"/>
+      <c r="AG19" s="44"/>
+      <c r="AH19" s="40"/>
+      <c r="AI19" s="41"/>
+      <c r="AJ19" s="42"/>
+      <c r="AK19" s="42"/>
+      <c r="AL19" s="42"/>
+      <c r="AM19" s="42"/>
+      <c r="AN19" s="42"/>
+      <c r="AO19" s="42"/>
+      <c r="AP19" s="42"/>
+      <c r="AQ19" s="43"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="44"/>
+      <c r="AT19" s="40"/>
+      <c r="AU19" s="41"/>
+      <c r="AV19" s="42"/>
+      <c r="AW19" s="42"/>
+      <c r="AX19" s="42"/>
+      <c r="AY19" s="42"/>
+      <c r="AZ19" s="42"/>
+      <c r="BA19" s="42"/>
+      <c r="BB19" s="42"/>
+      <c r="BC19" s="43"/>
+      <c r="BD19" s="43"/>
+      <c r="BE19" s="44"/>
+      <c r="BF19" s="40"/>
+      <c r="BG19" s="41"/>
+      <c r="BH19" s="42"/>
+      <c r="BI19" s="42"/>
+      <c r="BJ19" s="42"/>
+      <c r="BK19" s="42"/>
+      <c r="BL19" s="42"/>
+      <c r="BM19" s="42"/>
+      <c r="BN19" s="42"/>
+      <c r="BO19" s="43"/>
+      <c r="BP19" s="43"/>
+      <c r="BQ19" s="44"/>
+      <c r="BR19" s="40"/>
+      <c r="BS19" s="41"/>
+      <c r="BT19" s="42"/>
+      <c r="BU19" s="42"/>
+      <c r="BV19" s="42"/>
+      <c r="BW19" s="42"/>
+      <c r="BX19" s="42"/>
+      <c r="BY19" s="42"/>
+      <c r="BZ19" s="42"/>
+      <c r="CA19" s="43"/>
+      <c r="CB19" s="43"/>
+      <c r="CC19" s="44"/>
+      <c r="CD19" s="40"/>
       <c r="CE19" s="41"/>
-      <c r="CF19" s="33"/>
-      <c r="CG19" s="33"/>
-      <c r="CH19" s="33"/>
-      <c r="CI19" s="33"/>
-      <c r="CJ19" s="33"/>
-      <c r="CK19" s="33"/>
-      <c r="CL19" s="33"/>
-      <c r="CM19" s="35"/>
-      <c r="CN19" s="35"/>
-      <c r="CO19" s="34"/>
-      <c r="CP19" s="28"/>
-      <c r="CQ19" s="40"/>
-      <c r="CR19" s="33"/>
-      <c r="CS19" s="33"/>
-      <c r="CT19" s="33"/>
-      <c r="CU19" s="33"/>
-      <c r="CV19" s="33"/>
-      <c r="CW19" s="33"/>
-      <c r="CX19" s="33"/>
-      <c r="CY19" s="35"/>
-      <c r="CZ19" s="35"/>
-      <c r="DA19" s="34"/>
-      <c r="DB19" s="28"/>
-      <c r="DC19" s="40"/>
-      <c r="DD19" s="33"/>
-      <c r="DE19" s="33"/>
-      <c r="DF19" s="33"/>
-      <c r="DG19" s="33"/>
-      <c r="DH19" s="33"/>
-      <c r="DI19" s="33"/>
-      <c r="DJ19" s="33"/>
-      <c r="DK19" s="35"/>
-      <c r="DL19" s="35"/>
-      <c r="DM19" s="34"/>
-      <c r="DN19" s="28"/>
-      <c r="DO19" s="40"/>
-      <c r="DP19" s="33"/>
-      <c r="DQ19" s="33"/>
-      <c r="DR19" s="33"/>
-      <c r="DS19" s="33"/>
-      <c r="DT19" s="33"/>
-      <c r="DU19" s="33"/>
-      <c r="DV19" s="33"/>
-      <c r="DW19" s="35"/>
-      <c r="DX19" s="35"/>
-      <c r="DY19" s="34"/>
-      <c r="DZ19" s="28"/>
-      <c r="EA19" s="40"/>
-      <c r="EB19" s="33"/>
-      <c r="EC19" s="33"/>
-      <c r="ED19" s="33"/>
-      <c r="EE19" s="33"/>
-      <c r="EF19" s="33"/>
-      <c r="EG19" s="33"/>
-      <c r="EH19" s="33"/>
-      <c r="EI19" s="35"/>
-      <c r="EJ19" s="35"/>
-      <c r="EK19" s="34"/>
-      <c r="EL19" s="28"/>
-      <c r="EM19" s="40"/>
-      <c r="EN19" s="33"/>
-      <c r="EO19" s="33"/>
-      <c r="EP19" s="33"/>
-      <c r="EQ19" s="33"/>
-      <c r="ER19" s="33"/>
-      <c r="ES19" s="33"/>
-      <c r="ET19" s="33"/>
-      <c r="EU19" s="35"/>
-      <c r="EV19" s="35"/>
-      <c r="EW19" s="34"/>
-      <c r="EX19" s="28"/>
-      <c r="EY19" s="40"/>
-      <c r="EZ19" s="33"/>
-      <c r="FA19" s="33"/>
-      <c r="FB19" s="33"/>
-      <c r="FC19" s="33"/>
-      <c r="FD19" s="33"/>
-      <c r="FE19" s="33"/>
-      <c r="FF19" s="33"/>
-      <c r="FG19" s="35"/>
-      <c r="FH19" s="35"/>
-      <c r="FI19" s="34"/>
+      <c r="CF19" s="42"/>
+      <c r="CG19" s="42"/>
+      <c r="CH19" s="42"/>
+      <c r="CI19" s="42"/>
+      <c r="CJ19" s="42"/>
+      <c r="CK19" s="42"/>
+      <c r="CL19" s="42"/>
+      <c r="CM19" s="43"/>
+      <c r="CN19" s="43"/>
+      <c r="CO19" s="44"/>
+      <c r="CP19" s="40"/>
+      <c r="CQ19" s="41"/>
+      <c r="CR19" s="42"/>
+      <c r="CS19" s="42"/>
+      <c r="CT19" s="42"/>
+      <c r="CU19" s="42"/>
+      <c r="CV19" s="42"/>
+      <c r="CW19" s="42"/>
+      <c r="CX19" s="42"/>
+      <c r="CY19" s="43"/>
+      <c r="CZ19" s="43"/>
+      <c r="DA19" s="44"/>
+      <c r="DB19" s="40"/>
+      <c r="DC19" s="41"/>
+      <c r="DD19" s="42"/>
+      <c r="DE19" s="42"/>
+      <c r="DF19" s="42"/>
+      <c r="DG19" s="42"/>
+      <c r="DH19" s="42"/>
+      <c r="DI19" s="42"/>
+      <c r="DJ19" s="42"/>
+      <c r="DK19" s="43"/>
+      <c r="DL19" s="43"/>
+      <c r="DM19" s="44"/>
+      <c r="DN19" s="40"/>
+      <c r="DO19" s="41"/>
+      <c r="DP19" s="42"/>
+      <c r="DQ19" s="42"/>
+      <c r="DR19" s="42"/>
+      <c r="DS19" s="42"/>
+      <c r="DT19" s="42"/>
+      <c r="DU19" s="42"/>
+      <c r="DV19" s="42"/>
+      <c r="DW19" s="43"/>
+      <c r="DX19" s="43"/>
+      <c r="DY19" s="44"/>
+      <c r="DZ19" s="40"/>
+      <c r="EA19" s="41"/>
+      <c r="EB19" s="42"/>
+      <c r="EC19" s="42"/>
+      <c r="ED19" s="42"/>
+      <c r="EE19" s="42"/>
+      <c r="EF19" s="42"/>
+      <c r="EG19" s="42"/>
+      <c r="EH19" s="42"/>
+      <c r="EI19" s="43"/>
+      <c r="EJ19" s="43"/>
+      <c r="EK19" s="44"/>
+      <c r="EL19" s="40"/>
+      <c r="EM19" s="41"/>
+      <c r="EN19" s="42"/>
+      <c r="EO19" s="42"/>
+      <c r="EP19" s="42"/>
+      <c r="EQ19" s="42"/>
+      <c r="ER19" s="42"/>
+      <c r="ES19" s="42"/>
+      <c r="ET19" s="42"/>
+      <c r="EU19" s="43"/>
+      <c r="EV19" s="43"/>
+      <c r="EW19" s="44"/>
+      <c r="EX19" s="40"/>
+      <c r="EY19" s="41"/>
+      <c r="EZ19" s="42"/>
+      <c r="FA19" s="42"/>
+      <c r="FB19" s="42"/>
+      <c r="FC19" s="42"/>
+      <c r="FD19" s="42"/>
+      <c r="FE19" s="42"/>
+      <c r="FF19" s="42"/>
+      <c r="FG19" s="43"/>
+      <c r="FH19" s="43"/>
+      <c r="FI19" s="44"/>
     </row>
-    <row r="20" spans="1:165" s="36" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:165" s="26" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" s="40"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="28" t="s">
-        <v>69</v>
-      </c>
+      <c r="B20" s="23"/>
+      <c r="C20" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="42"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="42"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="44"/>
+      <c r="V20" s="40"/>
       <c r="W20" s="41"/>
-      <c r="X20" s="33"/>
-      <c r="Y20" s="33"/>
-      <c r="Z20" s="33"/>
-      <c r="AA20" s="33"/>
-      <c r="AB20" s="33"/>
-      <c r="AC20" s="33"/>
-      <c r="AD20" s="33"/>
-      <c r="AE20" s="30"/>
-      <c r="AF20" s="30"/>
-      <c r="AG20" s="34"/>
-      <c r="AH20" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI20" s="40"/>
-      <c r="AJ20" s="33"/>
-      <c r="AK20" s="33"/>
-      <c r="AL20" s="33"/>
-      <c r="AM20" s="33"/>
-      <c r="AN20" s="33"/>
-      <c r="AO20" s="33"/>
-      <c r="AP20" s="33"/>
-      <c r="AQ20" s="30"/>
-      <c r="AR20" s="30"/>
-      <c r="AS20" s="34"/>
-      <c r="AT20" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="AU20" s="40"/>
-      <c r="AV20" s="33"/>
-      <c r="AW20" s="33"/>
-      <c r="AX20" s="33"/>
-      <c r="AY20" s="33"/>
-      <c r="AZ20" s="33"/>
-      <c r="BA20" s="33"/>
-      <c r="BB20" s="33"/>
-      <c r="BC20" s="30"/>
-      <c r="BD20" s="30"/>
-      <c r="BE20" s="34"/>
-      <c r="BF20" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="BG20" s="33"/>
-      <c r="BH20" s="33"/>
-      <c r="BI20" s="33"/>
-      <c r="BJ20" s="33"/>
-      <c r="BK20" s="33"/>
-      <c r="BL20" s="33"/>
-      <c r="BM20" s="33"/>
-      <c r="BN20" s="33"/>
-      <c r="BO20" s="30"/>
-      <c r="BP20" s="30"/>
-      <c r="BQ20" s="34"/>
-      <c r="BR20" s="31"/>
-      <c r="BS20" s="40"/>
-      <c r="BT20" s="33"/>
-      <c r="BU20" s="33"/>
-      <c r="BV20" s="33"/>
-      <c r="BW20" s="33"/>
-      <c r="BX20" s="33"/>
-      <c r="BY20" s="33"/>
-      <c r="BZ20" s="33"/>
-      <c r="CA20" s="30"/>
-      <c r="CB20" s="30"/>
-      <c r="CC20" s="34"/>
-      <c r="CD20" s="31"/>
+      <c r="X20" s="42"/>
+      <c r="Y20" s="42"/>
+      <c r="Z20" s="42"/>
+      <c r="AA20" s="42"/>
+      <c r="AB20" s="42"/>
+      <c r="AC20" s="42"/>
+      <c r="AD20" s="42"/>
+      <c r="AE20" s="43"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="44"/>
+      <c r="AH20" s="40"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="42"/>
+      <c r="AK20" s="42"/>
+      <c r="AL20" s="42"/>
+      <c r="AM20" s="42"/>
+      <c r="AN20" s="42"/>
+      <c r="AO20" s="42"/>
+      <c r="AP20" s="42"/>
+      <c r="AQ20" s="43"/>
+      <c r="AR20" s="43"/>
+      <c r="AS20" s="44"/>
+      <c r="AT20" s="40"/>
+      <c r="AU20" s="41"/>
+      <c r="AV20" s="42"/>
+      <c r="AW20" s="42"/>
+      <c r="AX20" s="42"/>
+      <c r="AY20" s="42"/>
+      <c r="AZ20" s="42"/>
+      <c r="BA20" s="42"/>
+      <c r="BB20" s="42"/>
+      <c r="BC20" s="43"/>
+      <c r="BD20" s="43"/>
+      <c r="BE20" s="44"/>
+      <c r="BF20" s="40"/>
+      <c r="BG20" s="41"/>
+      <c r="BH20" s="42"/>
+      <c r="BI20" s="42"/>
+      <c r="BJ20" s="42"/>
+      <c r="BK20" s="42"/>
+      <c r="BL20" s="42"/>
+      <c r="BM20" s="42"/>
+      <c r="BN20" s="42"/>
+      <c r="BO20" s="43"/>
+      <c r="BP20" s="43"/>
+      <c r="BQ20" s="44"/>
+      <c r="BR20" s="40"/>
+      <c r="BS20" s="41"/>
+      <c r="BT20" s="42"/>
+      <c r="BU20" s="42"/>
+      <c r="BV20" s="42"/>
+      <c r="BW20" s="42"/>
+      <c r="BX20" s="42"/>
+      <c r="BY20" s="42"/>
+      <c r="BZ20" s="42"/>
+      <c r="CA20" s="43"/>
+      <c r="CB20" s="43"/>
+      <c r="CC20" s="44"/>
+      <c r="CD20" s="40"/>
       <c r="CE20" s="41"/>
-      <c r="CF20" s="33"/>
-      <c r="CG20" s="33"/>
-      <c r="CH20" s="33"/>
-      <c r="CI20" s="33"/>
-      <c r="CJ20" s="33"/>
-      <c r="CK20" s="33"/>
-      <c r="CL20" s="33"/>
-      <c r="CM20" s="35"/>
-      <c r="CN20" s="35"/>
-      <c r="CO20" s="34"/>
-      <c r="CP20" s="28"/>
-      <c r="CQ20" s="40"/>
-      <c r="CR20" s="33"/>
-      <c r="CS20" s="33"/>
-      <c r="CT20" s="33"/>
-      <c r="CU20" s="33"/>
-      <c r="CV20" s="33"/>
-      <c r="CW20" s="33"/>
-      <c r="CX20" s="33"/>
-      <c r="CY20" s="35"/>
-      <c r="CZ20" s="35"/>
-      <c r="DA20" s="34"/>
-      <c r="DB20" s="28"/>
-      <c r="DC20" s="40"/>
-      <c r="DD20" s="33"/>
-      <c r="DE20" s="33"/>
-      <c r="DF20" s="33"/>
-      <c r="DG20" s="33"/>
-      <c r="DH20" s="33"/>
-      <c r="DI20" s="33"/>
-      <c r="DJ20" s="33"/>
-      <c r="DK20" s="35"/>
-      <c r="DL20" s="35"/>
-      <c r="DM20" s="34"/>
-      <c r="DN20" s="28"/>
-      <c r="DO20" s="40"/>
-      <c r="DP20" s="33"/>
-      <c r="DQ20" s="33"/>
-      <c r="DR20" s="33"/>
-      <c r="DS20" s="33"/>
-      <c r="DT20" s="33"/>
-      <c r="DU20" s="33"/>
-      <c r="DV20" s="33"/>
-      <c r="DW20" s="35"/>
-      <c r="DX20" s="35"/>
-      <c r="DY20" s="34"/>
-      <c r="DZ20" s="28"/>
-      <c r="EA20" s="40"/>
-      <c r="EB20" s="33"/>
-      <c r="EC20" s="33"/>
-      <c r="ED20" s="33"/>
-      <c r="EE20" s="33"/>
-      <c r="EF20" s="33"/>
-      <c r="EG20" s="33"/>
-      <c r="EH20" s="33"/>
-      <c r="EI20" s="35"/>
-      <c r="EJ20" s="35"/>
-      <c r="EK20" s="34"/>
-      <c r="EL20" s="28"/>
-      <c r="EM20" s="40"/>
-      <c r="EN20" s="33"/>
-      <c r="EO20" s="33"/>
-      <c r="EP20" s="33"/>
-      <c r="EQ20" s="33"/>
-      <c r="ER20" s="33"/>
-      <c r="ES20" s="33"/>
-      <c r="ET20" s="33"/>
-      <c r="EU20" s="35"/>
-      <c r="EV20" s="35"/>
-      <c r="EW20" s="34"/>
-      <c r="EX20" s="28"/>
-      <c r="EY20" s="40"/>
-      <c r="EZ20" s="33"/>
-      <c r="FA20" s="33"/>
-      <c r="FB20" s="33"/>
-      <c r="FC20" s="33"/>
-      <c r="FD20" s="33"/>
-      <c r="FE20" s="33"/>
-      <c r="FF20" s="33"/>
-      <c r="FG20" s="35"/>
-      <c r="FH20" s="35"/>
-      <c r="FI20" s="34"/>
+      <c r="CF20" s="42"/>
+      <c r="CG20" s="42"/>
+      <c r="CH20" s="42"/>
+      <c r="CI20" s="42"/>
+      <c r="CJ20" s="42"/>
+      <c r="CK20" s="42"/>
+      <c r="CL20" s="42"/>
+      <c r="CM20" s="43"/>
+      <c r="CN20" s="43"/>
+      <c r="CO20" s="44"/>
+      <c r="CP20" s="40"/>
+      <c r="CQ20" s="41"/>
+      <c r="CR20" s="42"/>
+      <c r="CS20" s="42"/>
+      <c r="CT20" s="42"/>
+      <c r="CU20" s="42"/>
+      <c r="CV20" s="42"/>
+      <c r="CW20" s="42"/>
+      <c r="CX20" s="42"/>
+      <c r="CY20" s="43"/>
+      <c r="CZ20" s="43"/>
+      <c r="DA20" s="44"/>
+      <c r="DB20" s="40"/>
+      <c r="DC20" s="41"/>
+      <c r="DD20" s="42"/>
+      <c r="DE20" s="42"/>
+      <c r="DF20" s="42"/>
+      <c r="DG20" s="42"/>
+      <c r="DH20" s="42"/>
+      <c r="DI20" s="42"/>
+      <c r="DJ20" s="42"/>
+      <c r="DK20" s="43"/>
+      <c r="DL20" s="43"/>
+      <c r="DM20" s="44"/>
+      <c r="DN20" s="40"/>
+      <c r="DO20" s="41"/>
+      <c r="DP20" s="42"/>
+      <c r="DQ20" s="42"/>
+      <c r="DR20" s="42"/>
+      <c r="DS20" s="42"/>
+      <c r="DT20" s="42"/>
+      <c r="DU20" s="42"/>
+      <c r="DV20" s="42"/>
+      <c r="DW20" s="43"/>
+      <c r="DX20" s="43"/>
+      <c r="DY20" s="44"/>
+      <c r="DZ20" s="40"/>
+      <c r="EA20" s="41"/>
+      <c r="EB20" s="42"/>
+      <c r="EC20" s="42"/>
+      <c r="ED20" s="42"/>
+      <c r="EE20" s="42"/>
+      <c r="EF20" s="42"/>
+      <c r="EG20" s="42"/>
+      <c r="EH20" s="42"/>
+      <c r="EI20" s="43"/>
+      <c r="EJ20" s="43"/>
+      <c r="EK20" s="44"/>
+      <c r="EL20" s="40"/>
+      <c r="EM20" s="41"/>
+      <c r="EN20" s="42"/>
+      <c r="EO20" s="42"/>
+      <c r="EP20" s="42"/>
+      <c r="EQ20" s="42"/>
+      <c r="ER20" s="42"/>
+      <c r="ES20" s="42"/>
+      <c r="ET20" s="42"/>
+      <c r="EU20" s="43"/>
+      <c r="EV20" s="43"/>
+      <c r="EW20" s="44"/>
+      <c r="EX20" s="40"/>
+      <c r="EY20" s="41"/>
+      <c r="EZ20" s="42"/>
+      <c r="FA20" s="42"/>
+      <c r="FB20" s="42"/>
+      <c r="FC20" s="42"/>
+      <c r="FD20" s="42"/>
+      <c r="FE20" s="42"/>
+      <c r="FF20" s="42"/>
+      <c r="FG20" s="43"/>
+      <c r="FH20" s="43"/>
+      <c r="FI20" s="44"/>
     </row>
     <row r="21" spans="1:165" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
-      <c r="B21" s="84" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="80" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="81"/>
-      <c r="J21" s="59" t="s">
-        <v>82</v>
-      </c>
-      <c r="K21" s="60"/>
-      <c r="L21" s="61"/>
-      <c r="M21" s="61"/>
-      <c r="N21" s="61"/>
-      <c r="O21" s="61"/>
-      <c r="P21" s="61"/>
-      <c r="Q21" s="61"/>
-      <c r="R21" s="61"/>
-      <c r="S21" s="62"/>
-      <c r="T21" s="62"/>
-      <c r="U21" s="63"/>
-      <c r="V21" s="59" t="s">
-        <v>72</v>
-      </c>
-      <c r="W21" s="60"/>
-      <c r="X21" s="61"/>
-      <c r="Y21" s="61"/>
-      <c r="Z21" s="61"/>
-      <c r="AA21" s="61"/>
-      <c r="AB21" s="61"/>
-      <c r="AC21" s="61"/>
-      <c r="AD21" s="61"/>
-      <c r="AE21" s="62"/>
-      <c r="AF21" s="62"/>
-      <c r="AG21" s="63"/>
-      <c r="AH21" s="59" t="s">
-        <v>71</v>
-      </c>
-      <c r="AI21" s="60"/>
-      <c r="AJ21" s="61"/>
-      <c r="AK21" s="61"/>
-      <c r="AL21" s="61"/>
-      <c r="AM21" s="61"/>
-      <c r="AN21" s="61"/>
-      <c r="AO21" s="61"/>
-      <c r="AP21" s="61"/>
-      <c r="AQ21" s="62"/>
-      <c r="AR21" s="62"/>
-      <c r="AS21" s="63"/>
-      <c r="AT21" s="59" t="s">
-        <v>83</v>
-      </c>
-      <c r="AU21" s="60"/>
-      <c r="AV21" s="61"/>
-      <c r="AW21" s="61"/>
-      <c r="AX21" s="61"/>
-      <c r="AY21" s="61"/>
-      <c r="AZ21" s="61"/>
-      <c r="BA21" s="61"/>
-      <c r="BB21" s="61"/>
-      <c r="BC21" s="62"/>
-      <c r="BD21" s="62"/>
-      <c r="BE21" s="63"/>
-      <c r="BF21" s="59" t="s">
-        <v>79</v>
-      </c>
-      <c r="BG21" s="61"/>
-      <c r="BH21" s="61"/>
-      <c r="BI21" s="61"/>
-      <c r="BJ21" s="61"/>
-      <c r="BK21" s="61"/>
-      <c r="BL21" s="61"/>
-      <c r="BM21" s="61"/>
-      <c r="BN21" s="61"/>
-      <c r="BO21" s="62"/>
-      <c r="BP21" s="62"/>
-      <c r="BQ21" s="63"/>
-      <c r="BR21" s="59"/>
-      <c r="BS21" s="60"/>
-      <c r="BT21" s="61"/>
-      <c r="BU21" s="61"/>
-      <c r="BV21" s="61"/>
-      <c r="BW21" s="61"/>
-      <c r="BX21" s="61"/>
-      <c r="BY21" s="61"/>
-      <c r="BZ21" s="61"/>
-      <c r="CA21" s="62"/>
-      <c r="CB21" s="62"/>
-      <c r="CC21" s="63"/>
-      <c r="CD21" s="59"/>
-      <c r="CE21" s="60"/>
-      <c r="CF21" s="61"/>
-      <c r="CG21" s="61"/>
-      <c r="CH21" s="61"/>
-      <c r="CI21" s="61"/>
-      <c r="CJ21" s="61"/>
-      <c r="CK21" s="61"/>
-      <c r="CL21" s="61"/>
-      <c r="CM21" s="62"/>
-      <c r="CN21" s="62"/>
-      <c r="CO21" s="63"/>
-      <c r="CP21" s="59"/>
-      <c r="CQ21" s="60"/>
-      <c r="CR21" s="61"/>
-      <c r="CS21" s="61"/>
-      <c r="CT21" s="61"/>
-      <c r="CU21" s="61"/>
-      <c r="CV21" s="61"/>
-      <c r="CW21" s="61"/>
-      <c r="CX21" s="61"/>
-      <c r="CY21" s="62"/>
-      <c r="CZ21" s="62"/>
-      <c r="DA21" s="63"/>
-      <c r="DB21" s="59"/>
-      <c r="DC21" s="60"/>
-      <c r="DD21" s="61"/>
-      <c r="DE21" s="61"/>
-      <c r="DF21" s="61"/>
-      <c r="DG21" s="61"/>
-      <c r="DH21" s="61"/>
-      <c r="DI21" s="61"/>
-      <c r="DJ21" s="61"/>
-      <c r="DK21" s="62"/>
-      <c r="DL21" s="62"/>
-      <c r="DM21" s="63"/>
-      <c r="DN21" s="69"/>
-      <c r="DO21" s="70"/>
-      <c r="DP21" s="71"/>
-      <c r="DQ21" s="71"/>
-      <c r="DR21" s="71"/>
-      <c r="DS21" s="71"/>
-      <c r="DT21" s="71"/>
-      <c r="DU21" s="71"/>
-      <c r="DV21" s="71"/>
-      <c r="DW21" s="72"/>
-      <c r="DX21" s="72"/>
-      <c r="DY21" s="73"/>
-      <c r="DZ21" s="69"/>
-      <c r="EA21" s="71"/>
-      <c r="EB21" s="71"/>
-      <c r="EC21" s="71"/>
-      <c r="ED21" s="71"/>
-      <c r="EE21" s="71"/>
-      <c r="EF21" s="71"/>
-      <c r="EG21" s="71"/>
-      <c r="EH21" s="71"/>
-      <c r="EI21" s="72"/>
-      <c r="EJ21" s="72"/>
-      <c r="EK21" s="73"/>
-      <c r="EL21" s="69"/>
-      <c r="EM21" s="71"/>
-      <c r="EN21" s="71"/>
-      <c r="EO21" s="71"/>
-      <c r="EP21" s="71"/>
-      <c r="EQ21" s="71"/>
-      <c r="ER21" s="71"/>
-      <c r="ES21" s="71"/>
-      <c r="ET21" s="71"/>
-      <c r="EU21" s="72"/>
-      <c r="EV21" s="72"/>
-      <c r="EW21" s="73"/>
-      <c r="EX21" s="69"/>
-      <c r="EY21" s="71"/>
-      <c r="EZ21" s="71"/>
-      <c r="FA21" s="71"/>
-      <c r="FB21" s="71"/>
-      <c r="FC21" s="71"/>
-      <c r="FD21" s="71"/>
-      <c r="FE21" s="71"/>
-      <c r="FF21" s="71"/>
-      <c r="FG21" s="72"/>
-      <c r="FH21" s="72"/>
-      <c r="FI21" s="73"/>
+      <c r="B21" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="68"/>
+      <c r="D21" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E21" s="65"/>
+      <c r="F21" s="65"/>
+      <c r="G21" s="65"/>
+      <c r="H21" s="65"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="50"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="52"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="50"/>
+      <c r="Y21" s="50"/>
+      <c r="Z21" s="50"/>
+      <c r="AA21" s="50"/>
+      <c r="AB21" s="50"/>
+      <c r="AC21" s="50"/>
+      <c r="AD21" s="50"/>
+      <c r="AE21" s="51"/>
+      <c r="AF21" s="51"/>
+      <c r="AG21" s="52"/>
+      <c r="AH21" s="48"/>
+      <c r="AI21" s="49"/>
+      <c r="AJ21" s="50"/>
+      <c r="AK21" s="50"/>
+      <c r="AL21" s="50"/>
+      <c r="AM21" s="50"/>
+      <c r="AN21" s="50"/>
+      <c r="AO21" s="50"/>
+      <c r="AP21" s="50"/>
+      <c r="AQ21" s="51"/>
+      <c r="AR21" s="51"/>
+      <c r="AS21" s="52"/>
+      <c r="AT21" s="48"/>
+      <c r="AU21" s="49"/>
+      <c r="AV21" s="50"/>
+      <c r="AW21" s="50"/>
+      <c r="AX21" s="50"/>
+      <c r="AY21" s="50"/>
+      <c r="AZ21" s="50"/>
+      <c r="BA21" s="50"/>
+      <c r="BB21" s="50"/>
+      <c r="BC21" s="51"/>
+      <c r="BD21" s="51"/>
+      <c r="BE21" s="52"/>
+      <c r="BF21" s="48"/>
+      <c r="BG21" s="49"/>
+      <c r="BH21" s="50"/>
+      <c r="BI21" s="50"/>
+      <c r="BJ21" s="50"/>
+      <c r="BK21" s="50"/>
+      <c r="BL21" s="50"/>
+      <c r="BM21" s="50"/>
+      <c r="BN21" s="50"/>
+      <c r="BO21" s="51"/>
+      <c r="BP21" s="51"/>
+      <c r="BQ21" s="52"/>
+      <c r="BR21" s="48"/>
+      <c r="BS21" s="49"/>
+      <c r="BT21" s="50"/>
+      <c r="BU21" s="50"/>
+      <c r="BV21" s="50"/>
+      <c r="BW21" s="50"/>
+      <c r="BX21" s="50"/>
+      <c r="BY21" s="50"/>
+      <c r="BZ21" s="50"/>
+      <c r="CA21" s="51"/>
+      <c r="CB21" s="51"/>
+      <c r="CC21" s="52"/>
+      <c r="CD21" s="48"/>
+      <c r="CE21" s="49"/>
+      <c r="CF21" s="50"/>
+      <c r="CG21" s="50"/>
+      <c r="CH21" s="50"/>
+      <c r="CI21" s="50"/>
+      <c r="CJ21" s="50"/>
+      <c r="CK21" s="50"/>
+      <c r="CL21" s="50"/>
+      <c r="CM21" s="51"/>
+      <c r="CN21" s="51"/>
+      <c r="CO21" s="52"/>
+      <c r="CP21" s="48"/>
+      <c r="CQ21" s="49"/>
+      <c r="CR21" s="50"/>
+      <c r="CS21" s="50"/>
+      <c r="CT21" s="50"/>
+      <c r="CU21" s="50"/>
+      <c r="CV21" s="50"/>
+      <c r="CW21" s="50"/>
+      <c r="CX21" s="50"/>
+      <c r="CY21" s="51"/>
+      <c r="CZ21" s="51"/>
+      <c r="DA21" s="52"/>
+      <c r="DB21" s="48"/>
+      <c r="DC21" s="49"/>
+      <c r="DD21" s="50"/>
+      <c r="DE21" s="50"/>
+      <c r="DF21" s="50"/>
+      <c r="DG21" s="50"/>
+      <c r="DH21" s="50"/>
+      <c r="DI21" s="50"/>
+      <c r="DJ21" s="50"/>
+      <c r="DK21" s="51"/>
+      <c r="DL21" s="51"/>
+      <c r="DM21" s="52"/>
+      <c r="DN21" s="48"/>
+      <c r="DO21" s="49"/>
+      <c r="DP21" s="50"/>
+      <c r="DQ21" s="50"/>
+      <c r="DR21" s="50"/>
+      <c r="DS21" s="50"/>
+      <c r="DT21" s="50"/>
+      <c r="DU21" s="50"/>
+      <c r="DV21" s="50"/>
+      <c r="DW21" s="51"/>
+      <c r="DX21" s="51"/>
+      <c r="DY21" s="52"/>
+      <c r="DZ21" s="48"/>
+      <c r="EA21" s="49"/>
+      <c r="EB21" s="50"/>
+      <c r="EC21" s="50"/>
+      <c r="ED21" s="50"/>
+      <c r="EE21" s="50"/>
+      <c r="EF21" s="50"/>
+      <c r="EG21" s="50"/>
+      <c r="EH21" s="50"/>
+      <c r="EI21" s="51"/>
+      <c r="EJ21" s="51"/>
+      <c r="EK21" s="52"/>
+      <c r="EL21" s="48"/>
+      <c r="EM21" s="49"/>
+      <c r="EN21" s="50"/>
+      <c r="EO21" s="50"/>
+      <c r="EP21" s="50"/>
+      <c r="EQ21" s="50"/>
+      <c r="ER21" s="50"/>
+      <c r="ES21" s="50"/>
+      <c r="ET21" s="50"/>
+      <c r="EU21" s="51"/>
+      <c r="EV21" s="51"/>
+      <c r="EW21" s="52"/>
+      <c r="EX21" s="48"/>
+      <c r="EY21" s="49"/>
+      <c r="EZ21" s="50"/>
+      <c r="FA21" s="50"/>
+      <c r="FB21" s="50"/>
+      <c r="FC21" s="50"/>
+      <c r="FD21" s="50"/>
+      <c r="FE21" s="50"/>
+      <c r="FF21" s="50"/>
+      <c r="FG21" s="51"/>
+      <c r="FH21" s="51"/>
+      <c r="FI21" s="52"/>
     </row>
-    <row r="22" spans="1:165" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
-      <c r="B22" s="90"/>
-      <c r="C22" s="91"/>
-      <c r="D22" s="82" t="s">
+      <c r="B22" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="E22" s="82"/>
-      <c r="F22" s="82"/>
-      <c r="G22" s="82"/>
-      <c r="H22" s="82"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="85">
-        <v>4</v>
-      </c>
-      <c r="K22" s="89"/>
-      <c r="L22" s="86"/>
-      <c r="M22" s="86"/>
-      <c r="N22" s="86"/>
-      <c r="O22" s="86"/>
-      <c r="P22" s="86"/>
-      <c r="Q22" s="86"/>
-      <c r="R22" s="86"/>
-      <c r="S22" s="87"/>
-      <c r="T22" s="87"/>
-      <c r="U22" s="88"/>
-      <c r="V22" s="85">
-        <v>4.5</v>
-      </c>
-      <c r="W22" s="89"/>
-      <c r="X22" s="86"/>
-      <c r="Y22" s="86"/>
-      <c r="Z22" s="86"/>
-      <c r="AA22" s="86"/>
-      <c r="AB22" s="86"/>
-      <c r="AC22" s="86"/>
-      <c r="AD22" s="86"/>
-      <c r="AE22" s="87"/>
-      <c r="AF22" s="87"/>
-      <c r="AG22" s="88"/>
-      <c r="AH22" s="85">
-        <v>4.95</v>
-      </c>
-      <c r="AI22" s="89"/>
-      <c r="AJ22" s="86"/>
-      <c r="AK22" s="86"/>
-      <c r="AL22" s="86"/>
-      <c r="AM22" s="86"/>
-      <c r="AN22" s="86"/>
-      <c r="AO22" s="86"/>
-      <c r="AP22" s="86"/>
-      <c r="AQ22" s="87"/>
-      <c r="AR22" s="87"/>
-      <c r="AS22" s="88"/>
-      <c r="AT22" s="85">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="AU22" s="89"/>
-      <c r="AV22" s="86"/>
-      <c r="AW22" s="86"/>
-      <c r="AX22" s="86"/>
-      <c r="AY22" s="86"/>
-      <c r="AZ22" s="86"/>
-      <c r="BA22" s="86"/>
-      <c r="BB22" s="86"/>
-      <c r="BC22" s="87"/>
-      <c r="BD22" s="87"/>
-      <c r="BE22" s="88"/>
-      <c r="BF22" s="85">
-        <v>1.5</v>
-      </c>
-      <c r="BG22" s="86"/>
-      <c r="BH22" s="86"/>
-      <c r="BI22" s="86"/>
-      <c r="BJ22" s="86"/>
-      <c r="BK22" s="86"/>
-      <c r="BL22" s="86"/>
-      <c r="BM22" s="86"/>
-      <c r="BN22" s="86"/>
-      <c r="BO22" s="87"/>
-      <c r="BP22" s="87"/>
-      <c r="BQ22" s="88"/>
-      <c r="BR22" s="85">
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="62">
         <v>0</v>
       </c>
-      <c r="BS22" s="89"/>
-      <c r="BT22" s="86"/>
-      <c r="BU22" s="86"/>
-      <c r="BV22" s="86"/>
-      <c r="BW22" s="86"/>
-      <c r="BX22" s="86"/>
-      <c r="BY22" s="86"/>
-      <c r="BZ22" s="86"/>
-      <c r="CA22" s="87"/>
-      <c r="CB22" s="87"/>
-      <c r="CC22" s="88"/>
-      <c r="CD22" s="85">
+      <c r="K22" s="62"/>
+      <c r="L22" s="62"/>
+      <c r="M22" s="62"/>
+      <c r="N22" s="62"/>
+      <c r="O22" s="62"/>
+      <c r="P22" s="62"/>
+      <c r="Q22" s="62"/>
+      <c r="R22" s="62"/>
+      <c r="S22" s="62"/>
+      <c r="T22" s="62"/>
+      <c r="U22" s="62"/>
+      <c r="V22" s="62">
         <v>0</v>
       </c>
-      <c r="CE22" s="89"/>
-      <c r="CF22" s="86"/>
-      <c r="CG22" s="86"/>
-      <c r="CH22" s="86"/>
-      <c r="CI22" s="86"/>
-      <c r="CJ22" s="86"/>
-      <c r="CK22" s="86"/>
-      <c r="CL22" s="86"/>
-      <c r="CM22" s="87"/>
-      <c r="CN22" s="87"/>
-      <c r="CO22" s="88"/>
-      <c r="CP22" s="85">
+      <c r="W22" s="62"/>
+      <c r="X22" s="62"/>
+      <c r="Y22" s="62"/>
+      <c r="Z22" s="62"/>
+      <c r="AA22" s="62"/>
+      <c r="AB22" s="62"/>
+      <c r="AC22" s="62"/>
+      <c r="AD22" s="62"/>
+      <c r="AE22" s="62"/>
+      <c r="AF22" s="62"/>
+      <c r="AG22" s="62"/>
+      <c r="AH22" s="62">
         <v>0</v>
       </c>
-      <c r="CQ22" s="89"/>
-      <c r="CR22" s="86"/>
-      <c r="CS22" s="86"/>
-      <c r="CT22" s="86"/>
-      <c r="CU22" s="86"/>
-      <c r="CV22" s="86"/>
-      <c r="CW22" s="86"/>
-      <c r="CX22" s="86"/>
-      <c r="CY22" s="87"/>
-      <c r="CZ22" s="87"/>
-      <c r="DA22" s="88"/>
-      <c r="DB22" s="85">
+      <c r="AI22" s="62"/>
+      <c r="AJ22" s="62"/>
+      <c r="AK22" s="62"/>
+      <c r="AL22" s="62"/>
+      <c r="AM22" s="62"/>
+      <c r="AN22" s="62"/>
+      <c r="AO22" s="62"/>
+      <c r="AP22" s="62"/>
+      <c r="AQ22" s="62"/>
+      <c r="AR22" s="62"/>
+      <c r="AS22" s="62"/>
+      <c r="AT22" s="62">
         <v>0</v>
       </c>
-      <c r="DC22" s="89"/>
-      <c r="DD22" s="86"/>
-      <c r="DE22" s="86"/>
-      <c r="DF22" s="86"/>
-      <c r="DG22" s="86"/>
-      <c r="DH22" s="86"/>
-      <c r="DI22" s="86"/>
-      <c r="DJ22" s="86"/>
-      <c r="DK22" s="87"/>
-      <c r="DL22" s="87"/>
-      <c r="DM22" s="88"/>
-      <c r="DN22" s="85">
+      <c r="AU22" s="62"/>
+      <c r="AV22" s="62"/>
+      <c r="AW22" s="62"/>
+      <c r="AX22" s="62"/>
+      <c r="AY22" s="62"/>
+      <c r="AZ22" s="62"/>
+      <c r="BA22" s="62"/>
+      <c r="BB22" s="62"/>
+      <c r="BC22" s="62"/>
+      <c r="BD22" s="62"/>
+      <c r="BE22" s="62"/>
+      <c r="BF22" s="62">
         <v>0</v>
       </c>
-      <c r="DO22" s="89"/>
-      <c r="DP22" s="86"/>
-      <c r="DQ22" s="86"/>
-      <c r="DR22" s="86"/>
-      <c r="DS22" s="86"/>
-      <c r="DT22" s="86"/>
-      <c r="DU22" s="86"/>
-      <c r="DV22" s="86"/>
-      <c r="DW22" s="87"/>
-      <c r="DX22" s="87"/>
-      <c r="DY22" s="88"/>
-      <c r="DZ22" s="85">
+      <c r="BG22" s="62"/>
+      <c r="BH22" s="62"/>
+      <c r="BI22" s="62"/>
+      <c r="BJ22" s="62"/>
+      <c r="BK22" s="62"/>
+      <c r="BL22" s="62"/>
+      <c r="BM22" s="62"/>
+      <c r="BN22" s="62"/>
+      <c r="BO22" s="62"/>
+      <c r="BP22" s="62"/>
+      <c r="BQ22" s="62"/>
+      <c r="BR22" s="62">
         <v>0</v>
       </c>
-      <c r="EA22" s="86"/>
-      <c r="EB22" s="86"/>
-      <c r="EC22" s="86"/>
-      <c r="ED22" s="86"/>
-      <c r="EE22" s="86"/>
-      <c r="EF22" s="86"/>
-      <c r="EG22" s="86"/>
-      <c r="EH22" s="86"/>
-      <c r="EI22" s="87"/>
-      <c r="EJ22" s="87"/>
-      <c r="EK22" s="88"/>
-      <c r="EL22" s="85">
+      <c r="BS22" s="62"/>
+      <c r="BT22" s="62"/>
+      <c r="BU22" s="62"/>
+      <c r="BV22" s="62"/>
+      <c r="BW22" s="62"/>
+      <c r="BX22" s="62"/>
+      <c r="BY22" s="62"/>
+      <c r="BZ22" s="62"/>
+      <c r="CA22" s="62"/>
+      <c r="CB22" s="62"/>
+      <c r="CC22" s="62"/>
+      <c r="CD22" s="62">
         <v>0</v>
       </c>
-      <c r="EM22" s="86"/>
-      <c r="EN22" s="86"/>
-      <c r="EO22" s="86"/>
-      <c r="EP22" s="86"/>
-      <c r="EQ22" s="86"/>
-      <c r="ER22" s="86"/>
-      <c r="ES22" s="86"/>
-      <c r="ET22" s="86"/>
-      <c r="EU22" s="87"/>
-      <c r="EV22" s="87"/>
-      <c r="EW22" s="88"/>
-      <c r="EX22" s="85">
+      <c r="CE22" s="62"/>
+      <c r="CF22" s="62"/>
+      <c r="CG22" s="62"/>
+      <c r="CH22" s="62"/>
+      <c r="CI22" s="62"/>
+      <c r="CJ22" s="62"/>
+      <c r="CK22" s="62"/>
+      <c r="CL22" s="62"/>
+      <c r="CM22" s="62"/>
+      <c r="CN22" s="62"/>
+      <c r="CO22" s="62"/>
+      <c r="CP22" s="62">
         <v>0</v>
       </c>
-      <c r="EY22" s="86"/>
-      <c r="EZ22" s="86"/>
-      <c r="FA22" s="86"/>
-      <c r="FB22" s="86"/>
-      <c r="FC22" s="86"/>
-      <c r="FD22" s="86"/>
-      <c r="FE22" s="86"/>
-      <c r="FF22" s="86"/>
-      <c r="FG22" s="87"/>
-      <c r="FH22" s="87"/>
-      <c r="FI22" s="88"/>
+      <c r="CQ22" s="62"/>
+      <c r="CR22" s="62"/>
+      <c r="CS22" s="62"/>
+      <c r="CT22" s="62"/>
+      <c r="CU22" s="62"/>
+      <c r="CV22" s="62"/>
+      <c r="CW22" s="62"/>
+      <c r="CX22" s="62"/>
+      <c r="CY22" s="62"/>
+      <c r="CZ22" s="62"/>
+      <c r="DA22" s="62"/>
+      <c r="DB22" s="62">
+        <v>0</v>
+      </c>
+      <c r="DC22" s="62"/>
+      <c r="DD22" s="62"/>
+      <c r="DE22" s="62"/>
+      <c r="DF22" s="62"/>
+      <c r="DG22" s="62"/>
+      <c r="DH22" s="62"/>
+      <c r="DI22" s="62"/>
+      <c r="DJ22" s="62"/>
+      <c r="DK22" s="62"/>
+      <c r="DL22" s="62"/>
+      <c r="DM22" s="62"/>
+      <c r="DN22" s="62">
+        <v>0</v>
+      </c>
+      <c r="DO22" s="62"/>
+      <c r="DP22" s="62"/>
+      <c r="DQ22" s="62"/>
+      <c r="DR22" s="62"/>
+      <c r="DS22" s="62"/>
+      <c r="DT22" s="62"/>
+      <c r="DU22" s="62"/>
+      <c r="DV22" s="62"/>
+      <c r="DW22" s="62"/>
+      <c r="DX22" s="62"/>
+      <c r="DY22" s="62"/>
+      <c r="DZ22" s="62">
+        <v>0</v>
+      </c>
+      <c r="EA22" s="62"/>
+      <c r="EB22" s="62"/>
+      <c r="EC22" s="62"/>
+      <c r="ED22" s="62"/>
+      <c r="EE22" s="62"/>
+      <c r="EF22" s="62"/>
+      <c r="EG22" s="62"/>
+      <c r="EH22" s="62"/>
+      <c r="EI22" s="62"/>
+      <c r="EJ22" s="62"/>
+      <c r="EK22" s="62"/>
+      <c r="EL22" s="62">
+        <v>0</v>
+      </c>
+      <c r="EM22" s="62"/>
+      <c r="EN22" s="62"/>
+      <c r="EO22" s="62"/>
+      <c r="EP22" s="62"/>
+      <c r="EQ22" s="62"/>
+      <c r="ER22" s="62"/>
+      <c r="ES22" s="62"/>
+      <c r="ET22" s="62"/>
+      <c r="EU22" s="62"/>
+      <c r="EV22" s="62"/>
+      <c r="EW22" s="62"/>
+      <c r="EX22" s="62">
+        <v>0</v>
+      </c>
+      <c r="EY22" s="62"/>
+      <c r="EZ22" s="62"/>
+      <c r="FA22" s="62"/>
+      <c r="FB22" s="62"/>
+      <c r="FC22" s="62"/>
+      <c r="FD22" s="62"/>
+      <c r="FE22" s="62"/>
+      <c r="FF22" s="62"/>
+      <c r="FG22" s="62"/>
+      <c r="FH22" s="62"/>
+      <c r="FI22" s="62"/>
     </row>
     <row r="23" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="5"/>
@@ -12567,8 +11251,8 @@
     <mergeCell ref="V22:AG22"/>
     <mergeCell ref="D2:I2"/>
     <mergeCell ref="D21:I21"/>
-    <mergeCell ref="D22:I22"/>
     <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:I22"/>
     <mergeCell ref="DN21:DY21"/>
     <mergeCell ref="DZ21:EK21"/>
     <mergeCell ref="EL21:EW21"/>

--- a/activity/M01A02/M01A02.xlsx
+++ b/activity/M01A02/M01A02.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E3A540-9D6A-4FF0-BF10-CFE8BB7812E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CBDD0B-4909-4CB1-82F0-B00015EE8819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -1322,19 +1322,19 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1352,20 +1352,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2447,15 +2447,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>57065</xdr:colOff>
+      <xdr:colOff>57064</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>14883</xdr:rowOff>
+      <xdr:rowOff>14882</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>123065</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>78590</xdr:rowOff>
+      <xdr:colOff>149689</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>108656</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3305,10 +3305,10 @@
     </row>
     <row r="2" spans="1:165" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="51" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="63" t="s">
@@ -3516,8 +3516,8 @@
       <c r="FI2" s="57"/>
     </row>
     <row r="3" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="59"/>
-      <c r="C3" s="61"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="52"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -7060,162 +7060,162 @@
       <c r="G21" s="65"/>
       <c r="H21" s="65"/>
       <c r="I21" s="66"/>
-      <c r="J21" s="48"/>
-      <c r="K21" s="49"/>
-      <c r="L21" s="50"/>
-      <c r="M21" s="50"/>
-      <c r="N21" s="50"/>
-      <c r="O21" s="50"/>
-      <c r="P21" s="50"/>
-      <c r="Q21" s="50"/>
-      <c r="R21" s="50"/>
-      <c r="S21" s="51"/>
-      <c r="T21" s="51"/>
-      <c r="U21" s="52"/>
-      <c r="V21" s="48"/>
-      <c r="W21" s="49"/>
-      <c r="X21" s="50"/>
-      <c r="Y21" s="50"/>
-      <c r="Z21" s="50"/>
-      <c r="AA21" s="50"/>
-      <c r="AB21" s="50"/>
-      <c r="AC21" s="50"/>
-      <c r="AD21" s="50"/>
-      <c r="AE21" s="51"/>
-      <c r="AF21" s="51"/>
-      <c r="AG21" s="52"/>
-      <c r="AH21" s="48"/>
-      <c r="AI21" s="49"/>
-      <c r="AJ21" s="50"/>
-      <c r="AK21" s="50"/>
-      <c r="AL21" s="50"/>
-      <c r="AM21" s="50"/>
-      <c r="AN21" s="50"/>
-      <c r="AO21" s="50"/>
-      <c r="AP21" s="50"/>
-      <c r="AQ21" s="51"/>
-      <c r="AR21" s="51"/>
-      <c r="AS21" s="52"/>
-      <c r="AT21" s="48"/>
-      <c r="AU21" s="49"/>
-      <c r="AV21" s="50"/>
-      <c r="AW21" s="50"/>
-      <c r="AX21" s="50"/>
-      <c r="AY21" s="50"/>
-      <c r="AZ21" s="50"/>
-      <c r="BA21" s="50"/>
-      <c r="BB21" s="50"/>
-      <c r="BC21" s="51"/>
-      <c r="BD21" s="51"/>
-      <c r="BE21" s="52"/>
-      <c r="BF21" s="48"/>
-      <c r="BG21" s="49"/>
-      <c r="BH21" s="50"/>
-      <c r="BI21" s="50"/>
-      <c r="BJ21" s="50"/>
-      <c r="BK21" s="50"/>
-      <c r="BL21" s="50"/>
-      <c r="BM21" s="50"/>
-      <c r="BN21" s="50"/>
-      <c r="BO21" s="51"/>
-      <c r="BP21" s="51"/>
-      <c r="BQ21" s="52"/>
-      <c r="BR21" s="48"/>
-      <c r="BS21" s="49"/>
-      <c r="BT21" s="50"/>
-      <c r="BU21" s="50"/>
-      <c r="BV21" s="50"/>
-      <c r="BW21" s="50"/>
-      <c r="BX21" s="50"/>
-      <c r="BY21" s="50"/>
-      <c r="BZ21" s="50"/>
-      <c r="CA21" s="51"/>
-      <c r="CB21" s="51"/>
-      <c r="CC21" s="52"/>
-      <c r="CD21" s="48"/>
-      <c r="CE21" s="49"/>
-      <c r="CF21" s="50"/>
-      <c r="CG21" s="50"/>
-      <c r="CH21" s="50"/>
-      <c r="CI21" s="50"/>
-      <c r="CJ21" s="50"/>
-      <c r="CK21" s="50"/>
-      <c r="CL21" s="50"/>
-      <c r="CM21" s="51"/>
-      <c r="CN21" s="51"/>
-      <c r="CO21" s="52"/>
-      <c r="CP21" s="48"/>
-      <c r="CQ21" s="49"/>
-      <c r="CR21" s="50"/>
-      <c r="CS21" s="50"/>
-      <c r="CT21" s="50"/>
-      <c r="CU21" s="50"/>
-      <c r="CV21" s="50"/>
-      <c r="CW21" s="50"/>
-      <c r="CX21" s="50"/>
-      <c r="CY21" s="51"/>
-      <c r="CZ21" s="51"/>
-      <c r="DA21" s="52"/>
-      <c r="DB21" s="48"/>
-      <c r="DC21" s="49"/>
-      <c r="DD21" s="50"/>
-      <c r="DE21" s="50"/>
-      <c r="DF21" s="50"/>
-      <c r="DG21" s="50"/>
-      <c r="DH21" s="50"/>
-      <c r="DI21" s="50"/>
-      <c r="DJ21" s="50"/>
-      <c r="DK21" s="51"/>
-      <c r="DL21" s="51"/>
-      <c r="DM21" s="52"/>
-      <c r="DN21" s="48"/>
-      <c r="DO21" s="49"/>
-      <c r="DP21" s="50"/>
-      <c r="DQ21" s="50"/>
-      <c r="DR21" s="50"/>
-      <c r="DS21" s="50"/>
-      <c r="DT21" s="50"/>
-      <c r="DU21" s="50"/>
-      <c r="DV21" s="50"/>
-      <c r="DW21" s="51"/>
-      <c r="DX21" s="51"/>
-      <c r="DY21" s="52"/>
-      <c r="DZ21" s="48"/>
-      <c r="EA21" s="49"/>
-      <c r="EB21" s="50"/>
-      <c r="EC21" s="50"/>
-      <c r="ED21" s="50"/>
-      <c r="EE21" s="50"/>
-      <c r="EF21" s="50"/>
-      <c r="EG21" s="50"/>
-      <c r="EH21" s="50"/>
-      <c r="EI21" s="51"/>
-      <c r="EJ21" s="51"/>
-      <c r="EK21" s="52"/>
-      <c r="EL21" s="48"/>
-      <c r="EM21" s="49"/>
-      <c r="EN21" s="50"/>
-      <c r="EO21" s="50"/>
-      <c r="EP21" s="50"/>
-      <c r="EQ21" s="50"/>
-      <c r="ER21" s="50"/>
-      <c r="ES21" s="50"/>
-      <c r="ET21" s="50"/>
-      <c r="EU21" s="51"/>
-      <c r="EV21" s="51"/>
-      <c r="EW21" s="52"/>
-      <c r="EX21" s="48"/>
-      <c r="EY21" s="49"/>
-      <c r="EZ21" s="50"/>
-      <c r="FA21" s="50"/>
-      <c r="FB21" s="50"/>
-      <c r="FC21" s="50"/>
-      <c r="FD21" s="50"/>
-      <c r="FE21" s="50"/>
-      <c r="FF21" s="50"/>
-      <c r="FG21" s="51"/>
-      <c r="FH21" s="51"/>
-      <c r="FI21" s="52"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="59"/>
+      <c r="L21" s="60"/>
+      <c r="M21" s="60"/>
+      <c r="N21" s="60"/>
+      <c r="O21" s="60"/>
+      <c r="P21" s="60"/>
+      <c r="Q21" s="60"/>
+      <c r="R21" s="60"/>
+      <c r="S21" s="61"/>
+      <c r="T21" s="61"/>
+      <c r="U21" s="62"/>
+      <c r="V21" s="58"/>
+      <c r="W21" s="59"/>
+      <c r="X21" s="60"/>
+      <c r="Y21" s="60"/>
+      <c r="Z21" s="60"/>
+      <c r="AA21" s="60"/>
+      <c r="AB21" s="60"/>
+      <c r="AC21" s="60"/>
+      <c r="AD21" s="60"/>
+      <c r="AE21" s="61"/>
+      <c r="AF21" s="61"/>
+      <c r="AG21" s="62"/>
+      <c r="AH21" s="58"/>
+      <c r="AI21" s="59"/>
+      <c r="AJ21" s="60"/>
+      <c r="AK21" s="60"/>
+      <c r="AL21" s="60"/>
+      <c r="AM21" s="60"/>
+      <c r="AN21" s="60"/>
+      <c r="AO21" s="60"/>
+      <c r="AP21" s="60"/>
+      <c r="AQ21" s="61"/>
+      <c r="AR21" s="61"/>
+      <c r="AS21" s="62"/>
+      <c r="AT21" s="58"/>
+      <c r="AU21" s="59"/>
+      <c r="AV21" s="60"/>
+      <c r="AW21" s="60"/>
+      <c r="AX21" s="60"/>
+      <c r="AY21" s="60"/>
+      <c r="AZ21" s="60"/>
+      <c r="BA21" s="60"/>
+      <c r="BB21" s="60"/>
+      <c r="BC21" s="61"/>
+      <c r="BD21" s="61"/>
+      <c r="BE21" s="62"/>
+      <c r="BF21" s="58"/>
+      <c r="BG21" s="59"/>
+      <c r="BH21" s="60"/>
+      <c r="BI21" s="60"/>
+      <c r="BJ21" s="60"/>
+      <c r="BK21" s="60"/>
+      <c r="BL21" s="60"/>
+      <c r="BM21" s="60"/>
+      <c r="BN21" s="60"/>
+      <c r="BO21" s="61"/>
+      <c r="BP21" s="61"/>
+      <c r="BQ21" s="62"/>
+      <c r="BR21" s="58"/>
+      <c r="BS21" s="59"/>
+      <c r="BT21" s="60"/>
+      <c r="BU21" s="60"/>
+      <c r="BV21" s="60"/>
+      <c r="BW21" s="60"/>
+      <c r="BX21" s="60"/>
+      <c r="BY21" s="60"/>
+      <c r="BZ21" s="60"/>
+      <c r="CA21" s="61"/>
+      <c r="CB21" s="61"/>
+      <c r="CC21" s="62"/>
+      <c r="CD21" s="58"/>
+      <c r="CE21" s="59"/>
+      <c r="CF21" s="60"/>
+      <c r="CG21" s="60"/>
+      <c r="CH21" s="60"/>
+      <c r="CI21" s="60"/>
+      <c r="CJ21" s="60"/>
+      <c r="CK21" s="60"/>
+      <c r="CL21" s="60"/>
+      <c r="CM21" s="61"/>
+      <c r="CN21" s="61"/>
+      <c r="CO21" s="62"/>
+      <c r="CP21" s="58"/>
+      <c r="CQ21" s="59"/>
+      <c r="CR21" s="60"/>
+      <c r="CS21" s="60"/>
+      <c r="CT21" s="60"/>
+      <c r="CU21" s="60"/>
+      <c r="CV21" s="60"/>
+      <c r="CW21" s="60"/>
+      <c r="CX21" s="60"/>
+      <c r="CY21" s="61"/>
+      <c r="CZ21" s="61"/>
+      <c r="DA21" s="62"/>
+      <c r="DB21" s="58"/>
+      <c r="DC21" s="59"/>
+      <c r="DD21" s="60"/>
+      <c r="DE21" s="60"/>
+      <c r="DF21" s="60"/>
+      <c r="DG21" s="60"/>
+      <c r="DH21" s="60"/>
+      <c r="DI21" s="60"/>
+      <c r="DJ21" s="60"/>
+      <c r="DK21" s="61"/>
+      <c r="DL21" s="61"/>
+      <c r="DM21" s="62"/>
+      <c r="DN21" s="58"/>
+      <c r="DO21" s="59"/>
+      <c r="DP21" s="60"/>
+      <c r="DQ21" s="60"/>
+      <c r="DR21" s="60"/>
+      <c r="DS21" s="60"/>
+      <c r="DT21" s="60"/>
+      <c r="DU21" s="60"/>
+      <c r="DV21" s="60"/>
+      <c r="DW21" s="61"/>
+      <c r="DX21" s="61"/>
+      <c r="DY21" s="62"/>
+      <c r="DZ21" s="58"/>
+      <c r="EA21" s="59"/>
+      <c r="EB21" s="60"/>
+      <c r="EC21" s="60"/>
+      <c r="ED21" s="60"/>
+      <c r="EE21" s="60"/>
+      <c r="EF21" s="60"/>
+      <c r="EG21" s="60"/>
+      <c r="EH21" s="60"/>
+      <c r="EI21" s="61"/>
+      <c r="EJ21" s="61"/>
+      <c r="EK21" s="62"/>
+      <c r="EL21" s="58"/>
+      <c r="EM21" s="59"/>
+      <c r="EN21" s="60"/>
+      <c r="EO21" s="60"/>
+      <c r="EP21" s="60"/>
+      <c r="EQ21" s="60"/>
+      <c r="ER21" s="60"/>
+      <c r="ES21" s="60"/>
+      <c r="ET21" s="60"/>
+      <c r="EU21" s="61"/>
+      <c r="EV21" s="61"/>
+      <c r="EW21" s="62"/>
+      <c r="EX21" s="58"/>
+      <c r="EY21" s="59"/>
+      <c r="EZ21" s="60"/>
+      <c r="FA21" s="60"/>
+      <c r="FB21" s="60"/>
+      <c r="FC21" s="60"/>
+      <c r="FD21" s="60"/>
+      <c r="FE21" s="60"/>
+      <c r="FF21" s="60"/>
+      <c r="FG21" s="61"/>
+      <c r="FH21" s="61"/>
+      <c r="FI21" s="62"/>
     </row>
     <row r="22" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="1"/>
@@ -7229,188 +7229,188 @@
       <c r="G22" s="69"/>
       <c r="H22" s="69"/>
       <c r="I22" s="69"/>
-      <c r="J22" s="62">
+      <c r="J22" s="48">
         <v>0</v>
       </c>
-      <c r="K22" s="62"/>
-      <c r="L22" s="62"/>
-      <c r="M22" s="62"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="62"/>
-      <c r="P22" s="62"/>
-      <c r="Q22" s="62"/>
-      <c r="R22" s="62"/>
-      <c r="S22" s="62"/>
-      <c r="T22" s="62"/>
-      <c r="U22" s="62"/>
-      <c r="V22" s="62">
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48">
         <v>0</v>
       </c>
-      <c r="W22" s="62"/>
-      <c r="X22" s="62"/>
-      <c r="Y22" s="62"/>
-      <c r="Z22" s="62"/>
-      <c r="AA22" s="62"/>
-      <c r="AB22" s="62"/>
-      <c r="AC22" s="62"/>
-      <c r="AD22" s="62"/>
-      <c r="AE22" s="62"/>
-      <c r="AF22" s="62"/>
-      <c r="AG22" s="62"/>
-      <c r="AH22" s="62">
+      <c r="W22" s="48"/>
+      <c r="X22" s="48"/>
+      <c r="Y22" s="48"/>
+      <c r="Z22" s="48"/>
+      <c r="AA22" s="48"/>
+      <c r="AB22" s="48"/>
+      <c r="AC22" s="48"/>
+      <c r="AD22" s="48"/>
+      <c r="AE22" s="48"/>
+      <c r="AF22" s="48"/>
+      <c r="AG22" s="48"/>
+      <c r="AH22" s="48">
         <v>0</v>
       </c>
-      <c r="AI22" s="62"/>
-      <c r="AJ22" s="62"/>
-      <c r="AK22" s="62"/>
-      <c r="AL22" s="62"/>
-      <c r="AM22" s="62"/>
-      <c r="AN22" s="62"/>
-      <c r="AO22" s="62"/>
-      <c r="AP22" s="62"/>
-      <c r="AQ22" s="62"/>
-      <c r="AR22" s="62"/>
-      <c r="AS22" s="62"/>
-      <c r="AT22" s="62">
+      <c r="AI22" s="48"/>
+      <c r="AJ22" s="48"/>
+      <c r="AK22" s="48"/>
+      <c r="AL22" s="48"/>
+      <c r="AM22" s="48"/>
+      <c r="AN22" s="48"/>
+      <c r="AO22" s="48"/>
+      <c r="AP22" s="48"/>
+      <c r="AQ22" s="48"/>
+      <c r="AR22" s="48"/>
+      <c r="AS22" s="48"/>
+      <c r="AT22" s="48">
         <v>0</v>
       </c>
-      <c r="AU22" s="62"/>
-      <c r="AV22" s="62"/>
-      <c r="AW22" s="62"/>
-      <c r="AX22" s="62"/>
-      <c r="AY22" s="62"/>
-      <c r="AZ22" s="62"/>
-      <c r="BA22" s="62"/>
-      <c r="BB22" s="62"/>
-      <c r="BC22" s="62"/>
-      <c r="BD22" s="62"/>
-      <c r="BE22" s="62"/>
-      <c r="BF22" s="62">
+      <c r="AU22" s="48"/>
+      <c r="AV22" s="48"/>
+      <c r="AW22" s="48"/>
+      <c r="AX22" s="48"/>
+      <c r="AY22" s="48"/>
+      <c r="AZ22" s="48"/>
+      <c r="BA22" s="48"/>
+      <c r="BB22" s="48"/>
+      <c r="BC22" s="48"/>
+      <c r="BD22" s="48"/>
+      <c r="BE22" s="48"/>
+      <c r="BF22" s="48">
         <v>0</v>
       </c>
-      <c r="BG22" s="62"/>
-      <c r="BH22" s="62"/>
-      <c r="BI22" s="62"/>
-      <c r="BJ22" s="62"/>
-      <c r="BK22" s="62"/>
-      <c r="BL22" s="62"/>
-      <c r="BM22" s="62"/>
-      <c r="BN22" s="62"/>
-      <c r="BO22" s="62"/>
-      <c r="BP22" s="62"/>
-      <c r="BQ22" s="62"/>
-      <c r="BR22" s="62">
+      <c r="BG22" s="48"/>
+      <c r="BH22" s="48"/>
+      <c r="BI22" s="48"/>
+      <c r="BJ22" s="48"/>
+      <c r="BK22" s="48"/>
+      <c r="BL22" s="48"/>
+      <c r="BM22" s="48"/>
+      <c r="BN22" s="48"/>
+      <c r="BO22" s="48"/>
+      <c r="BP22" s="48"/>
+      <c r="BQ22" s="48"/>
+      <c r="BR22" s="48">
         <v>0</v>
       </c>
-      <c r="BS22" s="62"/>
-      <c r="BT22" s="62"/>
-      <c r="BU22" s="62"/>
-      <c r="BV22" s="62"/>
-      <c r="BW22" s="62"/>
-      <c r="BX22" s="62"/>
-      <c r="BY22" s="62"/>
-      <c r="BZ22" s="62"/>
-      <c r="CA22" s="62"/>
-      <c r="CB22" s="62"/>
-      <c r="CC22" s="62"/>
-      <c r="CD22" s="62">
+      <c r="BS22" s="48"/>
+      <c r="BT22" s="48"/>
+      <c r="BU22" s="48"/>
+      <c r="BV22" s="48"/>
+      <c r="BW22" s="48"/>
+      <c r="BX22" s="48"/>
+      <c r="BY22" s="48"/>
+      <c r="BZ22" s="48"/>
+      <c r="CA22" s="48"/>
+      <c r="CB22" s="48"/>
+      <c r="CC22" s="48"/>
+      <c r="CD22" s="48">
         <v>0</v>
       </c>
-      <c r="CE22" s="62"/>
-      <c r="CF22" s="62"/>
-      <c r="CG22" s="62"/>
-      <c r="CH22" s="62"/>
-      <c r="CI22" s="62"/>
-      <c r="CJ22" s="62"/>
-      <c r="CK22" s="62"/>
-      <c r="CL22" s="62"/>
-      <c r="CM22" s="62"/>
-      <c r="CN22" s="62"/>
-      <c r="CO22" s="62"/>
-      <c r="CP22" s="62">
+      <c r="CE22" s="48"/>
+      <c r="CF22" s="48"/>
+      <c r="CG22" s="48"/>
+      <c r="CH22" s="48"/>
+      <c r="CI22" s="48"/>
+      <c r="CJ22" s="48"/>
+      <c r="CK22" s="48"/>
+      <c r="CL22" s="48"/>
+      <c r="CM22" s="48"/>
+      <c r="CN22" s="48"/>
+      <c r="CO22" s="48"/>
+      <c r="CP22" s="48">
         <v>0</v>
       </c>
-      <c r="CQ22" s="62"/>
-      <c r="CR22" s="62"/>
-      <c r="CS22" s="62"/>
-      <c r="CT22" s="62"/>
-      <c r="CU22" s="62"/>
-      <c r="CV22" s="62"/>
-      <c r="CW22" s="62"/>
-      <c r="CX22" s="62"/>
-      <c r="CY22" s="62"/>
-      <c r="CZ22" s="62"/>
-      <c r="DA22" s="62"/>
-      <c r="DB22" s="62">
+      <c r="CQ22" s="48"/>
+      <c r="CR22" s="48"/>
+      <c r="CS22" s="48"/>
+      <c r="CT22" s="48"/>
+      <c r="CU22" s="48"/>
+      <c r="CV22" s="48"/>
+      <c r="CW22" s="48"/>
+      <c r="CX22" s="48"/>
+      <c r="CY22" s="48"/>
+      <c r="CZ22" s="48"/>
+      <c r="DA22" s="48"/>
+      <c r="DB22" s="48">
         <v>0</v>
       </c>
-      <c r="DC22" s="62"/>
-      <c r="DD22" s="62"/>
-      <c r="DE22" s="62"/>
-      <c r="DF22" s="62"/>
-      <c r="DG22" s="62"/>
-      <c r="DH22" s="62"/>
-      <c r="DI22" s="62"/>
-      <c r="DJ22" s="62"/>
-      <c r="DK22" s="62"/>
-      <c r="DL22" s="62"/>
-      <c r="DM22" s="62"/>
-      <c r="DN22" s="62">
+      <c r="DC22" s="48"/>
+      <c r="DD22" s="48"/>
+      <c r="DE22" s="48"/>
+      <c r="DF22" s="48"/>
+      <c r="DG22" s="48"/>
+      <c r="DH22" s="48"/>
+      <c r="DI22" s="48"/>
+      <c r="DJ22" s="48"/>
+      <c r="DK22" s="48"/>
+      <c r="DL22" s="48"/>
+      <c r="DM22" s="48"/>
+      <c r="DN22" s="48">
         <v>0</v>
       </c>
-      <c r="DO22" s="62"/>
-      <c r="DP22" s="62"/>
-      <c r="DQ22" s="62"/>
-      <c r="DR22" s="62"/>
-      <c r="DS22" s="62"/>
-      <c r="DT22" s="62"/>
-      <c r="DU22" s="62"/>
-      <c r="DV22" s="62"/>
-      <c r="DW22" s="62"/>
-      <c r="DX22" s="62"/>
-      <c r="DY22" s="62"/>
-      <c r="DZ22" s="62">
+      <c r="DO22" s="48"/>
+      <c r="DP22" s="48"/>
+      <c r="DQ22" s="48"/>
+      <c r="DR22" s="48"/>
+      <c r="DS22" s="48"/>
+      <c r="DT22" s="48"/>
+      <c r="DU22" s="48"/>
+      <c r="DV22" s="48"/>
+      <c r="DW22" s="48"/>
+      <c r="DX22" s="48"/>
+      <c r="DY22" s="48"/>
+      <c r="DZ22" s="48">
         <v>0</v>
       </c>
-      <c r="EA22" s="62"/>
-      <c r="EB22" s="62"/>
-      <c r="EC22" s="62"/>
-      <c r="ED22" s="62"/>
-      <c r="EE22" s="62"/>
-      <c r="EF22" s="62"/>
-      <c r="EG22" s="62"/>
-      <c r="EH22" s="62"/>
-      <c r="EI22" s="62"/>
-      <c r="EJ22" s="62"/>
-      <c r="EK22" s="62"/>
-      <c r="EL22" s="62">
+      <c r="EA22" s="48"/>
+      <c r="EB22" s="48"/>
+      <c r="EC22" s="48"/>
+      <c r="ED22" s="48"/>
+      <c r="EE22" s="48"/>
+      <c r="EF22" s="48"/>
+      <c r="EG22" s="48"/>
+      <c r="EH22" s="48"/>
+      <c r="EI22" s="48"/>
+      <c r="EJ22" s="48"/>
+      <c r="EK22" s="48"/>
+      <c r="EL22" s="48">
         <v>0</v>
       </c>
-      <c r="EM22" s="62"/>
-      <c r="EN22" s="62"/>
-      <c r="EO22" s="62"/>
-      <c r="EP22" s="62"/>
-      <c r="EQ22" s="62"/>
-      <c r="ER22" s="62"/>
-      <c r="ES22" s="62"/>
-      <c r="ET22" s="62"/>
-      <c r="EU22" s="62"/>
-      <c r="EV22" s="62"/>
-      <c r="EW22" s="62"/>
-      <c r="EX22" s="62">
+      <c r="EM22" s="48"/>
+      <c r="EN22" s="48"/>
+      <c r="EO22" s="48"/>
+      <c r="EP22" s="48"/>
+      <c r="EQ22" s="48"/>
+      <c r="ER22" s="48"/>
+      <c r="ES22" s="48"/>
+      <c r="ET22" s="48"/>
+      <c r="EU22" s="48"/>
+      <c r="EV22" s="48"/>
+      <c r="EW22" s="48"/>
+      <c r="EX22" s="48">
         <v>0</v>
       </c>
-      <c r="EY22" s="62"/>
-      <c r="EZ22" s="62"/>
-      <c r="FA22" s="62"/>
-      <c r="FB22" s="62"/>
-      <c r="FC22" s="62"/>
-      <c r="FD22" s="62"/>
-      <c r="FE22" s="62"/>
-      <c r="FF22" s="62"/>
-      <c r="FG22" s="62"/>
-      <c r="FH22" s="62"/>
-      <c r="FI22" s="62"/>
+      <c r="EY22" s="48"/>
+      <c r="EZ22" s="48"/>
+      <c r="FA22" s="48"/>
+      <c r="FB22" s="48"/>
+      <c r="FC22" s="48"/>
+      <c r="FD22" s="48"/>
+      <c r="FE22" s="48"/>
+      <c r="FF22" s="48"/>
+      <c r="FG22" s="48"/>
+      <c r="FH22" s="48"/>
+      <c r="FI22" s="48"/>
     </row>
     <row r="23" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B23" s="5"/>
@@ -11232,35 +11232,6 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="BF22:BQ22"/>
-    <mergeCell ref="BR22:CC22"/>
-    <mergeCell ref="CD22:CO22"/>
-    <mergeCell ref="EX22:FI22"/>
-    <mergeCell ref="CP22:DA22"/>
-    <mergeCell ref="DB22:DM22"/>
-    <mergeCell ref="DN22:DY22"/>
-    <mergeCell ref="DZ22:EK22"/>
-    <mergeCell ref="EL22:EW22"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="AH22:AS22"/>
-    <mergeCell ref="AT22:BE22"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="J21:U21"/>
-    <mergeCell ref="J22:U22"/>
-    <mergeCell ref="V22:AG22"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="DN21:DY21"/>
-    <mergeCell ref="DZ21:EK21"/>
-    <mergeCell ref="EL21:EW21"/>
-    <mergeCell ref="EL2:EW2"/>
-    <mergeCell ref="EX2:FI2"/>
-    <mergeCell ref="EX21:FI21"/>
-    <mergeCell ref="DZ2:EK2"/>
-    <mergeCell ref="DN2:DY2"/>
     <mergeCell ref="DB21:DM21"/>
     <mergeCell ref="DB2:DM2"/>
     <mergeCell ref="CP2:DA2"/>
@@ -11277,6 +11248,35 @@
     <mergeCell ref="AH2:AS2"/>
     <mergeCell ref="AH21:AS21"/>
     <mergeCell ref="V21:AG21"/>
+    <mergeCell ref="DN21:DY21"/>
+    <mergeCell ref="DZ21:EK21"/>
+    <mergeCell ref="EL21:EW21"/>
+    <mergeCell ref="EL2:EW2"/>
+    <mergeCell ref="EX2:FI2"/>
+    <mergeCell ref="EX21:FI21"/>
+    <mergeCell ref="DZ2:EK2"/>
+    <mergeCell ref="DN2:DY2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AH22:AS22"/>
+    <mergeCell ref="AT22:BE22"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="J21:U21"/>
+    <mergeCell ref="J22:U22"/>
+    <mergeCell ref="V22:AG22"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D21:I21"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="BF22:BQ22"/>
+    <mergeCell ref="BR22:CC22"/>
+    <mergeCell ref="CD22:CO22"/>
+    <mergeCell ref="EX22:FI22"/>
+    <mergeCell ref="CP22:DA22"/>
+    <mergeCell ref="DB22:DM22"/>
+    <mergeCell ref="DN22:DY22"/>
+    <mergeCell ref="DZ22:EK22"/>
+    <mergeCell ref="EL22:EW22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/activity/M01A02/M01A02.xlsx
+++ b/activity/M01A02/M01A02.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CBDD0B-4909-4CB1-82F0-B00015EE8819}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60423794-6AC5-45BB-BB91-DF28C35F5316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Calificacion!$B$2:$F$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$U$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$U$23</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="67">
   <si>
     <t>J4660</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>Calificación 1.2. Modelación hidrológica para obtención de caudales de diseño e hidrogramas para tránsito de crecientes</t>
+  </si>
+  <si>
+    <t>Crear la capa geográfica shapefile de localización de puntos de estudio.</t>
   </si>
 </sst>
 </file>
@@ -1322,19 +1325,19 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1352,20 +1355,20 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2841,7 +2844,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="10">
-        <f>Detalle!J22*C5/5</f>
+        <f>Detalle!J23*C5/5</f>
         <v>0</v>
       </c>
       <c r="E5" s="33">
@@ -2860,7 +2863,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="10">
-        <f>Detalle!V22*C6/5</f>
+        <f>Detalle!V23*C6/5</f>
         <v>0</v>
       </c>
       <c r="E6" s="33"/>
@@ -2877,7 +2880,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="10">
-        <f>Detalle!AH22*C7/5</f>
+        <f>Detalle!AH23*C7/5</f>
         <v>0</v>
       </c>
       <c r="E7" s="33"/>
@@ -2894,7 +2897,7 @@
         <v>5</v>
       </c>
       <c r="D8" s="10">
-        <f>Detalle!AT22*C8/5</f>
+        <f>Detalle!AT23*C8/5</f>
         <v>0</v>
       </c>
       <c r="E8" s="33"/>
@@ -2911,7 +2914,7 @@
         <v>5</v>
       </c>
       <c r="D9" s="10">
-        <f>Detalle!BF22*C9/5</f>
+        <f>Detalle!BF23*C9/5</f>
         <v>0</v>
       </c>
       <c r="E9" s="33"/>
@@ -2928,7 +2931,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="10">
-        <f>Detalle!BR22*C10/5</f>
+        <f>Detalle!BR23*C10/5</f>
         <v>0</v>
       </c>
       <c r="E10" s="33"/>
@@ -2945,7 +2948,7 @@
         <v>5</v>
       </c>
       <c r="D11" s="10">
-        <f>Detalle!CD22*C11/5</f>
+        <f>Detalle!CD23*C11/5</f>
         <v>0</v>
       </c>
       <c r="E11" s="33"/>
@@ -2962,7 +2965,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="10">
-        <f>Detalle!CP22*C12/5</f>
+        <f>Detalle!CP23*C12/5</f>
         <v>0</v>
       </c>
       <c r="E12" s="33"/>
@@ -2979,7 +2982,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="10">
-        <f>Detalle!DB22*C13/5</f>
+        <f>Detalle!DB23*C13/5</f>
         <v>0</v>
       </c>
       <c r="E13" s="33"/>
@@ -2996,7 +2999,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="10">
-        <f>Detalle!DN22*C14/5</f>
+        <f>Detalle!DN23*C14/5</f>
         <v>0</v>
       </c>
       <c r="E14" s="33"/>
@@ -3013,7 +3016,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="10">
-        <f>Detalle!DZ22*C15/5</f>
+        <f>Detalle!DZ23*C15/5</f>
         <v>0</v>
       </c>
       <c r="E15" s="33"/>
@@ -3030,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="10">
-        <f>Detalle!EL22*C16/5</f>
+        <f>Detalle!EL23*C16/5</f>
         <v>0</v>
       </c>
       <c r="E16" s="33"/>
@@ -3047,7 +3050,7 @@
         <v>5</v>
       </c>
       <c r="D17" s="28">
-        <f>Detalle!EX22*C17/5</f>
+        <f>Detalle!EX23*C17/5</f>
         <v>0</v>
       </c>
       <c r="E17" s="34"/>
@@ -3099,7 +3102,7 @@
   <sheetPr codeName="Hoja1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:FI45"/>
+  <dimension ref="A1:FI46"/>
   <sheetFormatPr defaultColWidth="11.33203125" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
@@ -3305,10 +3308,10 @@
     </row>
     <row r="2" spans="1:165" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="49" t="s">
+      <c r="B2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="51" t="s">
+      <c r="C2" s="60" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="63" t="s">
@@ -3516,8 +3519,8 @@
       <c r="FI2" s="57"/>
     </row>
     <row r="3" spans="1:165" ht="30.75" x14ac:dyDescent="0.45">
-      <c r="B3" s="50"/>
-      <c r="C3" s="52"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="61"/>
       <c r="D3" s="8" t="s">
         <v>7</v>
       </c>
@@ -6032,11 +6035,11 @@
       <c r="FH14" s="43"/>
       <c r="FI14" s="44"/>
     </row>
-    <row r="15" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A15" s="1"/>
       <c r="B15" s="23"/>
-      <c r="C15" s="24" t="s">
-        <v>45</v>
+      <c r="C15" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="D15" s="24"/>
       <c r="E15" s="24"/>
@@ -6201,11 +6204,11 @@
       <c r="FH15" s="43"/>
       <c r="FI15" s="44"/>
     </row>
-    <row r="16" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
       <c r="B16" s="23"/>
-      <c r="C16" s="16" t="s">
-        <v>32</v>
+      <c r="C16" s="24" t="s">
+        <v>45</v>
       </c>
       <c r="D16" s="24"/>
       <c r="E16" s="24"/>
@@ -6370,11 +6373,11 @@
       <c r="FH16" s="43"/>
       <c r="FI16" s="44"/>
     </row>
-    <row r="17" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:165" s="26" customFormat="1" ht="30.75" x14ac:dyDescent="0.45">
       <c r="A17" s="1"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="24" t="s">
-        <v>25</v>
+      <c r="C17" s="16" t="s">
+        <v>32</v>
       </c>
       <c r="D17" s="24"/>
       <c r="E17" s="24"/>
@@ -6543,7 +6546,7 @@
       <c r="A18" s="1"/>
       <c r="B18" s="23"/>
       <c r="C18" s="24" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D18" s="24"/>
       <c r="E18" s="24"/>
@@ -6712,7 +6715,7 @@
       <c r="A19" s="1"/>
       <c r="B19" s="23"/>
       <c r="C19" s="24" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
@@ -6877,11 +6880,11 @@
       <c r="FH19" s="43"/>
       <c r="FI19" s="44"/>
     </row>
-    <row r="20" spans="1:165" s="26" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:165" s="26" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A20" s="1"/>
       <c r="B20" s="23"/>
       <c r="C20" s="24" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D20" s="24"/>
       <c r="E20" s="24"/>
@@ -7046,540 +7049,543 @@
       <c r="FH20" s="43"/>
       <c r="FI20" s="44"/>
     </row>
-    <row r="21" spans="1:165" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:165" s="26" customFormat="1" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="1"/>
-      <c r="B21" s="67" t="s">
+      <c r="B21" s="23"/>
+      <c r="C21" s="24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="42"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="42"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="44"/>
+      <c r="V21" s="40"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="42"/>
+      <c r="AC21" s="42"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="43"/>
+      <c r="AF21" s="43"/>
+      <c r="AG21" s="44"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="41"/>
+      <c r="AJ21" s="42"/>
+      <c r="AK21" s="42"/>
+      <c r="AL21" s="42"/>
+      <c r="AM21" s="42"/>
+      <c r="AN21" s="42"/>
+      <c r="AO21" s="42"/>
+      <c r="AP21" s="42"/>
+      <c r="AQ21" s="43"/>
+      <c r="AR21" s="43"/>
+      <c r="AS21" s="44"/>
+      <c r="AT21" s="40"/>
+      <c r="AU21" s="41"/>
+      <c r="AV21" s="42"/>
+      <c r="AW21" s="42"/>
+      <c r="AX21" s="42"/>
+      <c r="AY21" s="42"/>
+      <c r="AZ21" s="42"/>
+      <c r="BA21" s="42"/>
+      <c r="BB21" s="42"/>
+      <c r="BC21" s="43"/>
+      <c r="BD21" s="43"/>
+      <c r="BE21" s="44"/>
+      <c r="BF21" s="40"/>
+      <c r="BG21" s="41"/>
+      <c r="BH21" s="42"/>
+      <c r="BI21" s="42"/>
+      <c r="BJ21" s="42"/>
+      <c r="BK21" s="42"/>
+      <c r="BL21" s="42"/>
+      <c r="BM21" s="42"/>
+      <c r="BN21" s="42"/>
+      <c r="BO21" s="43"/>
+      <c r="BP21" s="43"/>
+      <c r="BQ21" s="44"/>
+      <c r="BR21" s="40"/>
+      <c r="BS21" s="41"/>
+      <c r="BT21" s="42"/>
+      <c r="BU21" s="42"/>
+      <c r="BV21" s="42"/>
+      <c r="BW21" s="42"/>
+      <c r="BX21" s="42"/>
+      <c r="BY21" s="42"/>
+      <c r="BZ21" s="42"/>
+      <c r="CA21" s="43"/>
+      <c r="CB21" s="43"/>
+      <c r="CC21" s="44"/>
+      <c r="CD21" s="40"/>
+      <c r="CE21" s="41"/>
+      <c r="CF21" s="42"/>
+      <c r="CG21" s="42"/>
+      <c r="CH21" s="42"/>
+      <c r="CI21" s="42"/>
+      <c r="CJ21" s="42"/>
+      <c r="CK21" s="42"/>
+      <c r="CL21" s="42"/>
+      <c r="CM21" s="43"/>
+      <c r="CN21" s="43"/>
+      <c r="CO21" s="44"/>
+      <c r="CP21" s="40"/>
+      <c r="CQ21" s="41"/>
+      <c r="CR21" s="42"/>
+      <c r="CS21" s="42"/>
+      <c r="CT21" s="42"/>
+      <c r="CU21" s="42"/>
+      <c r="CV21" s="42"/>
+      <c r="CW21" s="42"/>
+      <c r="CX21" s="42"/>
+      <c r="CY21" s="43"/>
+      <c r="CZ21" s="43"/>
+      <c r="DA21" s="44"/>
+      <c r="DB21" s="40"/>
+      <c r="DC21" s="41"/>
+      <c r="DD21" s="42"/>
+      <c r="DE21" s="42"/>
+      <c r="DF21" s="42"/>
+      <c r="DG21" s="42"/>
+      <c r="DH21" s="42"/>
+      <c r="DI21" s="42"/>
+      <c r="DJ21" s="42"/>
+      <c r="DK21" s="43"/>
+      <c r="DL21" s="43"/>
+      <c r="DM21" s="44"/>
+      <c r="DN21" s="40"/>
+      <c r="DO21" s="41"/>
+      <c r="DP21" s="42"/>
+      <c r="DQ21" s="42"/>
+      <c r="DR21" s="42"/>
+      <c r="DS21" s="42"/>
+      <c r="DT21" s="42"/>
+      <c r="DU21" s="42"/>
+      <c r="DV21" s="42"/>
+      <c r="DW21" s="43"/>
+      <c r="DX21" s="43"/>
+      <c r="DY21" s="44"/>
+      <c r="DZ21" s="40"/>
+      <c r="EA21" s="41"/>
+      <c r="EB21" s="42"/>
+      <c r="EC21" s="42"/>
+      <c r="ED21" s="42"/>
+      <c r="EE21" s="42"/>
+      <c r="EF21" s="42"/>
+      <c r="EG21" s="42"/>
+      <c r="EH21" s="42"/>
+      <c r="EI21" s="43"/>
+      <c r="EJ21" s="43"/>
+      <c r="EK21" s="44"/>
+      <c r="EL21" s="40"/>
+      <c r="EM21" s="41"/>
+      <c r="EN21" s="42"/>
+      <c r="EO21" s="42"/>
+      <c r="EP21" s="42"/>
+      <c r="EQ21" s="42"/>
+      <c r="ER21" s="42"/>
+      <c r="ES21" s="42"/>
+      <c r="ET21" s="42"/>
+      <c r="EU21" s="43"/>
+      <c r="EV21" s="43"/>
+      <c r="EW21" s="44"/>
+      <c r="EX21" s="40"/>
+      <c r="EY21" s="41"/>
+      <c r="EZ21" s="42"/>
+      <c r="FA21" s="42"/>
+      <c r="FB21" s="42"/>
+      <c r="FC21" s="42"/>
+      <c r="FD21" s="42"/>
+      <c r="FE21" s="42"/>
+      <c r="FF21" s="42"/>
+      <c r="FG21" s="43"/>
+      <c r="FH21" s="43"/>
+      <c r="FI21" s="44"/>
+    </row>
+    <row r="22" spans="1:165" s="2" customFormat="1" ht="84" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="1"/>
+      <c r="B22" s="67" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="D21" s="65" t="s">
+      <c r="C22" s="68"/>
+      <c r="D22" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="60"/>
-      <c r="M21" s="60"/>
-      <c r="N21" s="60"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
-      <c r="Q21" s="60"/>
-      <c r="R21" s="60"/>
-      <c r="S21" s="61"/>
-      <c r="T21" s="61"/>
-      <c r="U21" s="62"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="60"/>
-      <c r="Y21" s="60"/>
-      <c r="Z21" s="60"/>
-      <c r="AA21" s="60"/>
-      <c r="AB21" s="60"/>
-      <c r="AC21" s="60"/>
-      <c r="AD21" s="60"/>
-      <c r="AE21" s="61"/>
-      <c r="AF21" s="61"/>
-      <c r="AG21" s="62"/>
-      <c r="AH21" s="58"/>
-      <c r="AI21" s="59"/>
-      <c r="AJ21" s="60"/>
-      <c r="AK21" s="60"/>
-      <c r="AL21" s="60"/>
-      <c r="AM21" s="60"/>
-      <c r="AN21" s="60"/>
-      <c r="AO21" s="60"/>
-      <c r="AP21" s="60"/>
-      <c r="AQ21" s="61"/>
-      <c r="AR21" s="61"/>
-      <c r="AS21" s="62"/>
-      <c r="AT21" s="58"/>
-      <c r="AU21" s="59"/>
-      <c r="AV21" s="60"/>
-      <c r="AW21" s="60"/>
-      <c r="AX21" s="60"/>
-      <c r="AY21" s="60"/>
-      <c r="AZ21" s="60"/>
-      <c r="BA21" s="60"/>
-      <c r="BB21" s="60"/>
-      <c r="BC21" s="61"/>
-      <c r="BD21" s="61"/>
-      <c r="BE21" s="62"/>
-      <c r="BF21" s="58"/>
-      <c r="BG21" s="59"/>
-      <c r="BH21" s="60"/>
-      <c r="BI21" s="60"/>
-      <c r="BJ21" s="60"/>
-      <c r="BK21" s="60"/>
-      <c r="BL21" s="60"/>
-      <c r="BM21" s="60"/>
-      <c r="BN21" s="60"/>
-      <c r="BO21" s="61"/>
-      <c r="BP21" s="61"/>
-      <c r="BQ21" s="62"/>
-      <c r="BR21" s="58"/>
-      <c r="BS21" s="59"/>
-      <c r="BT21" s="60"/>
-      <c r="BU21" s="60"/>
-      <c r="BV21" s="60"/>
-      <c r="BW21" s="60"/>
-      <c r="BX21" s="60"/>
-      <c r="BY21" s="60"/>
-      <c r="BZ21" s="60"/>
-      <c r="CA21" s="61"/>
-      <c r="CB21" s="61"/>
-      <c r="CC21" s="62"/>
-      <c r="CD21" s="58"/>
-      <c r="CE21" s="59"/>
-      <c r="CF21" s="60"/>
-      <c r="CG21" s="60"/>
-      <c r="CH21" s="60"/>
-      <c r="CI21" s="60"/>
-      <c r="CJ21" s="60"/>
-      <c r="CK21" s="60"/>
-      <c r="CL21" s="60"/>
-      <c r="CM21" s="61"/>
-      <c r="CN21" s="61"/>
-      <c r="CO21" s="62"/>
-      <c r="CP21" s="58"/>
-      <c r="CQ21" s="59"/>
-      <c r="CR21" s="60"/>
-      <c r="CS21" s="60"/>
-      <c r="CT21" s="60"/>
-      <c r="CU21" s="60"/>
-      <c r="CV21" s="60"/>
-      <c r="CW21" s="60"/>
-      <c r="CX21" s="60"/>
-      <c r="CY21" s="61"/>
-      <c r="CZ21" s="61"/>
-      <c r="DA21" s="62"/>
-      <c r="DB21" s="58"/>
-      <c r="DC21" s="59"/>
-      <c r="DD21" s="60"/>
-      <c r="DE21" s="60"/>
-      <c r="DF21" s="60"/>
-      <c r="DG21" s="60"/>
-      <c r="DH21" s="60"/>
-      <c r="DI21" s="60"/>
-      <c r="DJ21" s="60"/>
-      <c r="DK21" s="61"/>
-      <c r="DL21" s="61"/>
-      <c r="DM21" s="62"/>
-      <c r="DN21" s="58"/>
-      <c r="DO21" s="59"/>
-      <c r="DP21" s="60"/>
-      <c r="DQ21" s="60"/>
-      <c r="DR21" s="60"/>
-      <c r="DS21" s="60"/>
-      <c r="DT21" s="60"/>
-      <c r="DU21" s="60"/>
-      <c r="DV21" s="60"/>
-      <c r="DW21" s="61"/>
-      <c r="DX21" s="61"/>
-      <c r="DY21" s="62"/>
-      <c r="DZ21" s="58"/>
-      <c r="EA21" s="59"/>
-      <c r="EB21" s="60"/>
-      <c r="EC21" s="60"/>
-      <c r="ED21" s="60"/>
-      <c r="EE21" s="60"/>
-      <c r="EF21" s="60"/>
-      <c r="EG21" s="60"/>
-      <c r="EH21" s="60"/>
-      <c r="EI21" s="61"/>
-      <c r="EJ21" s="61"/>
-      <c r="EK21" s="62"/>
-      <c r="EL21" s="58"/>
-      <c r="EM21" s="59"/>
-      <c r="EN21" s="60"/>
-      <c r="EO21" s="60"/>
-      <c r="EP21" s="60"/>
-      <c r="EQ21" s="60"/>
-      <c r="ER21" s="60"/>
-      <c r="ES21" s="60"/>
-      <c r="ET21" s="60"/>
-      <c r="EU21" s="61"/>
-      <c r="EV21" s="61"/>
-      <c r="EW21" s="62"/>
-      <c r="EX21" s="58"/>
-      <c r="EY21" s="59"/>
-      <c r="EZ21" s="60"/>
-      <c r="FA21" s="60"/>
-      <c r="FB21" s="60"/>
-      <c r="FC21" s="60"/>
-      <c r="FD21" s="60"/>
-      <c r="FE21" s="60"/>
-      <c r="FF21" s="60"/>
-      <c r="FG21" s="61"/>
-      <c r="FH21" s="61"/>
-      <c r="FI21" s="62"/>
+      <c r="E22" s="65"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="65"/>
+      <c r="H22" s="65"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="51"/>
+      <c r="T22" s="51"/>
+      <c r="U22" s="52"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="50"/>
+      <c r="Y22" s="50"/>
+      <c r="Z22" s="50"/>
+      <c r="AA22" s="50"/>
+      <c r="AB22" s="50"/>
+      <c r="AC22" s="50"/>
+      <c r="AD22" s="50"/>
+      <c r="AE22" s="51"/>
+      <c r="AF22" s="51"/>
+      <c r="AG22" s="52"/>
+      <c r="AH22" s="48"/>
+      <c r="AI22" s="49"/>
+      <c r="AJ22" s="50"/>
+      <c r="AK22" s="50"/>
+      <c r="AL22" s="50"/>
+      <c r="AM22" s="50"/>
+      <c r="AN22" s="50"/>
+      <c r="AO22" s="50"/>
+      <c r="AP22" s="50"/>
+      <c r="AQ22" s="51"/>
+      <c r="AR22" s="51"/>
+      <c r="AS22" s="52"/>
+      <c r="AT22" s="48"/>
+      <c r="AU22" s="49"/>
+      <c r="AV22" s="50"/>
+      <c r="AW22" s="50"/>
+      <c r="AX22" s="50"/>
+      <c r="AY22" s="50"/>
+      <c r="AZ22" s="50"/>
+      <c r="BA22" s="50"/>
+      <c r="BB22" s="50"/>
+      <c r="BC22" s="51"/>
+      <c r="BD22" s="51"/>
+      <c r="BE22" s="52"/>
+      <c r="BF22" s="48"/>
+      <c r="BG22" s="49"/>
+      <c r="BH22" s="50"/>
+      <c r="BI22" s="50"/>
+      <c r="BJ22" s="50"/>
+      <c r="BK22" s="50"/>
+      <c r="BL22" s="50"/>
+      <c r="BM22" s="50"/>
+      <c r="BN22" s="50"/>
+      <c r="BO22" s="51"/>
+      <c r="BP22" s="51"/>
+      <c r="BQ22" s="52"/>
+      <c r="BR22" s="48"/>
+      <c r="BS22" s="49"/>
+      <c r="BT22" s="50"/>
+      <c r="BU22" s="50"/>
+      <c r="BV22" s="50"/>
+      <c r="BW22" s="50"/>
+      <c r="BX22" s="50"/>
+      <c r="BY22" s="50"/>
+      <c r="BZ22" s="50"/>
+      <c r="CA22" s="51"/>
+      <c r="CB22" s="51"/>
+      <c r="CC22" s="52"/>
+      <c r="CD22" s="48"/>
+      <c r="CE22" s="49"/>
+      <c r="CF22" s="50"/>
+      <c r="CG22" s="50"/>
+      <c r="CH22" s="50"/>
+      <c r="CI22" s="50"/>
+      <c r="CJ22" s="50"/>
+      <c r="CK22" s="50"/>
+      <c r="CL22" s="50"/>
+      <c r="CM22" s="51"/>
+      <c r="CN22" s="51"/>
+      <c r="CO22" s="52"/>
+      <c r="CP22" s="48"/>
+      <c r="CQ22" s="49"/>
+      <c r="CR22" s="50"/>
+      <c r="CS22" s="50"/>
+      <c r="CT22" s="50"/>
+      <c r="CU22" s="50"/>
+      <c r="CV22" s="50"/>
+      <c r="CW22" s="50"/>
+      <c r="CX22" s="50"/>
+      <c r="CY22" s="51"/>
+      <c r="CZ22" s="51"/>
+      <c r="DA22" s="52"/>
+      <c r="DB22" s="48"/>
+      <c r="DC22" s="49"/>
+      <c r="DD22" s="50"/>
+      <c r="DE22" s="50"/>
+      <c r="DF22" s="50"/>
+      <c r="DG22" s="50"/>
+      <c r="DH22" s="50"/>
+      <c r="DI22" s="50"/>
+      <c r="DJ22" s="50"/>
+      <c r="DK22" s="51"/>
+      <c r="DL22" s="51"/>
+      <c r="DM22" s="52"/>
+      <c r="DN22" s="48"/>
+      <c r="DO22" s="49"/>
+      <c r="DP22" s="50"/>
+      <c r="DQ22" s="50"/>
+      <c r="DR22" s="50"/>
+      <c r="DS22" s="50"/>
+      <c r="DT22" s="50"/>
+      <c r="DU22" s="50"/>
+      <c r="DV22" s="50"/>
+      <c r="DW22" s="51"/>
+      <c r="DX22" s="51"/>
+      <c r="DY22" s="52"/>
+      <c r="DZ22" s="48"/>
+      <c r="EA22" s="49"/>
+      <c r="EB22" s="50"/>
+      <c r="EC22" s="50"/>
+      <c r="ED22" s="50"/>
+      <c r="EE22" s="50"/>
+      <c r="EF22" s="50"/>
+      <c r="EG22" s="50"/>
+      <c r="EH22" s="50"/>
+      <c r="EI22" s="51"/>
+      <c r="EJ22" s="51"/>
+      <c r="EK22" s="52"/>
+      <c r="EL22" s="48"/>
+      <c r="EM22" s="49"/>
+      <c r="EN22" s="50"/>
+      <c r="EO22" s="50"/>
+      <c r="EP22" s="50"/>
+      <c r="EQ22" s="50"/>
+      <c r="ER22" s="50"/>
+      <c r="ES22" s="50"/>
+      <c r="ET22" s="50"/>
+      <c r="EU22" s="51"/>
+      <c r="EV22" s="51"/>
+      <c r="EW22" s="52"/>
+      <c r="EX22" s="48"/>
+      <c r="EY22" s="49"/>
+      <c r="EZ22" s="50"/>
+      <c r="FA22" s="50"/>
+      <c r="FB22" s="50"/>
+      <c r="FC22" s="50"/>
+      <c r="FD22" s="50"/>
+      <c r="FE22" s="50"/>
+      <c r="FF22" s="50"/>
+      <c r="FG22" s="51"/>
+      <c r="FH22" s="51"/>
+      <c r="FI22" s="52"/>
     </row>
-    <row r="22" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="1"/>
-      <c r="B22" s="69" t="s">
+    <row r="23" spans="1:165" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="1"/>
+      <c r="B23" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
-      <c r="H22" s="69"/>
-      <c r="I22" s="69"/>
-      <c r="J22" s="48">
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69"/>
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="62">
         <v>0</v>
       </c>
-      <c r="K22" s="48"/>
-      <c r="L22" s="48"/>
-      <c r="M22" s="48"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="48"/>
-      <c r="P22" s="48"/>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="48"/>
-      <c r="S22" s="48"/>
-      <c r="T22" s="48"/>
-      <c r="U22" s="48"/>
-      <c r="V22" s="48">
+      <c r="K23" s="62"/>
+      <c r="L23" s="62"/>
+      <c r="M23" s="62"/>
+      <c r="N23" s="62"/>
+      <c r="O23" s="62"/>
+      <c r="P23" s="62"/>
+      <c r="Q23" s="62"/>
+      <c r="R23" s="62"/>
+      <c r="S23" s="62"/>
+      <c r="T23" s="62"/>
+      <c r="U23" s="62"/>
+      <c r="V23" s="62">
         <v>0</v>
       </c>
-      <c r="W22" s="48"/>
-      <c r="X22" s="48"/>
-      <c r="Y22" s="48"/>
-      <c r="Z22" s="48"/>
-      <c r="AA22" s="48"/>
-      <c r="AB22" s="48"/>
-      <c r="AC22" s="48"/>
-      <c r="AD22" s="48"/>
-      <c r="AE22" s="48"/>
-      <c r="AF22" s="48"/>
-      <c r="AG22" s="48"/>
-      <c r="AH22" s="48">
+      <c r="W23" s="62"/>
+      <c r="X23" s="62"/>
+      <c r="Y23" s="62"/>
+      <c r="Z23" s="62"/>
+      <c r="AA23" s="62"/>
+      <c r="AB23" s="62"/>
+      <c r="AC23" s="62"/>
+      <c r="AD23" s="62"/>
+      <c r="AE23" s="62"/>
+      <c r="AF23" s="62"/>
+      <c r="AG23" s="62"/>
+      <c r="AH23" s="62">
         <v>0</v>
       </c>
-      <c r="AI22" s="48"/>
-      <c r="AJ22" s="48"/>
-      <c r="AK22" s="48"/>
-      <c r="AL22" s="48"/>
-      <c r="AM22" s="48"/>
-      <c r="AN22" s="48"/>
-      <c r="AO22" s="48"/>
-      <c r="AP22" s="48"/>
-      <c r="AQ22" s="48"/>
-      <c r="AR22" s="48"/>
-      <c r="AS22" s="48"/>
-      <c r="AT22" s="48">
+      <c r="AI23" s="62"/>
+      <c r="AJ23" s="62"/>
+      <c r="AK23" s="62"/>
+      <c r="AL23" s="62"/>
+      <c r="AM23" s="62"/>
+      <c r="AN23" s="62"/>
+      <c r="AO23" s="62"/>
+      <c r="AP23" s="62"/>
+      <c r="AQ23" s="62"/>
+      <c r="AR23" s="62"/>
+      <c r="AS23" s="62"/>
+      <c r="AT23" s="62">
         <v>0</v>
       </c>
-      <c r="AU22" s="48"/>
-      <c r="AV22" s="48"/>
-      <c r="AW22" s="48"/>
-      <c r="AX22" s="48"/>
-      <c r="AY22" s="48"/>
-      <c r="AZ22" s="48"/>
-      <c r="BA22" s="48"/>
-      <c r="BB22" s="48"/>
-      <c r="BC22" s="48"/>
-      <c r="BD22" s="48"/>
-      <c r="BE22" s="48"/>
-      <c r="BF22" s="48">
+      <c r="AU23" s="62"/>
+      <c r="AV23" s="62"/>
+      <c r="AW23" s="62"/>
+      <c r="AX23" s="62"/>
+      <c r="AY23" s="62"/>
+      <c r="AZ23" s="62"/>
+      <c r="BA23" s="62"/>
+      <c r="BB23" s="62"/>
+      <c r="BC23" s="62"/>
+      <c r="BD23" s="62"/>
+      <c r="BE23" s="62"/>
+      <c r="BF23" s="62">
         <v>0</v>
       </c>
-      <c r="BG22" s="48"/>
-      <c r="BH22" s="48"/>
-      <c r="BI22" s="48"/>
-      <c r="BJ22" s="48"/>
-      <c r="BK22" s="48"/>
-      <c r="BL22" s="48"/>
-      <c r="BM22" s="48"/>
-      <c r="BN22" s="48"/>
-      <c r="BO22" s="48"/>
-      <c r="BP22" s="48"/>
-      <c r="BQ22" s="48"/>
-      <c r="BR22" s="48">
+      <c r="BG23" s="62"/>
+      <c r="BH23" s="62"/>
+      <c r="BI23" s="62"/>
+      <c r="BJ23" s="62"/>
+      <c r="BK23" s="62"/>
+      <c r="BL23" s="62"/>
+      <c r="BM23" s="62"/>
+      <c r="BN23" s="62"/>
+      <c r="BO23" s="62"/>
+      <c r="BP23" s="62"/>
+      <c r="BQ23" s="62"/>
+      <c r="BR23" s="62">
         <v>0</v>
       </c>
-      <c r="BS22" s="48"/>
-      <c r="BT22" s="48"/>
-      <c r="BU22" s="48"/>
-      <c r="BV22" s="48"/>
-      <c r="BW22" s="48"/>
-      <c r="BX22" s="48"/>
-      <c r="BY22" s="48"/>
-      <c r="BZ22" s="48"/>
-      <c r="CA22" s="48"/>
-      <c r="CB22" s="48"/>
-      <c r="CC22" s="48"/>
-      <c r="CD22" s="48">
+      <c r="BS23" s="62"/>
+      <c r="BT23" s="62"/>
+      <c r="BU23" s="62"/>
+      <c r="BV23" s="62"/>
+      <c r="BW23" s="62"/>
+      <c r="BX23" s="62"/>
+      <c r="BY23" s="62"/>
+      <c r="BZ23" s="62"/>
+      <c r="CA23" s="62"/>
+      <c r="CB23" s="62"/>
+      <c r="CC23" s="62"/>
+      <c r="CD23" s="62">
         <v>0</v>
       </c>
-      <c r="CE22" s="48"/>
-      <c r="CF22" s="48"/>
-      <c r="CG22" s="48"/>
-      <c r="CH22" s="48"/>
-      <c r="CI22" s="48"/>
-      <c r="CJ22" s="48"/>
-      <c r="CK22" s="48"/>
-      <c r="CL22" s="48"/>
-      <c r="CM22" s="48"/>
-      <c r="CN22" s="48"/>
-      <c r="CO22" s="48"/>
-      <c r="CP22" s="48">
+      <c r="CE23" s="62"/>
+      <c r="CF23" s="62"/>
+      <c r="CG23" s="62"/>
+      <c r="CH23" s="62"/>
+      <c r="CI23" s="62"/>
+      <c r="CJ23" s="62"/>
+      <c r="CK23" s="62"/>
+      <c r="CL23" s="62"/>
+      <c r="CM23" s="62"/>
+      <c r="CN23" s="62"/>
+      <c r="CO23" s="62"/>
+      <c r="CP23" s="62">
         <v>0</v>
       </c>
-      <c r="CQ22" s="48"/>
-      <c r="CR22" s="48"/>
-      <c r="CS22" s="48"/>
-      <c r="CT22" s="48"/>
-      <c r="CU22" s="48"/>
-      <c r="CV22" s="48"/>
-      <c r="CW22" s="48"/>
-      <c r="CX22" s="48"/>
-      <c r="CY22" s="48"/>
-      <c r="CZ22" s="48"/>
-      <c r="DA22" s="48"/>
-      <c r="DB22" s="48">
+      <c r="CQ23" s="62"/>
+      <c r="CR23" s="62"/>
+      <c r="CS23" s="62"/>
+      <c r="CT23" s="62"/>
+      <c r="CU23" s="62"/>
+      <c r="CV23" s="62"/>
+      <c r="CW23" s="62"/>
+      <c r="CX23" s="62"/>
+      <c r="CY23" s="62"/>
+      <c r="CZ23" s="62"/>
+      <c r="DA23" s="62"/>
+      <c r="DB23" s="62">
         <v>0</v>
       </c>
-      <c r="DC22" s="48"/>
-      <c r="DD22" s="48"/>
-      <c r="DE22" s="48"/>
-      <c r="DF22" s="48"/>
-      <c r="DG22" s="48"/>
-      <c r="DH22" s="48"/>
-      <c r="DI22" s="48"/>
-      <c r="DJ22" s="48"/>
-      <c r="DK22" s="48"/>
-      <c r="DL22" s="48"/>
-      <c r="DM22" s="48"/>
-      <c r="DN22" s="48">
+      <c r="DC23" s="62"/>
+      <c r="DD23" s="62"/>
+      <c r="DE23" s="62"/>
+      <c r="DF23" s="62"/>
+      <c r="DG23" s="62"/>
+      <c r="DH23" s="62"/>
+      <c r="DI23" s="62"/>
+      <c r="DJ23" s="62"/>
+      <c r="DK23" s="62"/>
+      <c r="DL23" s="62"/>
+      <c r="DM23" s="62"/>
+      <c r="DN23" s="62">
         <v>0</v>
       </c>
-      <c r="DO22" s="48"/>
-      <c r="DP22" s="48"/>
-      <c r="DQ22" s="48"/>
-      <c r="DR22" s="48"/>
-      <c r="DS22" s="48"/>
-      <c r="DT22" s="48"/>
-      <c r="DU22" s="48"/>
-      <c r="DV22" s="48"/>
-      <c r="DW22" s="48"/>
-      <c r="DX22" s="48"/>
-      <c r="DY22" s="48"/>
-      <c r="DZ22" s="48">
+      <c r="DO23" s="62"/>
+      <c r="DP23" s="62"/>
+      <c r="DQ23" s="62"/>
+      <c r="DR23" s="62"/>
+      <c r="DS23" s="62"/>
+      <c r="DT23" s="62"/>
+      <c r="DU23" s="62"/>
+      <c r="DV23" s="62"/>
+      <c r="DW23" s="62"/>
+      <c r="DX23" s="62"/>
+      <c r="DY23" s="62"/>
+      <c r="DZ23" s="62">
         <v>0</v>
       </c>
-      <c r="EA22" s="48"/>
-      <c r="EB22" s="48"/>
-      <c r="EC22" s="48"/>
-      <c r="ED22" s="48"/>
-      <c r="EE22" s="48"/>
-      <c r="EF22" s="48"/>
-      <c r="EG22" s="48"/>
-      <c r="EH22" s="48"/>
-      <c r="EI22" s="48"/>
-      <c r="EJ22" s="48"/>
-      <c r="EK22" s="48"/>
-      <c r="EL22" s="48">
+      <c r="EA23" s="62"/>
+      <c r="EB23" s="62"/>
+      <c r="EC23" s="62"/>
+      <c r="ED23" s="62"/>
+      <c r="EE23" s="62"/>
+      <c r="EF23" s="62"/>
+      <c r="EG23" s="62"/>
+      <c r="EH23" s="62"/>
+      <c r="EI23" s="62"/>
+      <c r="EJ23" s="62"/>
+      <c r="EK23" s="62"/>
+      <c r="EL23" s="62">
         <v>0</v>
       </c>
-      <c r="EM22" s="48"/>
-      <c r="EN22" s="48"/>
-      <c r="EO22" s="48"/>
-      <c r="EP22" s="48"/>
-      <c r="EQ22" s="48"/>
-      <c r="ER22" s="48"/>
-      <c r="ES22" s="48"/>
-      <c r="ET22" s="48"/>
-      <c r="EU22" s="48"/>
-      <c r="EV22" s="48"/>
-      <c r="EW22" s="48"/>
-      <c r="EX22" s="48">
+      <c r="EM23" s="62"/>
+      <c r="EN23" s="62"/>
+      <c r="EO23" s="62"/>
+      <c r="EP23" s="62"/>
+      <c r="EQ23" s="62"/>
+      <c r="ER23" s="62"/>
+      <c r="ES23" s="62"/>
+      <c r="ET23" s="62"/>
+      <c r="EU23" s="62"/>
+      <c r="EV23" s="62"/>
+      <c r="EW23" s="62"/>
+      <c r="EX23" s="62">
         <v>0</v>
       </c>
-      <c r="EY22" s="48"/>
-      <c r="EZ22" s="48"/>
-      <c r="FA22" s="48"/>
-      <c r="FB22" s="48"/>
-      <c r="FC22" s="48"/>
-      <c r="FD22" s="48"/>
-      <c r="FE22" s="48"/>
-      <c r="FF22" s="48"/>
-      <c r="FG22" s="48"/>
-      <c r="FH22" s="48"/>
-      <c r="FI22" s="48"/>
-    </row>
-    <row r="23" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="5"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
-      <c r="Q23" s="5"/>
-      <c r="R23" s="5"/>
-      <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
-      <c r="U23" s="5"/>
-      <c r="V23" s="5"/>
-      <c r="W23" s="5"/>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-      <c r="AA23" s="5"/>
-      <c r="AB23" s="5"/>
-      <c r="AC23" s="5"/>
-      <c r="AD23" s="5"/>
-      <c r="AE23" s="5"/>
-      <c r="AF23" s="5"/>
-      <c r="AG23" s="5"/>
-      <c r="AH23" s="5"/>
-      <c r="AI23" s="5"/>
-      <c r="AJ23" s="5"/>
-      <c r="AK23" s="5"/>
-      <c r="AL23" s="5"/>
-      <c r="AM23" s="5"/>
-      <c r="AN23" s="5"/>
-      <c r="AO23" s="5"/>
-      <c r="AP23" s="5"/>
-      <c r="AQ23" s="5"/>
-      <c r="AR23" s="5"/>
-      <c r="AS23" s="5"/>
-      <c r="AT23" s="5"/>
-      <c r="AU23" s="5"/>
-      <c r="AV23" s="5"/>
-      <c r="AW23" s="5"/>
-      <c r="AX23" s="5"/>
-      <c r="AY23" s="5"/>
-      <c r="AZ23" s="5"/>
-      <c r="BA23" s="5"/>
-      <c r="BB23" s="5"/>
-      <c r="BC23" s="5"/>
-      <c r="BD23" s="5"/>
-      <c r="BE23" s="5"/>
-      <c r="BF23" s="5"/>
-      <c r="BG23" s="5"/>
-      <c r="BH23" s="5"/>
-      <c r="BI23" s="5"/>
-      <c r="BJ23" s="5"/>
-      <c r="BK23" s="5"/>
-      <c r="BL23" s="5"/>
-      <c r="BM23" s="5"/>
-      <c r="BN23" s="5"/>
-      <c r="BO23" s="5"/>
-      <c r="BP23" s="5"/>
-      <c r="BQ23" s="5"/>
-      <c r="BR23" s="5"/>
-      <c r="BS23" s="5"/>
-      <c r="BT23" s="5"/>
-      <c r="BU23" s="5"/>
-      <c r="BV23" s="5"/>
-      <c r="BW23" s="5"/>
-      <c r="BX23" s="5"/>
-      <c r="BY23" s="5"/>
-      <c r="BZ23" s="5"/>
-      <c r="CA23" s="5"/>
-      <c r="CB23" s="5"/>
-      <c r="CC23" s="5"/>
-      <c r="CD23" s="5"/>
-      <c r="CE23" s="5"/>
-      <c r="CF23" s="5"/>
-      <c r="CG23" s="5"/>
-      <c r="CH23" s="5"/>
-      <c r="CI23" s="5"/>
-      <c r="CJ23" s="5"/>
-      <c r="CK23" s="5"/>
-      <c r="CL23" s="5"/>
-      <c r="CM23" s="5"/>
-      <c r="CN23" s="5"/>
-      <c r="CO23" s="5"/>
-      <c r="CP23" s="5"/>
-      <c r="CQ23" s="5"/>
-      <c r="CR23" s="5"/>
-      <c r="CS23" s="5"/>
-      <c r="CT23" s="5"/>
-      <c r="CU23" s="5"/>
-      <c r="CV23" s="5"/>
-      <c r="CW23" s="5"/>
-      <c r="CX23" s="5"/>
-      <c r="CY23" s="5"/>
-      <c r="CZ23" s="5"/>
-      <c r="DA23" s="5"/>
-      <c r="DB23" s="5"/>
-      <c r="DC23" s="5"/>
-      <c r="DD23" s="5"/>
-      <c r="DE23" s="5"/>
-      <c r="DF23" s="5"/>
-      <c r="DG23" s="5"/>
-      <c r="DH23" s="5"/>
-      <c r="DI23" s="5"/>
-      <c r="DJ23" s="5"/>
-      <c r="DK23" s="5"/>
-      <c r="DL23" s="5"/>
-      <c r="DM23" s="5"/>
-      <c r="DN23" s="5"/>
-      <c r="DO23" s="5"/>
-      <c r="DP23" s="5"/>
-      <c r="DQ23" s="5"/>
-      <c r="DR23" s="5"/>
-      <c r="DS23" s="5"/>
-      <c r="DT23" s="5"/>
-      <c r="DU23" s="5"/>
-      <c r="DV23" s="5"/>
-      <c r="DW23" s="5"/>
-      <c r="DX23" s="5"/>
-      <c r="DY23" s="5"/>
-      <c r="DZ23" s="5"/>
-      <c r="EA23" s="5"/>
-      <c r="EB23" s="5"/>
-      <c r="EC23" s="5"/>
-      <c r="ED23" s="5"/>
-      <c r="EE23" s="5"/>
-      <c r="EF23" s="5"/>
-      <c r="EG23" s="5"/>
-      <c r="EH23" s="5"/>
-      <c r="EI23" s="5"/>
-      <c r="EJ23" s="5"/>
-      <c r="EK23" s="5"/>
-      <c r="EL23" s="5"/>
-      <c r="EM23" s="5"/>
-      <c r="EN23" s="5"/>
-      <c r="EO23" s="5"/>
-      <c r="EP23" s="5"/>
-      <c r="EQ23" s="5"/>
-      <c r="ER23" s="5"/>
-      <c r="ES23" s="5"/>
-      <c r="ET23" s="5"/>
-      <c r="EU23" s="5"/>
-      <c r="EV23" s="5"/>
-      <c r="EW23" s="5"/>
-      <c r="EX23" s="5"/>
-      <c r="EY23" s="5"/>
-      <c r="EZ23" s="5"/>
-      <c r="FA23" s="5"/>
-      <c r="FB23" s="5"/>
-      <c r="FC23" s="5"/>
-      <c r="FD23" s="5"/>
-      <c r="FE23" s="5"/>
-      <c r="FF23" s="5"/>
-      <c r="FG23" s="5"/>
-      <c r="FH23" s="5"/>
-      <c r="FI23" s="5"/>
+      <c r="EY23" s="62"/>
+      <c r="EZ23" s="62"/>
+      <c r="FA23" s="62"/>
+      <c r="FB23" s="62"/>
+      <c r="FC23" s="62"/>
+      <c r="FD23" s="62"/>
+      <c r="FE23" s="62"/>
+      <c r="FF23" s="62"/>
+      <c r="FG23" s="62"/>
+      <c r="FH23" s="62"/>
+      <c r="FI23" s="62"/>
     </row>
     <row r="24" spans="1:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B24" s="4"/>
+      <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="5"/>
       <c r="E24" s="5"/>
@@ -11230,53 +11236,219 @@
       <c r="FH45" s="5"/>
       <c r="FI45" s="5"/>
     </row>
+    <row r="46" spans="2:165" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="4"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="5"/>
+      <c r="V46" s="5"/>
+      <c r="W46" s="5"/>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5"/>
+      <c r="AA46" s="5"/>
+      <c r="AB46" s="5"/>
+      <c r="AC46" s="5"/>
+      <c r="AD46" s="5"/>
+      <c r="AE46" s="5"/>
+      <c r="AF46" s="5"/>
+      <c r="AG46" s="5"/>
+      <c r="AH46" s="5"/>
+      <c r="AI46" s="5"/>
+      <c r="AJ46" s="5"/>
+      <c r="AK46" s="5"/>
+      <c r="AL46" s="5"/>
+      <c r="AM46" s="5"/>
+      <c r="AN46" s="5"/>
+      <c r="AO46" s="5"/>
+      <c r="AP46" s="5"/>
+      <c r="AQ46" s="5"/>
+      <c r="AR46" s="5"/>
+      <c r="AS46" s="5"/>
+      <c r="AT46" s="5"/>
+      <c r="AU46" s="5"/>
+      <c r="AV46" s="5"/>
+      <c r="AW46" s="5"/>
+      <c r="AX46" s="5"/>
+      <c r="AY46" s="5"/>
+      <c r="AZ46" s="5"/>
+      <c r="BA46" s="5"/>
+      <c r="BB46" s="5"/>
+      <c r="BC46" s="5"/>
+      <c r="BD46" s="5"/>
+      <c r="BE46" s="5"/>
+      <c r="BF46" s="5"/>
+      <c r="BG46" s="5"/>
+      <c r="BH46" s="5"/>
+      <c r="BI46" s="5"/>
+      <c r="BJ46" s="5"/>
+      <c r="BK46" s="5"/>
+      <c r="BL46" s="5"/>
+      <c r="BM46" s="5"/>
+      <c r="BN46" s="5"/>
+      <c r="BO46" s="5"/>
+      <c r="BP46" s="5"/>
+      <c r="BQ46" s="5"/>
+      <c r="BR46" s="5"/>
+      <c r="BS46" s="5"/>
+      <c r="BT46" s="5"/>
+      <c r="BU46" s="5"/>
+      <c r="BV46" s="5"/>
+      <c r="BW46" s="5"/>
+      <c r="BX46" s="5"/>
+      <c r="BY46" s="5"/>
+      <c r="BZ46" s="5"/>
+      <c r="CA46" s="5"/>
+      <c r="CB46" s="5"/>
+      <c r="CC46" s="5"/>
+      <c r="CD46" s="5"/>
+      <c r="CE46" s="5"/>
+      <c r="CF46" s="5"/>
+      <c r="CG46" s="5"/>
+      <c r="CH46" s="5"/>
+      <c r="CI46" s="5"/>
+      <c r="CJ46" s="5"/>
+      <c r="CK46" s="5"/>
+      <c r="CL46" s="5"/>
+      <c r="CM46" s="5"/>
+      <c r="CN46" s="5"/>
+      <c r="CO46" s="5"/>
+      <c r="CP46" s="5"/>
+      <c r="CQ46" s="5"/>
+      <c r="CR46" s="5"/>
+      <c r="CS46" s="5"/>
+      <c r="CT46" s="5"/>
+      <c r="CU46" s="5"/>
+      <c r="CV46" s="5"/>
+      <c r="CW46" s="5"/>
+      <c r="CX46" s="5"/>
+      <c r="CY46" s="5"/>
+      <c r="CZ46" s="5"/>
+      <c r="DA46" s="5"/>
+      <c r="DB46" s="5"/>
+      <c r="DC46" s="5"/>
+      <c r="DD46" s="5"/>
+      <c r="DE46" s="5"/>
+      <c r="DF46" s="5"/>
+      <c r="DG46" s="5"/>
+      <c r="DH46" s="5"/>
+      <c r="DI46" s="5"/>
+      <c r="DJ46" s="5"/>
+      <c r="DK46" s="5"/>
+      <c r="DL46" s="5"/>
+      <c r="DM46" s="5"/>
+      <c r="DN46" s="5"/>
+      <c r="DO46" s="5"/>
+      <c r="DP46" s="5"/>
+      <c r="DQ46" s="5"/>
+      <c r="DR46" s="5"/>
+      <c r="DS46" s="5"/>
+      <c r="DT46" s="5"/>
+      <c r="DU46" s="5"/>
+      <c r="DV46" s="5"/>
+      <c r="DW46" s="5"/>
+      <c r="DX46" s="5"/>
+      <c r="DY46" s="5"/>
+      <c r="DZ46" s="5"/>
+      <c r="EA46" s="5"/>
+      <c r="EB46" s="5"/>
+      <c r="EC46" s="5"/>
+      <c r="ED46" s="5"/>
+      <c r="EE46" s="5"/>
+      <c r="EF46" s="5"/>
+      <c r="EG46" s="5"/>
+      <c r="EH46" s="5"/>
+      <c r="EI46" s="5"/>
+      <c r="EJ46" s="5"/>
+      <c r="EK46" s="5"/>
+      <c r="EL46" s="5"/>
+      <c r="EM46" s="5"/>
+      <c r="EN46" s="5"/>
+      <c r="EO46" s="5"/>
+      <c r="EP46" s="5"/>
+      <c r="EQ46" s="5"/>
+      <c r="ER46" s="5"/>
+      <c r="ES46" s="5"/>
+      <c r="ET46" s="5"/>
+      <c r="EU46" s="5"/>
+      <c r="EV46" s="5"/>
+      <c r="EW46" s="5"/>
+      <c r="EX46" s="5"/>
+      <c r="EY46" s="5"/>
+      <c r="EZ46" s="5"/>
+      <c r="FA46" s="5"/>
+      <c r="FB46" s="5"/>
+      <c r="FC46" s="5"/>
+      <c r="FD46" s="5"/>
+      <c r="FE46" s="5"/>
+      <c r="FF46" s="5"/>
+      <c r="FG46" s="5"/>
+      <c r="FH46" s="5"/>
+      <c r="FI46" s="5"/>
+    </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="DB21:DM21"/>
+    <mergeCell ref="BF23:BQ23"/>
+    <mergeCell ref="BR23:CC23"/>
+    <mergeCell ref="CD23:CO23"/>
+    <mergeCell ref="EX23:FI23"/>
+    <mergeCell ref="CP23:DA23"/>
+    <mergeCell ref="DB23:DM23"/>
+    <mergeCell ref="DN23:DY23"/>
+    <mergeCell ref="DZ23:EK23"/>
+    <mergeCell ref="EL23:EW23"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="AH23:AS23"/>
+    <mergeCell ref="AT23:BE23"/>
+    <mergeCell ref="J2:U2"/>
+    <mergeCell ref="J22:U22"/>
+    <mergeCell ref="J23:U23"/>
+    <mergeCell ref="V23:AG23"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D22:I22"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="DN22:DY22"/>
+    <mergeCell ref="DZ22:EK22"/>
+    <mergeCell ref="EL22:EW22"/>
+    <mergeCell ref="EL2:EW2"/>
+    <mergeCell ref="EX2:FI2"/>
+    <mergeCell ref="EX22:FI22"/>
+    <mergeCell ref="DZ2:EK2"/>
+    <mergeCell ref="DN2:DY2"/>
+    <mergeCell ref="DB22:DM22"/>
     <mergeCell ref="DB2:DM2"/>
     <mergeCell ref="CP2:DA2"/>
     <mergeCell ref="BF2:BQ2"/>
     <mergeCell ref="V2:AG2"/>
-    <mergeCell ref="CP21:DA21"/>
+    <mergeCell ref="CP22:DA22"/>
     <mergeCell ref="CD2:CO2"/>
-    <mergeCell ref="CD21:CO21"/>
+    <mergeCell ref="CD22:CO22"/>
     <mergeCell ref="BR2:CC2"/>
-    <mergeCell ref="BR21:CC21"/>
-    <mergeCell ref="BF21:BQ21"/>
+    <mergeCell ref="BR22:CC22"/>
+    <mergeCell ref="BF22:BQ22"/>
     <mergeCell ref="AT2:BE2"/>
-    <mergeCell ref="AT21:BE21"/>
+    <mergeCell ref="AT22:BE22"/>
     <mergeCell ref="AH2:AS2"/>
-    <mergeCell ref="AH21:AS21"/>
-    <mergeCell ref="V21:AG21"/>
-    <mergeCell ref="DN21:DY21"/>
-    <mergeCell ref="DZ21:EK21"/>
-    <mergeCell ref="EL21:EW21"/>
-    <mergeCell ref="EL2:EW2"/>
-    <mergeCell ref="EX2:FI2"/>
-    <mergeCell ref="EX21:FI21"/>
-    <mergeCell ref="DZ2:EK2"/>
-    <mergeCell ref="DN2:DY2"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
     <mergeCell ref="AH22:AS22"/>
-    <mergeCell ref="AT22:BE22"/>
-    <mergeCell ref="J2:U2"/>
-    <mergeCell ref="J21:U21"/>
-    <mergeCell ref="J22:U22"/>
     <mergeCell ref="V22:AG22"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D21:I21"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="BF22:BQ22"/>
-    <mergeCell ref="BR22:CC22"/>
-    <mergeCell ref="CD22:CO22"/>
-    <mergeCell ref="EX22:FI22"/>
-    <mergeCell ref="CP22:DA22"/>
-    <mergeCell ref="DB22:DM22"/>
-    <mergeCell ref="DN22:DY22"/>
-    <mergeCell ref="DZ22:EK22"/>
-    <mergeCell ref="EL22:EW22"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="62" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
